--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="F14" t="n">
-        <v>7.15</v>
+        <v>7.33</v>
       </c>
       <c r="G14" t="n">
-        <v>248.2</v>
+        <v>235.5</v>
       </c>
       <c r="H14" t="n">
-        <v>75.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>13.75</v>
+        <v>-19.83</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6</v>
+        <v>62.25</v>
       </c>
       <c r="L14" t="n">
-        <v>14.85</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:33:13</t>
+          <t>04:34:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="F15" t="n">
-        <v>7.39</v>
+        <v>6.98</v>
       </c>
       <c r="G15" t="n">
-        <v>233.7</v>
+        <v>227.7</v>
       </c>
       <c r="H15" t="n">
-        <v>88.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-24.56</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-70.16</v>
+        <v>132.16</v>
       </c>
       <c r="L15" t="n">
-        <v>74.34</v>
+        <v>165.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:21</t>
+          <t>04:35:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.15</v>
+        <v>0.96</v>
       </c>
       <c r="F16" t="n">
-        <v>6.89</v>
+        <v>7.82</v>
       </c>
       <c r="G16" t="n">
-        <v>239.7</v>
+        <v>240.1</v>
       </c>
       <c r="H16" t="n">
-        <v>73.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.77</v>
+        <v>-20.48</v>
       </c>
       <c r="K16" t="n">
-        <v>65.58</v>
+        <v>-66.3</v>
       </c>
       <c r="L16" t="n">
-        <v>68.5</v>
+        <v>69.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:04</t>
+          <t>04:39:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="F17" t="n">
-        <v>6.42</v>
+        <v>7.45</v>
       </c>
       <c r="G17" t="n">
-        <v>238.3</v>
+        <v>237.3</v>
       </c>
       <c r="H17" t="n">
-        <v>79.8</v>
+        <v>80.5</v>
       </c>
       <c r="I17" t="n">
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.58</v>
+        <v>-123.46</v>
       </c>
       <c r="K17" t="n">
-        <v>8.779999999999999</v>
+        <v>180.24</v>
       </c>
       <c r="L17" t="n">
-        <v>9.15</v>
+        <v>218.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:27</t>
+          <t>04:42:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.71</v>
+        <v>0.89</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6.94</v>
       </c>
       <c r="G18" t="n">
-        <v>237.8</v>
+        <v>238.6</v>
       </c>
       <c r="H18" t="n">
-        <v>85.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>63.56</v>
+        <v>18.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-60.89</v>
+        <v>-84.37</v>
       </c>
       <c r="L18" t="n">
-        <v>88.02</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:43:58</t>
+          <t>04:43:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="F19" t="n">
-        <v>7.03</v>
+        <v>6.93</v>
       </c>
       <c r="G19" t="n">
-        <v>243.2</v>
+        <v>233.4</v>
       </c>
       <c r="H19" t="n">
-        <v>85.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>104.75</v>
+        <v>9.92</v>
       </c>
       <c r="K19" t="n">
-        <v>35.56</v>
+        <v>178.58</v>
       </c>
       <c r="L19" t="n">
-        <v>110.62</v>
+        <v>178.86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:48:41</t>
+          <t>04:47:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.47</v>
+        <v>0.71</v>
       </c>
       <c r="F20" t="n">
-        <v>6.74</v>
+        <v>7.39</v>
       </c>
       <c r="G20" t="n">
-        <v>252.4</v>
+        <v>249.1</v>
       </c>
       <c r="H20" t="n">
-        <v>80.2</v>
+        <v>80.7</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-24.87</v>
+        <v>21.66</v>
       </c>
       <c r="K20" t="n">
-        <v>-81.98999999999999</v>
+        <v>-103.94</v>
       </c>
       <c r="L20" t="n">
-        <v>85.68000000000001</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:50:18</t>
+          <t>04:48:23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="F21" t="n">
-        <v>7.17</v>
+        <v>7.01</v>
       </c>
       <c r="G21" t="n">
-        <v>242.9</v>
+        <v>238.7</v>
       </c>
       <c r="H21" t="n">
-        <v>79</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-146.24</v>
+        <v>168.83</v>
       </c>
       <c r="K21" t="n">
-        <v>4.46</v>
+        <v>427.98</v>
       </c>
       <c r="L21" t="n">
-        <v>146.31</v>
+        <v>460.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:52:14</t>
+          <t>04:50:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="F22" t="n">
-        <v>6.32</v>
+        <v>6.73</v>
       </c>
       <c r="G22" t="n">
-        <v>258.5</v>
+        <v>248</v>
       </c>
       <c r="H22" t="n">
-        <v>82.7</v>
+        <v>83.2</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-145.1</v>
+        <v>-13.9</v>
       </c>
       <c r="K22" t="n">
-        <v>102.91</v>
+        <v>113.14</v>
       </c>
       <c r="L22" t="n">
-        <v>177.89</v>
+        <v>113.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:56:46</t>
+          <t>04:55:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.24</v>
+        <v>0.86</v>
       </c>
       <c r="F23" t="n">
-        <v>7.01</v>
+        <v>6.54</v>
       </c>
       <c r="G23" t="n">
-        <v>249.4</v>
+        <v>253.9</v>
       </c>
       <c r="H23" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>223.98</v>
+        <v>-255.04</v>
       </c>
       <c r="K23" t="n">
-        <v>1.67</v>
+        <v>-331.37</v>
       </c>
       <c r="L23" t="n">
-        <v>223.99</v>
+        <v>418.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:59:13</t>
+          <t>04:57:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="F24" t="n">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
       <c r="G24" t="n">
-        <v>221.6</v>
+        <v>242</v>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>126.5</v>
+        <v>84.62</v>
       </c>
       <c r="K24" t="n">
-        <v>-21.89</v>
+        <v>-72.81</v>
       </c>
       <c r="L24" t="n">
-        <v>128.38</v>
+        <v>111.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:01:10</t>
+          <t>04:59:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>1.48</v>
       </c>
       <c r="F25" t="n">
-        <v>7.51</v>
+        <v>6.59</v>
       </c>
       <c r="G25" t="n">
-        <v>223.8</v>
+        <v>241.2</v>
       </c>
       <c r="H25" t="n">
-        <v>77.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>191.39</v>
+        <v>87.58</v>
       </c>
       <c r="K25" t="n">
-        <v>15.42</v>
+        <v>-329.44</v>
       </c>
       <c r="L25" t="n">
-        <v>192.01</v>
+        <v>340.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:05:21</t>
+          <t>05:04:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.76</v>
+        <v>1.56</v>
       </c>
       <c r="F26" t="n">
-        <v>7.03</v>
+        <v>7.41</v>
       </c>
       <c r="G26" t="n">
-        <v>241.5</v>
+        <v>234.3</v>
       </c>
       <c r="H26" t="n">
-        <v>83.2</v>
+        <v>80.5</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>340.79</v>
+        <v>-233.32</v>
       </c>
       <c r="K26" t="n">
-        <v>16.54</v>
+        <v>48.32</v>
       </c>
       <c r="L26" t="n">
-        <v>341.19</v>
+        <v>238.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:06:42</t>
+          <t>05:06:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="F27" t="n">
-        <v>7.29</v>
+        <v>7.52</v>
       </c>
       <c r="G27" t="n">
-        <v>230.4</v>
+        <v>242.6</v>
       </c>
       <c r="H27" t="n">
-        <v>87.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>511.77</v>
+        <v>180.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-37.92</v>
+        <v>-44.74</v>
       </c>
       <c r="L27" t="n">
-        <v>513.17</v>
+        <v>185.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:09:11</t>
+          <t>05:07:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="F28" t="n">
-        <v>7.37</v>
+        <v>7.12</v>
       </c>
       <c r="G28" t="n">
-        <v>244.8</v>
+        <v>237.6</v>
       </c>
       <c r="H28" t="n">
-        <v>78.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-98.06</v>
+        <v>-64.47</v>
       </c>
       <c r="K28" t="n">
-        <v>-169.14</v>
+        <v>-144.51</v>
       </c>
       <c r="L28" t="n">
-        <v>195.51</v>
+        <v>158.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:20:21</t>
+          <t>05:16:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.33</v>
+        <v>0.95</v>
       </c>
       <c r="F29" t="n">
-        <v>7.72</v>
+        <v>7.39</v>
       </c>
       <c r="G29" t="n">
-        <v>238</v>
+        <v>240.7</v>
       </c>
       <c r="H29" t="n">
-        <v>77.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>59.87</v>
+        <v>-40.11</v>
       </c>
       <c r="K29" t="n">
-        <v>61.4</v>
+        <v>-42.91</v>
       </c>
       <c r="L29" t="n">
-        <v>85.75</v>
+        <v>58.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:21:08</t>
+          <t>05:17:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="F30" t="n">
-        <v>7.44</v>
+        <v>6.53</v>
       </c>
       <c r="G30" t="n">
-        <v>258</v>
+        <v>227.6</v>
       </c>
       <c r="H30" t="n">
-        <v>77.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>56.83</v>
+        <v>145.09</v>
       </c>
       <c r="K30" t="n">
-        <v>55.73</v>
+        <v>112.08</v>
       </c>
       <c r="L30" t="n">
-        <v>79.59</v>
+        <v>183.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:23:50</t>
+          <t>05:19:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="F31" t="n">
-        <v>7.67</v>
+        <v>6.77</v>
       </c>
       <c r="G31" t="n">
-        <v>236.7</v>
+        <v>238.2</v>
       </c>
       <c r="H31" t="n">
-        <v>91.2</v>
+        <v>81.3</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.65</v>
+        <v>-35.57</v>
       </c>
       <c r="K31" t="n">
-        <v>-46.35</v>
+        <v>64.02</v>
       </c>
       <c r="L31" t="n">
-        <v>46.43</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:27:44</t>
+          <t>05:23:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.33</v>
+        <v>0.82</v>
       </c>
       <c r="F32" t="n">
-        <v>7.04</v>
+        <v>7.22</v>
       </c>
       <c r="G32" t="n">
-        <v>238.3</v>
+        <v>239.3</v>
       </c>
       <c r="H32" t="n">
-        <v>81.7</v>
+        <v>77.2</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>17.18</v>
+        <v>19.21</v>
       </c>
       <c r="K32" t="n">
-        <v>-82.47</v>
+        <v>-26.87</v>
       </c>
       <c r="L32" t="n">
-        <v>84.23999999999999</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:30:11</t>
+          <t>05:25:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="F33" t="n">
-        <v>7.15</v>
+        <v>6.99</v>
       </c>
       <c r="G33" t="n">
-        <v>256.8</v>
+        <v>242.7</v>
       </c>
       <c r="H33" t="n">
-        <v>85.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-56.23</v>
+        <v>145.59</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.03</v>
+        <v>37.74</v>
       </c>
       <c r="L33" t="n">
-        <v>56.27</v>
+        <v>150.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:31:40</t>
+          <t>05:26:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.96</v>
+        <v>1.17</v>
       </c>
       <c r="F34" t="n">
-        <v>6.89</v>
+        <v>6.97</v>
       </c>
       <c r="G34" t="n">
-        <v>245.9</v>
+        <v>239.1</v>
       </c>
       <c r="H34" t="n">
-        <v>77.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>35.16</v>
+        <v>40.89</v>
       </c>
       <c r="K34" t="n">
-        <v>-26.62</v>
+        <v>-55.94</v>
       </c>
       <c r="L34" t="n">
-        <v>44.1</v>
+        <v>69.29000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:37:44</t>
+          <t>05:31:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F35" t="n">
-        <v>7.17</v>
+        <v>6.46</v>
       </c>
       <c r="G35" t="n">
-        <v>262</v>
+        <v>226.1</v>
       </c>
       <c r="H35" t="n">
-        <v>68.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>75.70999999999999</v>
+        <v>172.05</v>
       </c>
       <c r="K35" t="n">
-        <v>-37.99</v>
+        <v>-91.84</v>
       </c>
       <c r="L35" t="n">
-        <v>84.70999999999999</v>
+        <v>195.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:39:31</t>
+          <t>05:34:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="F36" t="n">
-        <v>6.81</v>
+        <v>7.17</v>
       </c>
       <c r="G36" t="n">
-        <v>237.4</v>
+        <v>240.5</v>
       </c>
       <c r="H36" t="n">
-        <v>86.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-44.11</v>
+        <v>58.58</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.6</v>
+        <v>-112.01</v>
       </c>
       <c r="L36" t="n">
-        <v>45.15</v>
+        <v>126.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:41:04</t>
+          <t>05:36:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="F37" t="n">
-        <v>7.84</v>
+        <v>7.32</v>
       </c>
       <c r="G37" t="n">
-        <v>251.9</v>
+        <v>249.6</v>
       </c>
       <c r="H37" t="n">
-        <v>81.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-47.82</v>
+        <v>11.78</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8</v>
+        <v>130.09</v>
       </c>
       <c r="L37" t="n">
-        <v>47.83</v>
+        <v>130.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:46:00</t>
+          <t>05:40:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="F38" t="n">
-        <v>7.41</v>
+        <v>7.07</v>
       </c>
       <c r="G38" t="n">
-        <v>241.6</v>
+        <v>245.7</v>
       </c>
       <c r="H38" t="n">
-        <v>83.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-123.77</v>
+        <v>436.86</v>
       </c>
       <c r="K38" t="n">
-        <v>-134.43</v>
+        <v>-259.25</v>
       </c>
       <c r="L38" t="n">
-        <v>182.73</v>
+        <v>507.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:47:12</t>
+          <t>05:43:26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="F39" t="n">
-        <v>7.2</v>
+        <v>6.81</v>
       </c>
       <c r="G39" t="n">
-        <v>238.6</v>
+        <v>234.9</v>
       </c>
       <c r="H39" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="I39" t="n">
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-123.62</v>
+        <v>317.7</v>
       </c>
       <c r="K39" t="n">
-        <v>6.47</v>
+        <v>-177.03</v>
       </c>
       <c r="L39" t="n">
-        <v>123.79</v>
+        <v>363.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:48:33</t>
+          <t>05:45:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="F40" t="n">
-        <v>6.8</v>
+        <v>6.38</v>
       </c>
       <c r="G40" t="n">
-        <v>246.3</v>
+        <v>232</v>
       </c>
       <c r="H40" t="n">
-        <v>79.7</v>
+        <v>83.3</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-229.37</v>
+        <v>-267.64</v>
       </c>
       <c r="K40" t="n">
-        <v>-60.67</v>
+        <v>246.55</v>
       </c>
       <c r="L40" t="n">
-        <v>237.26</v>
+        <v>363.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:52:07</t>
+          <t>05:51:31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.67</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>6.95</v>
+        <v>7.92</v>
       </c>
       <c r="G41" t="n">
-        <v>245.9</v>
+        <v>230.5</v>
       </c>
       <c r="H41" t="n">
-        <v>89.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-113.46</v>
+        <v>-83.41</v>
       </c>
       <c r="K41" t="n">
-        <v>-149.33</v>
+        <v>-85.8</v>
       </c>
       <c r="L41" t="n">
-        <v>187.54</v>
+        <v>119.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:53:20</t>
+          <t>05:53:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.98</v>
+        <v>1.45</v>
       </c>
       <c r="F42" t="n">
-        <v>6.74</v>
+        <v>7.01</v>
       </c>
       <c r="G42" t="n">
-        <v>238.9</v>
+        <v>240</v>
       </c>
       <c r="H42" t="n">
-        <v>75.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-380.26</v>
+        <v>-317.53</v>
       </c>
       <c r="K42" t="n">
-        <v>35.09</v>
+        <v>511.72</v>
       </c>
       <c r="L42" t="n">
-        <v>381.87</v>
+        <v>602.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:55:06</t>
+          <t>05:55:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="F43" t="n">
-        <v>8.380000000000001</v>
+        <v>6.71</v>
       </c>
       <c r="G43" t="n">
-        <v>241.6</v>
+        <v>235.6</v>
       </c>
       <c r="H43" t="n">
-        <v>84.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="I43" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-33.37</v>
+        <v>-293.37</v>
       </c>
       <c r="K43" t="n">
-        <v>-253.44</v>
+        <v>190.26</v>
       </c>
       <c r="L43" t="n">
-        <v>255.62</v>
+        <v>349.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:34</t>
+          <t>06:08:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="F44" t="n">
-        <v>6.87</v>
+        <v>7.19</v>
       </c>
       <c r="G44" t="n">
-        <v>251.3</v>
+        <v>250.5</v>
       </c>
       <c r="H44" t="n">
-        <v>79.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-30.17</v>
+        <v>-98.95999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.89</v>
+        <v>-78.67</v>
       </c>
       <c r="L44" t="n">
-        <v>30.18</v>
+        <v>126.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:07:57</t>
+          <t>06:10:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="F45" t="n">
-        <v>7.23</v>
+        <v>6.87</v>
       </c>
       <c r="G45" t="n">
-        <v>235.6</v>
+        <v>235.7</v>
       </c>
       <c r="H45" t="n">
-        <v>79.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="I45" t="n">
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>31.07</v>
+        <v>-58.22</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.96</v>
+        <v>29.76</v>
       </c>
       <c r="L45" t="n">
-        <v>45.3</v>
+        <v>65.39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:09:46</t>
+          <t>06:11:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="F46" t="n">
-        <v>6.64</v>
+        <v>7.37</v>
       </c>
       <c r="G46" t="n">
-        <v>237.8</v>
+        <v>253.1</v>
       </c>
       <c r="H46" t="n">
-        <v>68.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.88</v>
+        <v>41.64</v>
       </c>
       <c r="K46" t="n">
-        <v>-33.8</v>
+        <v>-24.85</v>
       </c>
       <c r="L46" t="n">
-        <v>34.02</v>
+        <v>48.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:14:00</t>
+          <t>06:17:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="F47" t="n">
-        <v>6.64</v>
+        <v>6.53</v>
       </c>
       <c r="G47" t="n">
-        <v>234.5</v>
+        <v>256.5</v>
       </c>
       <c r="H47" t="n">
-        <v>79</v>
+        <v>81.2</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>45.43</v>
+        <v>-20.93</v>
       </c>
       <c r="K47" t="n">
-        <v>40.61</v>
+        <v>-143.09</v>
       </c>
       <c r="L47" t="n">
-        <v>60.93</v>
+        <v>144.61</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:16:23</t>
+          <t>06:18:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="F48" t="n">
-        <v>6.68</v>
+        <v>7.17</v>
       </c>
       <c r="G48" t="n">
-        <v>240.2</v>
+        <v>234.3</v>
       </c>
       <c r="H48" t="n">
-        <v>89.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-64.17</v>
+        <v>-74.65000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-48.95</v>
+        <v>-30.18</v>
       </c>
       <c r="L48" t="n">
-        <v>80.70999999999999</v>
+        <v>80.52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:17:27</t>
+          <t>06:20:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="F49" t="n">
-        <v>7.22</v>
+        <v>6.86</v>
       </c>
       <c r="G49" t="n">
-        <v>259.9</v>
+        <v>240.5</v>
       </c>
       <c r="H49" t="n">
-        <v>72.8</v>
+        <v>83.8</v>
       </c>
       <c r="I49" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-77.92</v>
+        <v>13.22</v>
       </c>
       <c r="K49" t="n">
-        <v>-41.75</v>
+        <v>-47.23</v>
       </c>
       <c r="L49" t="n">
-        <v>88.39</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:22:05</t>
+          <t>06:23:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="F50" t="n">
-        <v>6.98</v>
+        <v>6.63</v>
       </c>
       <c r="G50" t="n">
-        <v>239.7</v>
+        <v>245.6</v>
       </c>
       <c r="H50" t="n">
-        <v>79.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>7.39</v>
+        <v>-6.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-31.56</v>
+        <v>-267.67</v>
       </c>
       <c r="L50" t="n">
-        <v>32.42</v>
+        <v>267.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:23:50</t>
+          <t>06:24:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.86</v>
+        <v>1.35</v>
       </c>
       <c r="F51" t="n">
-        <v>7.37</v>
+        <v>7.53</v>
       </c>
       <c r="G51" t="n">
-        <v>225.3</v>
+        <v>257.4</v>
       </c>
       <c r="H51" t="n">
-        <v>78.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-53.76</v>
+        <v>-267.01</v>
       </c>
       <c r="K51" t="n">
-        <v>153.47</v>
+        <v>-99.14</v>
       </c>
       <c r="L51" t="n">
-        <v>162.62</v>
+        <v>284.82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:25:30</t>
+          <t>06:26:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="F52" t="n">
-        <v>6.39</v>
+        <v>6.99</v>
       </c>
       <c r="G52" t="n">
-        <v>245.8</v>
+        <v>250.1</v>
       </c>
       <c r="H52" t="n">
-        <v>82</v>
+        <v>80.7</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-73.58</v>
+        <v>-7.52</v>
       </c>
       <c r="K52" t="n">
-        <v>46.08</v>
+        <v>144.97</v>
       </c>
       <c r="L52" t="n">
-        <v>86.81999999999999</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:31:13</t>
+          <t>06:31:25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="F53" t="n">
-        <v>6.42</v>
+        <v>5.97</v>
       </c>
       <c r="G53" t="n">
-        <v>249.2</v>
+        <v>239</v>
       </c>
       <c r="H53" t="n">
-        <v>82.5</v>
+        <v>79.5</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>89.34</v>
+        <v>25.54</v>
       </c>
       <c r="K53" t="n">
-        <v>149.99</v>
+        <v>33.12</v>
       </c>
       <c r="L53" t="n">
-        <v>174.58</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:32:32</t>
+          <t>06:33:05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="F54" t="n">
-        <v>7.78</v>
+        <v>7.36</v>
       </c>
       <c r="G54" t="n">
-        <v>254.1</v>
+        <v>246.3</v>
       </c>
       <c r="H54" t="n">
-        <v>80.2</v>
+        <v>79.2</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-35.68</v>
+        <v>169.93</v>
       </c>
       <c r="K54" t="n">
-        <v>-47.97</v>
+        <v>-18.28</v>
       </c>
       <c r="L54" t="n">
-        <v>59.79</v>
+        <v>170.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:34:40</t>
+          <t>06:35:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="F55" t="n">
-        <v>7.32</v>
+        <v>6.69</v>
       </c>
       <c r="G55" t="n">
-        <v>250.8</v>
+        <v>230.3</v>
       </c>
       <c r="H55" t="n">
-        <v>76.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-263.21</v>
+        <v>-63.97</v>
       </c>
       <c r="K55" t="n">
-        <v>-175.45</v>
+        <v>-51.2</v>
       </c>
       <c r="L55" t="n">
-        <v>316.33</v>
+        <v>81.94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:41:09</t>
+          <t>06:40:05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="F56" t="n">
-        <v>6.78</v>
+        <v>7.26</v>
       </c>
       <c r="G56" t="n">
-        <v>240.6</v>
+        <v>261.4</v>
       </c>
       <c r="H56" t="n">
-        <v>81.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>294.88</v>
+        <v>-243.19</v>
       </c>
       <c r="K56" t="n">
-        <v>91.29000000000001</v>
+        <v>-4.08</v>
       </c>
       <c r="L56" t="n">
-        <v>308.69</v>
+        <v>243.22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:42:22</t>
+          <t>06:41:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="F57" t="n">
-        <v>6.66</v>
+        <v>6.77</v>
       </c>
       <c r="G57" t="n">
-        <v>238.1</v>
+        <v>229.4</v>
       </c>
       <c r="H57" t="n">
-        <v>79.2</v>
+        <v>84.8</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>-144.35</v>
+        <v>161.31</v>
       </c>
       <c r="K57" t="n">
-        <v>47.34</v>
+        <v>321.49</v>
       </c>
       <c r="L57" t="n">
-        <v>151.91</v>
+        <v>359.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:43:17</t>
+          <t>06:42:31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="F58" t="n">
-        <v>6.97</v>
+        <v>6.83</v>
       </c>
       <c r="G58" t="n">
-        <v>230.1</v>
+        <v>247.3</v>
       </c>
       <c r="H58" t="n">
-        <v>70.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>22.92</v>
+        <v>-164.24</v>
       </c>
       <c r="K58" t="n">
-        <v>312.72</v>
+        <v>-866.35</v>
       </c>
       <c r="L58" t="n">
-        <v>313.56</v>
+        <v>881.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:53:38</t>
+          <t>06:54:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="F59" t="n">
-        <v>6.84</v>
+        <v>7</v>
       </c>
       <c r="G59" t="n">
-        <v>243.3</v>
+        <v>232.6</v>
       </c>
       <c r="H59" t="n">
-        <v>78.7</v>
+        <v>80.7</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.93</v>
+        <v>-78.47</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.75</v>
+        <v>40.51</v>
       </c>
       <c r="L59" t="n">
-        <v>7.99</v>
+        <v>88.31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:15</t>
+          <t>06:56:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.99</v>
+        <v>1.31</v>
       </c>
       <c r="F60" t="n">
-        <v>7.21</v>
+        <v>6.91</v>
       </c>
       <c r="G60" t="n">
-        <v>240.9</v>
+        <v>240.7</v>
       </c>
       <c r="H60" t="n">
-        <v>85.5</v>
+        <v>72.8</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>4.91</v>
+        <v>46.84</v>
       </c>
       <c r="K60" t="n">
-        <v>15.21</v>
+        <v>44.95</v>
       </c>
       <c r="L60" t="n">
-        <v>15.99</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:58:43</t>
+          <t>06:59:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="F61" t="n">
-        <v>6.99</v>
+        <v>7.4</v>
       </c>
       <c r="G61" t="n">
-        <v>240.9</v>
+        <v>234</v>
       </c>
       <c r="H61" t="n">
-        <v>82.8</v>
+        <v>76.5</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-58.31</v>
+        <v>50.35</v>
       </c>
       <c r="K61" t="n">
-        <v>34.29</v>
+        <v>8.4</v>
       </c>
       <c r="L61" t="n">
-        <v>67.64</v>
+        <v>51.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:03:09</t>
+          <t>07:03:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="F62" t="n">
-        <v>6.85</v>
+        <v>6.83</v>
       </c>
       <c r="G62" t="n">
-        <v>226.8</v>
+        <v>246.7</v>
       </c>
       <c r="H62" t="n">
-        <v>75.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-109.79</v>
+        <v>50.49</v>
       </c>
       <c r="K62" t="n">
-        <v>-16.52</v>
+        <v>-4.11</v>
       </c>
       <c r="L62" t="n">
-        <v>111.02</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:05:36</t>
+          <t>07:05:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="F63" t="n">
-        <v>6.73</v>
+        <v>6.42</v>
       </c>
       <c r="G63" t="n">
-        <v>237.3</v>
+        <v>238.8</v>
       </c>
       <c r="H63" t="n">
-        <v>75.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-148.6</v>
+        <v>56.49</v>
       </c>
       <c r="K63" t="n">
-        <v>-44.39</v>
+        <v>72.7</v>
       </c>
       <c r="L63" t="n">
-        <v>155.08</v>
+        <v>92.06999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:06:52</t>
+          <t>07:05:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="F64" t="n">
-        <v>7.3</v>
+        <v>7.49</v>
       </c>
       <c r="G64" t="n">
-        <v>235.7</v>
+        <v>251.5</v>
       </c>
       <c r="H64" t="n">
-        <v>86.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-51.78</v>
+        <v>-16.06</v>
       </c>
       <c r="K64" t="n">
-        <v>61.75</v>
+        <v>-115.05</v>
       </c>
       <c r="L64" t="n">
-        <v>80.59</v>
+        <v>116.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:11:26</t>
+          <t>07:11:04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="F65" t="n">
-        <v>6.86</v>
+        <v>7.35</v>
       </c>
       <c r="G65" t="n">
-        <v>231.5</v>
+        <v>258.2</v>
       </c>
       <c r="H65" t="n">
-        <v>81.3</v>
+        <v>85.8</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>45.86</v>
+        <v>-188.4</v>
       </c>
       <c r="K65" t="n">
-        <v>-47.35</v>
+        <v>39.8</v>
       </c>
       <c r="L65" t="n">
-        <v>65.92</v>
+        <v>192.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:13:34</t>
+          <t>07:12:49</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="F66" t="n">
-        <v>7.05</v>
+        <v>7.06</v>
       </c>
       <c r="G66" t="n">
-        <v>251.2</v>
+        <v>246.4</v>
       </c>
       <c r="H66" t="n">
-        <v>76.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-149.38</v>
+        <v>-311.56</v>
       </c>
       <c r="K66" t="n">
-        <v>-97.26000000000001</v>
+        <v>20.12</v>
       </c>
       <c r="L66" t="n">
-        <v>178.25</v>
+        <v>312.21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:14:55</t>
+          <t>07:14:51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="F67" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="G67" t="n">
-        <v>238.1</v>
+        <v>244</v>
       </c>
       <c r="H67" t="n">
-        <v>82.09999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-68.39</v>
+        <v>-5.58</v>
       </c>
       <c r="K67" t="n">
-        <v>1.72</v>
+        <v>-112.41</v>
       </c>
       <c r="L67" t="n">
-        <v>68.41</v>
+        <v>112.55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:19:01</t>
+          <t>07:19:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="F68" t="n">
-        <v>6.56</v>
+        <v>6.96</v>
       </c>
       <c r="G68" t="n">
-        <v>254.8</v>
+        <v>242.7</v>
       </c>
       <c r="H68" t="n">
-        <v>77.3</v>
+        <v>82.8</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>125.58</v>
+        <v>-106.89</v>
       </c>
       <c r="K68" t="n">
-        <v>-97.56999999999999</v>
+        <v>-104.59</v>
       </c>
       <c r="L68" t="n">
-        <v>159.03</v>
+        <v>149.55</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:20:16</t>
+          <t>07:20:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F69" t="n">
-        <v>7.08</v>
+        <v>7.48</v>
       </c>
       <c r="G69" t="n">
-        <v>251.8</v>
+        <v>232.3</v>
       </c>
       <c r="H69" t="n">
-        <v>79.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>108.61</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>105.51</v>
+        <v>278.19</v>
       </c>
       <c r="L69" t="n">
-        <v>151.42</v>
+        <v>291.93</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:22:17</t>
+          <t>07:21:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="F70" t="n">
-        <v>6.6</v>
+        <v>7.38</v>
       </c>
       <c r="G70" t="n">
-        <v>253.7</v>
+        <v>248.5</v>
       </c>
       <c r="H70" t="n">
-        <v>76.8</v>
+        <v>81.7</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-333.53</v>
+        <v>-446.85</v>
       </c>
       <c r="K70" t="n">
-        <v>-102.98</v>
+        <v>-91.06999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>349.07</v>
+        <v>456.03</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:27:21</t>
+          <t>07:25:59</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="F71" t="n">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="G71" t="n">
-        <v>252.3</v>
+        <v>243.7</v>
       </c>
       <c r="H71" t="n">
-        <v>76.7</v>
+        <v>80.5</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-222.55</v>
+        <v>-197.84</v>
       </c>
       <c r="K71" t="n">
-        <v>-312.51</v>
+        <v>75.92</v>
       </c>
       <c r="L71" t="n">
-        <v>383.66</v>
+        <v>211.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:29:07</t>
+          <t>07:27:36</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="F72" t="n">
         <v>6.65</v>
       </c>
       <c r="G72" t="n">
-        <v>228.3</v>
+        <v>251.4</v>
       </c>
       <c r="H72" t="n">
-        <v>74.5</v>
+        <v>83.3</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-231.38</v>
+        <v>-14.83</v>
       </c>
       <c r="K72" t="n">
-        <v>-117.46</v>
+        <v>698.88</v>
       </c>
       <c r="L72" t="n">
-        <v>259.48</v>
+        <v>699.04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:30:11</t>
+          <t>07:29:12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="F73" t="n">
-        <v>7.26</v>
+        <v>7.65</v>
       </c>
       <c r="G73" t="n">
-        <v>240.7</v>
+        <v>231.7</v>
       </c>
       <c r="H73" t="n">
-        <v>82.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>186.54</v>
+        <v>-75.72</v>
       </c>
       <c r="K73" t="n">
-        <v>-192.84</v>
+        <v>-13.37</v>
       </c>
       <c r="L73" t="n">
-        <v>268.3</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:41:41</t>
+          <t>07:39:38</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="F74" t="n">
-        <v>6.66</v>
+        <v>6.28</v>
       </c>
       <c r="G74" t="n">
-        <v>231.6</v>
+        <v>245.2</v>
       </c>
       <c r="H74" t="n">
-        <v>82.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>48.47</v>
+        <v>82.41</v>
       </c>
       <c r="K74" t="n">
-        <v>21.36</v>
+        <v>40.23</v>
       </c>
       <c r="L74" t="n">
-        <v>52.96</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:43:11</t>
+          <t>07:41:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="F75" t="n">
-        <v>7.05</v>
+        <v>6.92</v>
       </c>
       <c r="G75" t="n">
-        <v>242.1</v>
+        <v>245.8</v>
       </c>
       <c r="H75" t="n">
-        <v>84.8</v>
+        <v>78.3</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>24.3</v>
+        <v>-5.47</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.78</v>
+        <v>129.06</v>
       </c>
       <c r="L75" t="n">
-        <v>24.77</v>
+        <v>129.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:45:29</t>
+          <t>07:44:03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="F76" t="n">
-        <v>6.86</v>
+        <v>7.32</v>
       </c>
       <c r="G76" t="n">
-        <v>248.9</v>
+        <v>242.3</v>
       </c>
       <c r="H76" t="n">
-        <v>88.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-30.65</v>
+        <v>30.88</v>
       </c>
       <c r="K76" t="n">
-        <v>15.23</v>
+        <v>-18.77</v>
       </c>
       <c r="L76" t="n">
-        <v>34.22</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:50:51</t>
+          <t>07:47:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="F77" t="n">
-        <v>7.61</v>
+        <v>7.01</v>
       </c>
       <c r="G77" t="n">
-        <v>245.9</v>
+        <v>232.7</v>
       </c>
       <c r="H77" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-50.31</v>
+        <v>69.75</v>
       </c>
       <c r="K77" t="n">
-        <v>69.2</v>
+        <v>-150.43</v>
       </c>
       <c r="L77" t="n">
-        <v>85.56</v>
+        <v>165.81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:51:46</t>
+          <t>07:49:36</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="F78" t="n">
-        <v>7.14</v>
+        <v>6.77</v>
       </c>
       <c r="G78" t="n">
-        <v>238.7</v>
+        <v>253.4</v>
       </c>
       <c r="H78" t="n">
-        <v>82.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>39.21</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-58.94</v>
+        <v>-55.06</v>
       </c>
       <c r="L78" t="n">
-        <v>70.79000000000001</v>
+        <v>97.65000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:53:33</t>
+          <t>07:51:21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="F79" t="n">
-        <v>7.83</v>
+        <v>6.76</v>
       </c>
       <c r="G79" t="n">
-        <v>254.5</v>
+        <v>261.3</v>
       </c>
       <c r="H79" t="n">
-        <v>77.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>39.67</v>
+        <v>-118.01</v>
       </c>
       <c r="K79" t="n">
-        <v>24.89</v>
+        <v>3.81</v>
       </c>
       <c r="L79" t="n">
-        <v>46.83</v>
+        <v>118.07</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:59:11</t>
+          <t>07:56:04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="F80" t="n">
-        <v>7.68</v>
+        <v>6.9</v>
       </c>
       <c r="G80" t="n">
-        <v>248.5</v>
+        <v>238.6</v>
       </c>
       <c r="H80" t="n">
-        <v>77.7</v>
+        <v>92</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-76.2</v>
+        <v>230.71</v>
       </c>
       <c r="K80" t="n">
-        <v>-147.64</v>
+        <v>143.28</v>
       </c>
       <c r="L80" t="n">
-        <v>166.14</v>
+        <v>271.58</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:00:21</t>
+          <t>07:58:09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.68</v>
+        <v>1.15</v>
       </c>
       <c r="F81" t="n">
-        <v>7.61</v>
+        <v>6.78</v>
       </c>
       <c r="G81" t="n">
-        <v>237.7</v>
+        <v>229.5</v>
       </c>
       <c r="H81" t="n">
-        <v>80.8</v>
+        <v>84.3</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-34.87</v>
+        <v>61.62</v>
       </c>
       <c r="K81" t="n">
-        <v>49.07</v>
+        <v>-40.64</v>
       </c>
       <c r="L81" t="n">
-        <v>60.2</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:01:51</t>
+          <t>08:00:07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.42</v>
+        <v>1.77</v>
       </c>
       <c r="F82" t="n">
-        <v>7.28</v>
+        <v>7.78</v>
       </c>
       <c r="G82" t="n">
-        <v>242.3</v>
+        <v>232.8</v>
       </c>
       <c r="H82" t="n">
-        <v>83.7</v>
+        <v>83.3</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>64.20999999999999</v>
+        <v>258.49</v>
       </c>
       <c r="K82" t="n">
-        <v>107.74</v>
+        <v>302.97</v>
       </c>
       <c r="L82" t="n">
-        <v>125.42</v>
+        <v>398.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:07:01</t>
+          <t>08:06:18</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="F83" t="n">
-        <v>6.44</v>
+        <v>7.47</v>
       </c>
       <c r="G83" t="n">
-        <v>246.1</v>
+        <v>251.4</v>
       </c>
       <c r="H83" t="n">
-        <v>77</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-294.19</v>
+        <v>-57.88</v>
       </c>
       <c r="K83" t="n">
-        <v>-131.85</v>
+        <v>-425.35</v>
       </c>
       <c r="L83" t="n">
-        <v>322.38</v>
+        <v>429.27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:08:40</t>
+          <t>08:07:42</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="F84" t="n">
-        <v>7.58</v>
+        <v>6.91</v>
       </c>
       <c r="G84" t="n">
-        <v>250.9</v>
+        <v>252.1</v>
       </c>
       <c r="H84" t="n">
-        <v>83.7</v>
+        <v>85.2</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>193.45</v>
+        <v>-65.14</v>
       </c>
       <c r="K84" t="n">
-        <v>-217.31</v>
+        <v>54.1</v>
       </c>
       <c r="L84" t="n">
-        <v>290.94</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:09:58</t>
+          <t>08:08:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="F85" t="n">
-        <v>7.09</v>
+        <v>7.02</v>
       </c>
       <c r="G85" t="n">
-        <v>243.4</v>
+        <v>241.6</v>
       </c>
       <c r="H85" t="n">
-        <v>80.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-231.77</v>
+        <v>-115.89</v>
       </c>
       <c r="K85" t="n">
-        <v>-86.26000000000001</v>
+        <v>314.4</v>
       </c>
       <c r="L85" t="n">
-        <v>247.31</v>
+        <v>335.08</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:13:34</t>
+          <t>08:12:35</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="F86" t="n">
-        <v>6.98</v>
+        <v>7.33</v>
       </c>
       <c r="G86" t="n">
-        <v>232.3</v>
+        <v>250.6</v>
       </c>
       <c r="H86" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>11.78</v>
+        <v>182.34</v>
       </c>
       <c r="K86" t="n">
-        <v>239.56</v>
+        <v>-504.82</v>
       </c>
       <c r="L86" t="n">
-        <v>239.85</v>
+        <v>536.75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:14:25</t>
+          <t>08:14:29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="F87" t="n">
-        <v>7.13</v>
+        <v>7.33</v>
       </c>
       <c r="G87" t="n">
-        <v>243.1</v>
+        <v>242.8</v>
       </c>
       <c r="H87" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>230.75</v>
+        <v>-15.65</v>
       </c>
       <c r="K87" t="n">
-        <v>-227.3</v>
+        <v>-382.4</v>
       </c>
       <c r="L87" t="n">
-        <v>323.9</v>
+        <v>382.72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:15:24</t>
+          <t>08:15:55</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="F88" t="n">
-        <v>6.83</v>
+        <v>6.51</v>
       </c>
       <c r="G88" t="n">
-        <v>227.7</v>
+        <v>245.4</v>
       </c>
       <c r="H88" t="n">
-        <v>76.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>223.87</v>
+        <v>229.52</v>
       </c>
       <c r="K88" t="n">
-        <v>174.59</v>
+        <v>54.47</v>
       </c>
       <c r="L88" t="n">
-        <v>283.9</v>
+        <v>235.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-19.83</v>
+        <v>-22.31</v>
       </c>
       <c r="K14" t="n">
-        <v>62.25</v>
+        <v>70.02</v>
       </c>
       <c r="L14" t="n">
-        <v>65.33</v>
+        <v>73.48999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>99.98999999999999</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>132.16</v>
+        <v>106.31</v>
       </c>
       <c r="L15" t="n">
-        <v>165.72</v>
+        <v>133.31</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.48</v>
+        <v>-22.35</v>
       </c>
       <c r="K16" t="n">
-        <v>-66.3</v>
+        <v>-72.38</v>
       </c>
       <c r="L16" t="n">
-        <v>69.39</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-123.46</v>
+        <v>-97.23999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>180.24</v>
+        <v>141.96</v>
       </c>
       <c r="L17" t="n">
-        <v>218.46</v>
+        <v>172.07</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>18.14</v>
+        <v>18.11</v>
       </c>
       <c r="K18" t="n">
-        <v>-84.37</v>
+        <v>-84.22</v>
       </c>
       <c r="L18" t="n">
-        <v>86.3</v>
+        <v>86.15000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>9.92</v>
+        <v>8.52</v>
       </c>
       <c r="K19" t="n">
-        <v>178.58</v>
+        <v>153.25</v>
       </c>
       <c r="L19" t="n">
-        <v>178.86</v>
+        <v>153.49</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>21.66</v>
+        <v>26.4</v>
       </c>
       <c r="K20" t="n">
-        <v>-103.94</v>
+        <v>-126.7</v>
       </c>
       <c r="L20" t="n">
-        <v>106.18</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>168.83</v>
+        <v>149.44</v>
       </c>
       <c r="K21" t="n">
-        <v>427.98</v>
+        <v>378.83</v>
       </c>
       <c r="L21" t="n">
-        <v>460.08</v>
+        <v>407.24</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-13.9</v>
+        <v>-17.07</v>
       </c>
       <c r="K22" t="n">
-        <v>113.14</v>
+        <v>138.93</v>
       </c>
       <c r="L22" t="n">
-        <v>113.99</v>
+        <v>139.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-255.04</v>
+        <v>-263.77</v>
       </c>
       <c r="K23" t="n">
-        <v>-331.37</v>
+        <v>-342.72</v>
       </c>
       <c r="L23" t="n">
-        <v>418.16</v>
+        <v>432.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>84.62</v>
+        <v>151.06</v>
       </c>
       <c r="K24" t="n">
-        <v>-72.81</v>
+        <v>-129.97</v>
       </c>
       <c r="L24" t="n">
-        <v>111.63</v>
+        <v>199.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>87.58</v>
+        <v>103.69</v>
       </c>
       <c r="K25" t="n">
-        <v>-329.44</v>
+        <v>-390.04</v>
       </c>
       <c r="L25" t="n">
-        <v>340.88</v>
+        <v>403.59</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-233.32</v>
+        <v>-357.66</v>
       </c>
       <c r="K26" t="n">
-        <v>48.32</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>238.27</v>
+        <v>365.25</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>180.2</v>
+        <v>326.66</v>
       </c>
       <c r="K27" t="n">
-        <v>-44.74</v>
+        <v>-81.11</v>
       </c>
       <c r="L27" t="n">
-        <v>185.67</v>
+        <v>336.58</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-64.47</v>
+        <v>-117.88</v>
       </c>
       <c r="K28" t="n">
-        <v>-144.51</v>
+        <v>-264.2</v>
       </c>
       <c r="L28" t="n">
-        <v>158.24</v>
+        <v>289.31</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-40.11</v>
+        <v>-50.23</v>
       </c>
       <c r="K29" t="n">
-        <v>-42.91</v>
+        <v>-53.74</v>
       </c>
       <c r="L29" t="n">
-        <v>58.73</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>145.09</v>
+        <v>129.8</v>
       </c>
       <c r="K30" t="n">
-        <v>112.08</v>
+        <v>100.26</v>
       </c>
       <c r="L30" t="n">
-        <v>183.34</v>
+        <v>164.01</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-35.57</v>
+        <v>-41.92</v>
       </c>
       <c r="K31" t="n">
-        <v>64.02</v>
+        <v>75.45</v>
       </c>
       <c r="L31" t="n">
-        <v>73.23999999999999</v>
+        <v>86.31999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>19.21</v>
+        <v>31.96</v>
       </c>
       <c r="K32" t="n">
-        <v>-26.87</v>
+        <v>-44.69</v>
       </c>
       <c r="L32" t="n">
-        <v>33.03</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>145.59</v>
+        <v>135.99</v>
       </c>
       <c r="K33" t="n">
-        <v>37.74</v>
+        <v>35.25</v>
       </c>
       <c r="L33" t="n">
-        <v>150.4</v>
+        <v>140.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>40.89</v>
+        <v>53.49</v>
       </c>
       <c r="K34" t="n">
-        <v>-55.94</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>69.29000000000001</v>
+        <v>90.65000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>172.05</v>
+        <v>179.85</v>
       </c>
       <c r="K35" t="n">
-        <v>-91.84</v>
+        <v>-96</v>
       </c>
       <c r="L35" t="n">
-        <v>195.02</v>
+        <v>203.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>58.58</v>
+        <v>80.22</v>
       </c>
       <c r="K36" t="n">
-        <v>-112.01</v>
+        <v>-153.38</v>
       </c>
       <c r="L36" t="n">
-        <v>126.41</v>
+        <v>173.09</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>11.78</v>
+        <v>15.07</v>
       </c>
       <c r="K37" t="n">
-        <v>130.09</v>
+        <v>166.43</v>
       </c>
       <c r="L37" t="n">
-        <v>130.62</v>
+        <v>167.11</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>436.86</v>
+        <v>459.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-259.25</v>
+        <v>-272.94</v>
       </c>
       <c r="L38" t="n">
-        <v>507.99</v>
+        <v>534.8200000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>317.7</v>
+        <v>340.08</v>
       </c>
       <c r="K39" t="n">
-        <v>-177.03</v>
+        <v>-189.5</v>
       </c>
       <c r="L39" t="n">
-        <v>363.7</v>
+        <v>389.31</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-267.64</v>
+        <v>-296.43</v>
       </c>
       <c r="K40" t="n">
-        <v>246.55</v>
+        <v>273.08</v>
       </c>
       <c r="L40" t="n">
-        <v>363.89</v>
+        <v>403.04</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-83.41</v>
+        <v>-181.1</v>
       </c>
       <c r="K41" t="n">
-        <v>-85.8</v>
+        <v>-186.3</v>
       </c>
       <c r="L41" t="n">
-        <v>119.66</v>
+        <v>259.82</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-317.53</v>
+        <v>-354.41</v>
       </c>
       <c r="K42" t="n">
-        <v>511.72</v>
+        <v>571.14</v>
       </c>
       <c r="L42" t="n">
-        <v>602.23</v>
+        <v>672.17</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-293.37</v>
+        <v>-406.11</v>
       </c>
       <c r="K43" t="n">
-        <v>190.26</v>
+        <v>263.38</v>
       </c>
       <c r="L43" t="n">
-        <v>349.67</v>
+        <v>484.04</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-98.95999999999999</v>
+        <v>-93.59</v>
       </c>
       <c r="K44" t="n">
-        <v>-78.67</v>
+        <v>-74.41</v>
       </c>
       <c r="L44" t="n">
-        <v>126.41</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-58.22</v>
+        <v>-59.9</v>
       </c>
       <c r="K45" t="n">
-        <v>29.76</v>
+        <v>30.62</v>
       </c>
       <c r="L45" t="n">
-        <v>65.39</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>41.64</v>
+        <v>49.62</v>
       </c>
       <c r="K46" t="n">
-        <v>-24.85</v>
+        <v>-29.62</v>
       </c>
       <c r="L46" t="n">
-        <v>48.49</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-20.93</v>
+        <v>-19.35</v>
       </c>
       <c r="K47" t="n">
-        <v>-143.09</v>
+        <v>-132.28</v>
       </c>
       <c r="L47" t="n">
-        <v>144.61</v>
+        <v>133.68</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-74.65000000000001</v>
+        <v>-91.48999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-30.18</v>
+        <v>-36.99</v>
       </c>
       <c r="L48" t="n">
-        <v>80.52</v>
+        <v>98.69</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>13.22</v>
+        <v>18.28</v>
       </c>
       <c r="K49" t="n">
-        <v>-47.23</v>
+        <v>-65.34</v>
       </c>
       <c r="L49" t="n">
-        <v>49.04</v>
+        <v>67.84999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.8</v>
+        <v>-7.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-267.67</v>
+        <v>-281.1</v>
       </c>
       <c r="L50" t="n">
-        <v>267.76</v>
+        <v>281.19</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-267.01</v>
+        <v>-249.65</v>
       </c>
       <c r="K51" t="n">
-        <v>-99.14</v>
+        <v>-92.69</v>
       </c>
       <c r="L51" t="n">
-        <v>284.82</v>
+        <v>266.3</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-7.52</v>
+        <v>-8.16</v>
       </c>
       <c r="K52" t="n">
-        <v>144.97</v>
+        <v>157.39</v>
       </c>
       <c r="L52" t="n">
-        <v>145.17</v>
+        <v>157.6</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>25.54</v>
+        <v>83.37</v>
       </c>
       <c r="K53" t="n">
-        <v>33.12</v>
+        <v>108.1</v>
       </c>
       <c r="L53" t="n">
-        <v>41.82</v>
+        <v>136.51</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>169.93</v>
+        <v>240.92</v>
       </c>
       <c r="K54" t="n">
-        <v>-18.28</v>
+        <v>-25.91</v>
       </c>
       <c r="L54" t="n">
-        <v>170.91</v>
+        <v>242.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-63.97</v>
+        <v>-140.11</v>
       </c>
       <c r="K55" t="n">
-        <v>-51.2</v>
+        <v>-112.14</v>
       </c>
       <c r="L55" t="n">
-        <v>81.94</v>
+        <v>179.46</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-243.19</v>
+        <v>-387.35</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.08</v>
+        <v>-6.5</v>
       </c>
       <c r="L56" t="n">
-        <v>243.22</v>
+        <v>387.41</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>161.31</v>
+        <v>217.93</v>
       </c>
       <c r="K57" t="n">
-        <v>321.49</v>
+        <v>434.34</v>
       </c>
       <c r="L57" t="n">
-        <v>359.69</v>
+        <v>485.95</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-164.24</v>
+        <v>-175.36</v>
       </c>
       <c r="K58" t="n">
-        <v>-866.35</v>
+        <v>-925</v>
       </c>
       <c r="L58" t="n">
-        <v>881.78</v>
+        <v>941.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-78.47</v>
+        <v>-79.77</v>
       </c>
       <c r="K59" t="n">
-        <v>40.51</v>
+        <v>41.18</v>
       </c>
       <c r="L59" t="n">
-        <v>88.31</v>
+        <v>89.77</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>46.84</v>
+        <v>55.85</v>
       </c>
       <c r="K60" t="n">
-        <v>44.95</v>
+        <v>53.6</v>
       </c>
       <c r="L60" t="n">
-        <v>64.92</v>
+        <v>77.41</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>50.35</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>8.4</v>
+        <v>11.19</v>
       </c>
       <c r="L61" t="n">
-        <v>51.04</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>50.49</v>
+        <v>70.48</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.11</v>
+        <v>-5.74</v>
       </c>
       <c r="L62" t="n">
-        <v>50.65</v>
+        <v>70.70999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>56.49</v>
+        <v>57.51</v>
       </c>
       <c r="K63" t="n">
-        <v>72.7</v>
+        <v>74.02</v>
       </c>
       <c r="L63" t="n">
-        <v>92.06999999999999</v>
+        <v>93.73</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-16.06</v>
+        <v>-15.28</v>
       </c>
       <c r="K64" t="n">
-        <v>-115.05</v>
+        <v>-109.45</v>
       </c>
       <c r="L64" t="n">
-        <v>116.17</v>
+        <v>110.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-188.4</v>
+        <v>-203.09</v>
       </c>
       <c r="K65" t="n">
-        <v>39.8</v>
+        <v>42.91</v>
       </c>
       <c r="L65" t="n">
-        <v>192.56</v>
+        <v>207.58</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-311.56</v>
+        <v>-267.88</v>
       </c>
       <c r="K66" t="n">
-        <v>20.12</v>
+        <v>17.3</v>
       </c>
       <c r="L66" t="n">
-        <v>312.21</v>
+        <v>268.44</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-5.58</v>
+        <v>-6.73</v>
       </c>
       <c r="K67" t="n">
-        <v>-112.41</v>
+        <v>-135.57</v>
       </c>
       <c r="L67" t="n">
-        <v>112.55</v>
+        <v>135.74</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-106.89</v>
+        <v>-158.1</v>
       </c>
       <c r="K68" t="n">
-        <v>-104.59</v>
+        <v>-154.69</v>
       </c>
       <c r="L68" t="n">
-        <v>149.55</v>
+        <v>221.19</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>88.51000000000001</v>
+        <v>111.38</v>
       </c>
       <c r="K69" t="n">
-        <v>278.19</v>
+        <v>350.08</v>
       </c>
       <c r="L69" t="n">
-        <v>291.93</v>
+        <v>367.38</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-446.85</v>
+        <v>-474.06</v>
       </c>
       <c r="K70" t="n">
-        <v>-91.06999999999999</v>
+        <v>-96.62</v>
       </c>
       <c r="L70" t="n">
-        <v>456.03</v>
+        <v>483.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-197.84</v>
+        <v>-341.08</v>
       </c>
       <c r="K71" t="n">
-        <v>75.92</v>
+        <v>130.88</v>
       </c>
       <c r="L71" t="n">
-        <v>211.9</v>
+        <v>365.32</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-14.83</v>
+        <v>-15.85</v>
       </c>
       <c r="K72" t="n">
-        <v>698.88</v>
+        <v>747.11</v>
       </c>
       <c r="L72" t="n">
-        <v>699.04</v>
+        <v>747.28</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-75.72</v>
+        <v>-203.3</v>
       </c>
       <c r="K73" t="n">
-        <v>-13.37</v>
+        <v>-35.9</v>
       </c>
       <c r="L73" t="n">
-        <v>76.89</v>
+        <v>206.45</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>82.41</v>
+        <v>76.09</v>
       </c>
       <c r="K74" t="n">
-        <v>40.23</v>
+        <v>37.15</v>
       </c>
       <c r="L74" t="n">
-        <v>91.7</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.47</v>
+        <v>-5.14</v>
       </c>
       <c r="K75" t="n">
-        <v>129.06</v>
+        <v>121.35</v>
       </c>
       <c r="L75" t="n">
-        <v>129.17</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>30.88</v>
+        <v>50.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-18.77</v>
+        <v>-30.91</v>
       </c>
       <c r="L76" t="n">
-        <v>36.14</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>69.75</v>
+        <v>58.62</v>
       </c>
       <c r="K77" t="n">
-        <v>-150.43</v>
+        <v>-126.43</v>
       </c>
       <c r="L77" t="n">
-        <v>165.81</v>
+        <v>139.36</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>80.65000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="K78" t="n">
-        <v>-55.06</v>
+        <v>-62.26</v>
       </c>
       <c r="L78" t="n">
-        <v>97.65000000000001</v>
+        <v>110.42</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-118.01</v>
+        <v>-120.4</v>
       </c>
       <c r="K79" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="L79" t="n">
-        <v>118.07</v>
+        <v>120.46</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>230.71</v>
+        <v>224.06</v>
       </c>
       <c r="K80" t="n">
-        <v>143.28</v>
+        <v>139.15</v>
       </c>
       <c r="L80" t="n">
-        <v>271.58</v>
+        <v>263.75</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>61.62</v>
+        <v>88.5</v>
       </c>
       <c r="K81" t="n">
-        <v>-40.64</v>
+        <v>-58.37</v>
       </c>
       <c r="L81" t="n">
-        <v>73.81</v>
+        <v>106.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>258.49</v>
+        <v>239.55</v>
       </c>
       <c r="K82" t="n">
-        <v>302.97</v>
+        <v>280.77</v>
       </c>
       <c r="L82" t="n">
-        <v>398.25</v>
+        <v>369.07</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-57.88</v>
+        <v>-61.13</v>
       </c>
       <c r="K83" t="n">
-        <v>-425.35</v>
+        <v>-449.19</v>
       </c>
       <c r="L83" t="n">
-        <v>429.27</v>
+        <v>453.33</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-65.14</v>
+        <v>-138.94</v>
       </c>
       <c r="K84" t="n">
-        <v>54.1</v>
+        <v>115.39</v>
       </c>
       <c r="L84" t="n">
-        <v>84.68000000000001</v>
+        <v>180.61</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-115.89</v>
+        <v>-133.4</v>
       </c>
       <c r="K85" t="n">
-        <v>314.4</v>
+        <v>361.89</v>
       </c>
       <c r="L85" t="n">
-        <v>335.08</v>
+        <v>385.7</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>182.34</v>
+        <v>219.68</v>
       </c>
       <c r="K86" t="n">
-        <v>-504.82</v>
+        <v>-608.2</v>
       </c>
       <c r="L86" t="n">
-        <v>536.75</v>
+        <v>646.66</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-15.65</v>
+        <v>-20.9</v>
       </c>
       <c r="K87" t="n">
-        <v>-382.4</v>
+        <v>-510.46</v>
       </c>
       <c r="L87" t="n">
-        <v>382.72</v>
+        <v>510.88</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>229.52</v>
+        <v>329.91</v>
       </c>
       <c r="K88" t="n">
-        <v>54.47</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>235.9</v>
+        <v>339.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.31</v>
+        <v>-16.35</v>
       </c>
       <c r="K14" t="n">
-        <v>70.02</v>
+        <v>51.32</v>
       </c>
       <c r="L14" t="n">
-        <v>73.48999999999999</v>
+        <v>53.87</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>80.43000000000001</v>
+        <v>61.16</v>
       </c>
       <c r="K15" t="n">
-        <v>106.31</v>
+        <v>80.84</v>
       </c>
       <c r="L15" t="n">
-        <v>133.31</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.35</v>
+        <v>-16.14</v>
       </c>
       <c r="K16" t="n">
-        <v>-72.38</v>
+        <v>-52.25</v>
       </c>
       <c r="L16" t="n">
-        <v>75.75</v>
+        <v>54.69</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-97.23999999999999</v>
+        <v>-74.54000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>141.96</v>
+        <v>108.83</v>
       </c>
       <c r="L17" t="n">
-        <v>172.07</v>
+        <v>131.91</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>18.11</v>
+        <v>13.93</v>
       </c>
       <c r="K18" t="n">
-        <v>-84.22</v>
+        <v>-64.81</v>
       </c>
       <c r="L18" t="n">
-        <v>86.15000000000001</v>
+        <v>66.29000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>8.52</v>
+        <v>6.1</v>
       </c>
       <c r="K19" t="n">
-        <v>153.25</v>
+        <v>109.76</v>
       </c>
       <c r="L19" t="n">
-        <v>153.49</v>
+        <v>109.93</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>26.4</v>
+        <v>16.89</v>
       </c>
       <c r="K20" t="n">
-        <v>-126.7</v>
+        <v>-81.09</v>
       </c>
       <c r="L20" t="n">
-        <v>129.42</v>
+        <v>82.83</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>149.44</v>
+        <v>88.02</v>
       </c>
       <c r="K21" t="n">
-        <v>378.83</v>
+        <v>223.13</v>
       </c>
       <c r="L21" t="n">
-        <v>407.24</v>
+        <v>239.86</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-17.07</v>
+        <v>-11.16</v>
       </c>
       <c r="K22" t="n">
-        <v>138.93</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>139.97</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-263.77</v>
+        <v>-142.04</v>
       </c>
       <c r="K23" t="n">
-        <v>-342.72</v>
+        <v>-184.55</v>
       </c>
       <c r="L23" t="n">
-        <v>432.47</v>
+        <v>232.88</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>151.06</v>
+        <v>76.83</v>
       </c>
       <c r="K24" t="n">
-        <v>-129.97</v>
+        <v>-66.09999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>199.28</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>103.69</v>
+        <v>51.33</v>
       </c>
       <c r="K25" t="n">
-        <v>-390.04</v>
+        <v>-193.1</v>
       </c>
       <c r="L25" t="n">
-        <v>403.59</v>
+        <v>199.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-357.66</v>
+        <v>-172.48</v>
       </c>
       <c r="K26" t="n">
-        <v>74.06999999999999</v>
+        <v>35.72</v>
       </c>
       <c r="L26" t="n">
-        <v>365.25</v>
+        <v>176.14</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>326.66</v>
+        <v>147.62</v>
       </c>
       <c r="K27" t="n">
-        <v>-81.11</v>
+        <v>-36.65</v>
       </c>
       <c r="L27" t="n">
-        <v>336.58</v>
+        <v>152.11</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-117.88</v>
+        <v>-57.34</v>
       </c>
       <c r="K28" t="n">
-        <v>-264.2</v>
+        <v>-128.51</v>
       </c>
       <c r="L28" t="n">
-        <v>289.31</v>
+        <v>140.72</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-50.23</v>
+        <v>-33.74</v>
       </c>
       <c r="K29" t="n">
-        <v>-53.74</v>
+        <v>-36.1</v>
       </c>
       <c r="L29" t="n">
-        <v>73.56</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>129.8</v>
+        <v>86.22</v>
       </c>
       <c r="K30" t="n">
-        <v>100.26</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>164.01</v>
+        <v>108.95</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-41.92</v>
+        <v>-27.84</v>
       </c>
       <c r="K31" t="n">
-        <v>75.45</v>
+        <v>50.11</v>
       </c>
       <c r="L31" t="n">
-        <v>86.31999999999999</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>31.96</v>
+        <v>24.02</v>
       </c>
       <c r="K32" t="n">
-        <v>-44.69</v>
+        <v>-33.58</v>
       </c>
       <c r="L32" t="n">
-        <v>54.94</v>
+        <v>41.29</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>135.99</v>
+        <v>92.97</v>
       </c>
       <c r="K33" t="n">
-        <v>35.25</v>
+        <v>24.1</v>
       </c>
       <c r="L33" t="n">
-        <v>140.48</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>53.49</v>
+        <v>35.62</v>
       </c>
       <c r="K34" t="n">
-        <v>-73.18000000000001</v>
+        <v>-48.73</v>
       </c>
       <c r="L34" t="n">
-        <v>90.65000000000001</v>
+        <v>60.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>179.85</v>
+        <v>109.47</v>
       </c>
       <c r="K35" t="n">
-        <v>-96</v>
+        <v>-58.43</v>
       </c>
       <c r="L35" t="n">
-        <v>203.87</v>
+        <v>124.09</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>80.22</v>
+        <v>44.71</v>
       </c>
       <c r="K36" t="n">
-        <v>-153.38</v>
+        <v>-85.48</v>
       </c>
       <c r="L36" t="n">
-        <v>173.09</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>15.07</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>166.43</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>167.11</v>
+        <v>96.64</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>459.93</v>
+        <v>233.6</v>
       </c>
       <c r="K38" t="n">
-        <v>-272.94</v>
+        <v>-138.63</v>
       </c>
       <c r="L38" t="n">
-        <v>534.8200000000001</v>
+        <v>271.63</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>340.08</v>
+        <v>188</v>
       </c>
       <c r="K39" t="n">
-        <v>-189.5</v>
+        <v>-104.76</v>
       </c>
       <c r="L39" t="n">
-        <v>389.31</v>
+        <v>215.21</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-296.43</v>
+        <v>-154.6</v>
       </c>
       <c r="K40" t="n">
-        <v>273.08</v>
+        <v>142.43</v>
       </c>
       <c r="L40" t="n">
-        <v>403.04</v>
+        <v>210.21</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-181.1</v>
+        <v>-85.87</v>
       </c>
       <c r="K41" t="n">
-        <v>-186.3</v>
+        <v>-88.34</v>
       </c>
       <c r="L41" t="n">
-        <v>259.82</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-354.41</v>
+        <v>-171.2</v>
       </c>
       <c r="K42" t="n">
-        <v>571.14</v>
+        <v>275.9</v>
       </c>
       <c r="L42" t="n">
-        <v>672.17</v>
+        <v>324.7</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-406.11</v>
+        <v>-182.74</v>
       </c>
       <c r="K43" t="n">
-        <v>263.38</v>
+        <v>118.52</v>
       </c>
       <c r="L43" t="n">
-        <v>484.04</v>
+        <v>217.81</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-93.59</v>
+        <v>-64.03</v>
       </c>
       <c r="K44" t="n">
-        <v>-74.41</v>
+        <v>-50.9</v>
       </c>
       <c r="L44" t="n">
-        <v>119.57</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-59.9</v>
+        <v>-47.01</v>
       </c>
       <c r="K45" t="n">
-        <v>30.62</v>
+        <v>24.03</v>
       </c>
       <c r="L45" t="n">
-        <v>67.28</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>49.62</v>
+        <v>38.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-29.62</v>
+        <v>-23.11</v>
       </c>
       <c r="L46" t="n">
-        <v>57.79</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-19.35</v>
+        <v>-13.84</v>
       </c>
       <c r="K47" t="n">
-        <v>-132.28</v>
+        <v>-94.62</v>
       </c>
       <c r="L47" t="n">
-        <v>133.68</v>
+        <v>95.62</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-91.48999999999999</v>
+        <v>-60.99</v>
       </c>
       <c r="K48" t="n">
-        <v>-36.99</v>
+        <v>-24.66</v>
       </c>
       <c r="L48" t="n">
-        <v>98.69</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>18.28</v>
+        <v>13.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-65.34</v>
+        <v>-48.44</v>
       </c>
       <c r="L49" t="n">
-        <v>67.84999999999999</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.14</v>
+        <v>-4</v>
       </c>
       <c r="K50" t="n">
-        <v>-281.1</v>
+        <v>-157.37</v>
       </c>
       <c r="L50" t="n">
-        <v>281.19</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-249.65</v>
+        <v>-154.98</v>
       </c>
       <c r="K51" t="n">
-        <v>-92.69</v>
+        <v>-57.54</v>
       </c>
       <c r="L51" t="n">
-        <v>266.3</v>
+        <v>165.31</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-8.16</v>
+        <v>-5.28</v>
       </c>
       <c r="K52" t="n">
-        <v>157.39</v>
+        <v>101.88</v>
       </c>
       <c r="L52" t="n">
-        <v>157.6</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>83.37</v>
+        <v>43.5</v>
       </c>
       <c r="K53" t="n">
-        <v>108.1</v>
+        <v>56.4</v>
       </c>
       <c r="L53" t="n">
-        <v>136.51</v>
+        <v>71.23</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>240.92</v>
+        <v>125.82</v>
       </c>
       <c r="K54" t="n">
-        <v>-25.91</v>
+        <v>-13.53</v>
       </c>
       <c r="L54" t="n">
-        <v>242.31</v>
+        <v>126.55</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-140.11</v>
+        <v>-69.47</v>
       </c>
       <c r="K55" t="n">
-        <v>-112.14</v>
+        <v>-55.6</v>
       </c>
       <c r="L55" t="n">
-        <v>179.46</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-387.35</v>
+        <v>-176.91</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.5</v>
+        <v>-2.97</v>
       </c>
       <c r="L56" t="n">
-        <v>387.41</v>
+        <v>176.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>217.93</v>
+        <v>100.32</v>
       </c>
       <c r="K57" t="n">
-        <v>434.34</v>
+        <v>199.95</v>
       </c>
       <c r="L57" t="n">
-        <v>485.95</v>
+        <v>223.71</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-175.36</v>
+        <v>-78.23999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>-925</v>
+        <v>-412.74</v>
       </c>
       <c r="L58" t="n">
-        <v>941.48</v>
+        <v>420.09</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-79.77</v>
+        <v>-56.98</v>
       </c>
       <c r="K59" t="n">
-        <v>41.18</v>
+        <v>29.41</v>
       </c>
       <c r="L59" t="n">
-        <v>89.77</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>55.85</v>
+        <v>38.04</v>
       </c>
       <c r="K60" t="n">
-        <v>53.6</v>
+        <v>36.51</v>
       </c>
       <c r="L60" t="n">
-        <v>77.41</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>67.06999999999999</v>
+        <v>44.24</v>
       </c>
       <c r="K61" t="n">
-        <v>11.19</v>
+        <v>7.38</v>
       </c>
       <c r="L61" t="n">
-        <v>68</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>70.48</v>
+        <v>52.06</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.74</v>
+        <v>-4.24</v>
       </c>
       <c r="L62" t="n">
-        <v>70.70999999999999</v>
+        <v>52.24</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>57.51</v>
+        <v>43.23</v>
       </c>
       <c r="K63" t="n">
-        <v>74.02</v>
+        <v>55.63</v>
       </c>
       <c r="L63" t="n">
-        <v>93.73</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-15.28</v>
+        <v>-11.41</v>
       </c>
       <c r="K64" t="n">
-        <v>-109.45</v>
+        <v>-81.73</v>
       </c>
       <c r="L64" t="n">
-        <v>110.51</v>
+        <v>82.52</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-203.09</v>
+        <v>-121.83</v>
       </c>
       <c r="K65" t="n">
-        <v>42.91</v>
+        <v>25.74</v>
       </c>
       <c r="L65" t="n">
-        <v>207.58</v>
+        <v>124.52</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-267.88</v>
+        <v>-177.05</v>
       </c>
       <c r="K66" t="n">
-        <v>17.3</v>
+        <v>11.43</v>
       </c>
       <c r="L66" t="n">
-        <v>268.44</v>
+        <v>177.42</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-6.73</v>
+        <v>-4.37</v>
       </c>
       <c r="K67" t="n">
-        <v>-135.57</v>
+        <v>-88.13</v>
       </c>
       <c r="L67" t="n">
-        <v>135.74</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-158.1</v>
+        <v>-82.56</v>
       </c>
       <c r="K68" t="n">
-        <v>-154.69</v>
+        <v>-80.78</v>
       </c>
       <c r="L68" t="n">
-        <v>221.19</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>111.38</v>
+        <v>53.82</v>
       </c>
       <c r="K69" t="n">
-        <v>350.08</v>
+        <v>169.17</v>
       </c>
       <c r="L69" t="n">
-        <v>367.38</v>
+        <v>177.53</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-474.06</v>
+        <v>-228.76</v>
       </c>
       <c r="K70" t="n">
-        <v>-96.62</v>
+        <v>-46.62</v>
       </c>
       <c r="L70" t="n">
-        <v>483.81</v>
+        <v>233.46</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-341.08</v>
+        <v>-152.37</v>
       </c>
       <c r="K71" t="n">
-        <v>130.88</v>
+        <v>58.47</v>
       </c>
       <c r="L71" t="n">
-        <v>365.32</v>
+        <v>163.2</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-15.85</v>
+        <v>-7.69</v>
       </c>
       <c r="K72" t="n">
-        <v>747.11</v>
+        <v>362.22</v>
       </c>
       <c r="L72" t="n">
-        <v>747.28</v>
+        <v>362.3</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-203.3</v>
+        <v>-103.74</v>
       </c>
       <c r="K73" t="n">
-        <v>-35.9</v>
+        <v>-18.32</v>
       </c>
       <c r="L73" t="n">
-        <v>206.45</v>
+        <v>105.35</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>76.09</v>
+        <v>57.07</v>
       </c>
       <c r="K74" t="n">
-        <v>37.15</v>
+        <v>27.86</v>
       </c>
       <c r="L74" t="n">
-        <v>84.68000000000001</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.14</v>
+        <v>-3.4</v>
       </c>
       <c r="K75" t="n">
-        <v>121.35</v>
+        <v>80.16</v>
       </c>
       <c r="L75" t="n">
-        <v>121.45</v>
+        <v>80.23</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>50.83</v>
+        <v>33.85</v>
       </c>
       <c r="K76" t="n">
-        <v>-30.91</v>
+        <v>-20.58</v>
       </c>
       <c r="L76" t="n">
-        <v>59.49</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>58.62</v>
+        <v>44.14</v>
       </c>
       <c r="K77" t="n">
-        <v>-126.43</v>
+        <v>-95.19</v>
       </c>
       <c r="L77" t="n">
-        <v>139.36</v>
+        <v>104.92</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>91.2</v>
+        <v>61.37</v>
       </c>
       <c r="K78" t="n">
-        <v>-62.26</v>
+        <v>-41.9</v>
       </c>
       <c r="L78" t="n">
-        <v>110.42</v>
+        <v>74.31</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-120.4</v>
+        <v>-80.89</v>
       </c>
       <c r="K79" t="n">
-        <v>3.88</v>
+        <v>2.61</v>
       </c>
       <c r="L79" t="n">
-        <v>120.46</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>224.06</v>
+        <v>135.19</v>
       </c>
       <c r="K80" t="n">
-        <v>139.15</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>263.75</v>
+        <v>159.14</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>88.5</v>
+        <v>58.75</v>
       </c>
       <c r="K81" t="n">
-        <v>-58.37</v>
+        <v>-38.75</v>
       </c>
       <c r="L81" t="n">
-        <v>106.01</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>239.55</v>
+        <v>132.42</v>
       </c>
       <c r="K82" t="n">
-        <v>280.77</v>
+        <v>155.21</v>
       </c>
       <c r="L82" t="n">
-        <v>369.07</v>
+        <v>204.02</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-61.13</v>
+        <v>-31.87</v>
       </c>
       <c r="K83" t="n">
-        <v>-449.19</v>
+        <v>-234.2</v>
       </c>
       <c r="L83" t="n">
-        <v>453.33</v>
+        <v>236.36</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-138.94</v>
+        <v>-68.77</v>
       </c>
       <c r="K84" t="n">
-        <v>115.39</v>
+        <v>57.11</v>
       </c>
       <c r="L84" t="n">
-        <v>180.61</v>
+        <v>89.39</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-133.4</v>
+        <v>-67.86</v>
       </c>
       <c r="K85" t="n">
-        <v>361.89</v>
+        <v>184.1</v>
       </c>
       <c r="L85" t="n">
-        <v>385.7</v>
+        <v>196.2</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>219.68</v>
+        <v>100.7</v>
       </c>
       <c r="K86" t="n">
-        <v>-608.2</v>
+        <v>-278.79</v>
       </c>
       <c r="L86" t="n">
-        <v>646.66</v>
+        <v>296.42</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-20.9</v>
+        <v>-9.42</v>
       </c>
       <c r="K87" t="n">
-        <v>-510.46</v>
+        <v>-230.03</v>
       </c>
       <c r="L87" t="n">
-        <v>510.88</v>
+        <v>230.23</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>329.91</v>
+        <v>168.76</v>
       </c>
       <c r="K88" t="n">
-        <v>78.29000000000001</v>
+        <v>40.05</v>
       </c>
       <c r="L88" t="n">
-        <v>339.08</v>
+        <v>173.44</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.35</v>
+        <v>-16.67</v>
       </c>
       <c r="K14" t="n">
-        <v>51.32</v>
+        <v>52.32</v>
       </c>
       <c r="L14" t="n">
-        <v>53.87</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>61.16</v>
+        <v>61.09</v>
       </c>
       <c r="K15" t="n">
-        <v>80.84</v>
+        <v>80.75</v>
       </c>
       <c r="L15" t="n">
-        <v>101.37</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.14</v>
+        <v>-16.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-52.25</v>
+        <v>-52</v>
       </c>
       <c r="L16" t="n">
-        <v>54.69</v>
+        <v>54.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.54000000000001</v>
+        <v>-78.5</v>
       </c>
       <c r="K17" t="n">
-        <v>108.83</v>
+        <v>114.6</v>
       </c>
       <c r="L17" t="n">
-        <v>131.91</v>
+        <v>138.91</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>13.93</v>
+        <v>14.65</v>
       </c>
       <c r="K18" t="n">
-        <v>-64.81</v>
+        <v>-68.15000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>66.29000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>6.1</v>
+        <v>6.46</v>
       </c>
       <c r="K19" t="n">
-        <v>109.76</v>
+        <v>116.23</v>
       </c>
       <c r="L19" t="n">
-        <v>109.93</v>
+        <v>116.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>16.89</v>
+        <v>19.03</v>
       </c>
       <c r="K20" t="n">
-        <v>-81.09</v>
+        <v>-91.34999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>82.83</v>
+        <v>93.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>88.02</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>223.13</v>
+        <v>253.48</v>
       </c>
       <c r="L21" t="n">
-        <v>239.86</v>
+        <v>272.49</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-11.16</v>
+        <v>-12.5</v>
       </c>
       <c r="K22" t="n">
-        <v>90.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="L22" t="n">
-        <v>91.53</v>
+        <v>102.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-142.04</v>
+        <v>-165.46</v>
       </c>
       <c r="K23" t="n">
-        <v>-184.55</v>
+        <v>-214.99</v>
       </c>
       <c r="L23" t="n">
-        <v>232.88</v>
+        <v>271.29</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>76.83</v>
+        <v>90.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-66.09999999999999</v>
+        <v>-77.61</v>
       </c>
       <c r="L24" t="n">
-        <v>101.35</v>
+        <v>118.99</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>51.33</v>
+        <v>59.97</v>
       </c>
       <c r="K25" t="n">
-        <v>-193.1</v>
+        <v>-225.59</v>
       </c>
       <c r="L25" t="n">
-        <v>199.8</v>
+        <v>233.42</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-172.48</v>
+        <v>-203.75</v>
       </c>
       <c r="K26" t="n">
-        <v>35.72</v>
+        <v>42.2</v>
       </c>
       <c r="L26" t="n">
-        <v>176.14</v>
+        <v>208.07</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>147.62</v>
+        <v>177.85</v>
       </c>
       <c r="K27" t="n">
-        <v>-36.65</v>
+        <v>-44.16</v>
       </c>
       <c r="L27" t="n">
-        <v>152.11</v>
+        <v>183.25</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-57.34</v>
+        <v>-67.98</v>
       </c>
       <c r="K28" t="n">
-        <v>-128.51</v>
+        <v>-152.38</v>
       </c>
       <c r="L28" t="n">
-        <v>140.72</v>
+        <v>166.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.74</v>
+        <v>-33.95</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.1</v>
+        <v>-36.32</v>
       </c>
       <c r="L29" t="n">
-        <v>49.41</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>86.22</v>
+        <v>89.95</v>
       </c>
       <c r="K30" t="n">
-        <v>66.59999999999999</v>
+        <v>69.48</v>
       </c>
       <c r="L30" t="n">
-        <v>108.95</v>
+        <v>113.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-27.84</v>
+        <v>-28.96</v>
       </c>
       <c r="K31" t="n">
-        <v>50.11</v>
+        <v>52.13</v>
       </c>
       <c r="L31" t="n">
-        <v>57.33</v>
+        <v>59.63</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>24.02</v>
+        <v>25.2</v>
       </c>
       <c r="K32" t="n">
-        <v>-33.58</v>
+        <v>-35.24</v>
       </c>
       <c r="L32" t="n">
-        <v>41.29</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>92.97</v>
+        <v>99.23</v>
       </c>
       <c r="K33" t="n">
-        <v>24.1</v>
+        <v>25.72</v>
       </c>
       <c r="L33" t="n">
-        <v>96.05</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>35.62</v>
+        <v>38.14</v>
       </c>
       <c r="K34" t="n">
-        <v>-48.73</v>
+        <v>-52.18</v>
       </c>
       <c r="L34" t="n">
-        <v>60.36</v>
+        <v>64.63</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>109.47</v>
+        <v>123.41</v>
       </c>
       <c r="K35" t="n">
-        <v>-58.43</v>
+        <v>-65.87</v>
       </c>
       <c r="L35" t="n">
-        <v>124.09</v>
+        <v>139.89</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>44.71</v>
+        <v>51.15</v>
       </c>
       <c r="K36" t="n">
-        <v>-85.48</v>
+        <v>-97.79000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>96.47</v>
+        <v>110.36</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>8.720000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>96.23999999999999</v>
+        <v>109.09</v>
       </c>
       <c r="L37" t="n">
-        <v>96.64</v>
+        <v>109.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>233.6</v>
+        <v>273.25</v>
       </c>
       <c r="K38" t="n">
-        <v>-138.63</v>
+        <v>-162.16</v>
       </c>
       <c r="L38" t="n">
-        <v>271.63</v>
+        <v>317.74</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>188</v>
+        <v>220.79</v>
       </c>
       <c r="K39" t="n">
-        <v>-104.76</v>
+        <v>-123.02</v>
       </c>
       <c r="L39" t="n">
-        <v>215.21</v>
+        <v>252.75</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-154.6</v>
+        <v>-181.36</v>
       </c>
       <c r="K40" t="n">
-        <v>142.43</v>
+        <v>167.08</v>
       </c>
       <c r="L40" t="n">
-        <v>210.21</v>
+        <v>246.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-85.87</v>
+        <v>-102.05</v>
       </c>
       <c r="K41" t="n">
-        <v>-88.34</v>
+        <v>-104.98</v>
       </c>
       <c r="L41" t="n">
-        <v>123.2</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-171.2</v>
+        <v>-201.56</v>
       </c>
       <c r="K42" t="n">
-        <v>275.9</v>
+        <v>324.82</v>
       </c>
       <c r="L42" t="n">
-        <v>324.7</v>
+        <v>382.28</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-182.74</v>
+        <v>-217.81</v>
       </c>
       <c r="K43" t="n">
-        <v>118.52</v>
+        <v>141.26</v>
       </c>
       <c r="L43" t="n">
-        <v>217.81</v>
+        <v>259.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-64.03</v>
+        <v>-65.09999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.9</v>
+        <v>-51.75</v>
       </c>
       <c r="L44" t="n">
-        <v>81.8</v>
+        <v>83.16</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-47.01</v>
+        <v>-46.63</v>
       </c>
       <c r="K45" t="n">
-        <v>24.03</v>
+        <v>23.84</v>
       </c>
       <c r="L45" t="n">
-        <v>52.8</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>38.72</v>
+        <v>39.14</v>
       </c>
       <c r="K46" t="n">
-        <v>-23.11</v>
+        <v>-23.36</v>
       </c>
       <c r="L46" t="n">
-        <v>45.09</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-13.84</v>
+        <v>-14.75</v>
       </c>
       <c r="K47" t="n">
-        <v>-94.62</v>
+        <v>-100.88</v>
       </c>
       <c r="L47" t="n">
-        <v>95.62</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-60.99</v>
+        <v>-65.88</v>
       </c>
       <c r="K48" t="n">
-        <v>-24.66</v>
+        <v>-26.64</v>
       </c>
       <c r="L48" t="n">
-        <v>65.79000000000001</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>13.56</v>
+        <v>14.39</v>
       </c>
       <c r="K49" t="n">
-        <v>-48.44</v>
+        <v>-51.43</v>
       </c>
       <c r="L49" t="n">
-        <v>50.3</v>
+        <v>53.41</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-4</v>
+        <v>-4.55</v>
       </c>
       <c r="K50" t="n">
-        <v>-157.37</v>
+        <v>-179.31</v>
       </c>
       <c r="L50" t="n">
-        <v>157.42</v>
+        <v>179.37</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-154.98</v>
+        <v>-174.36</v>
       </c>
       <c r="K51" t="n">
-        <v>-57.54</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>165.31</v>
+        <v>185.99</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.28</v>
+        <v>-5.93</v>
       </c>
       <c r="K52" t="n">
-        <v>101.88</v>
+        <v>114.26</v>
       </c>
       <c r="L52" t="n">
-        <v>102.01</v>
+        <v>114.42</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>43.5</v>
+        <v>50.77</v>
       </c>
       <c r="K53" t="n">
-        <v>56.4</v>
+        <v>65.83</v>
       </c>
       <c r="L53" t="n">
-        <v>71.23</v>
+        <v>83.14</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>125.82</v>
+        <v>146.83</v>
       </c>
       <c r="K54" t="n">
-        <v>-13.53</v>
+        <v>-15.79</v>
       </c>
       <c r="L54" t="n">
-        <v>126.55</v>
+        <v>147.68</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-69.47</v>
+        <v>-82.02</v>
       </c>
       <c r="K55" t="n">
-        <v>-55.6</v>
+        <v>-65.65000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>88.98</v>
+        <v>105.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-176.91</v>
+        <v>-211.32</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.97</v>
+        <v>-3.55</v>
       </c>
       <c r="L56" t="n">
-        <v>176.93</v>
+        <v>211.35</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>100.32</v>
+        <v>120.51</v>
       </c>
       <c r="K57" t="n">
-        <v>199.95</v>
+        <v>240.18</v>
       </c>
       <c r="L57" t="n">
-        <v>223.71</v>
+        <v>268.72</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-78.23999999999999</v>
+        <v>-93.44</v>
       </c>
       <c r="K58" t="n">
-        <v>-412.74</v>
+        <v>-492.9</v>
       </c>
       <c r="L58" t="n">
-        <v>420.09</v>
+        <v>501.68</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-56.98</v>
+        <v>-58.44</v>
       </c>
       <c r="K59" t="n">
-        <v>29.41</v>
+        <v>30.17</v>
       </c>
       <c r="L59" t="n">
-        <v>64.12</v>
+        <v>65.77</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>38.04</v>
+        <v>38.75</v>
       </c>
       <c r="K60" t="n">
-        <v>36.51</v>
+        <v>37.19</v>
       </c>
       <c r="L60" t="n">
-        <v>52.73</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>44.24</v>
+        <v>46.46</v>
       </c>
       <c r="K61" t="n">
-        <v>7.38</v>
+        <v>7.76</v>
       </c>
       <c r="L61" t="n">
-        <v>44.85</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>52.06</v>
+        <v>55.19</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.24</v>
+        <v>-4.49</v>
       </c>
       <c r="L62" t="n">
-        <v>52.24</v>
+        <v>55.38</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>43.23</v>
+        <v>45.53</v>
       </c>
       <c r="K63" t="n">
-        <v>55.63</v>
+        <v>58.6</v>
       </c>
       <c r="L63" t="n">
-        <v>70.45</v>
+        <v>74.20999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.41</v>
+        <v>-12.11</v>
       </c>
       <c r="K64" t="n">
-        <v>-81.73</v>
+        <v>-86.75</v>
       </c>
       <c r="L64" t="n">
-        <v>82.52</v>
+        <v>87.59</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-121.83</v>
+        <v>-138.78</v>
       </c>
       <c r="K65" t="n">
-        <v>25.74</v>
+        <v>29.32</v>
       </c>
       <c r="L65" t="n">
-        <v>124.52</v>
+        <v>141.84</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-177.05</v>
+        <v>-197.72</v>
       </c>
       <c r="K66" t="n">
-        <v>11.43</v>
+        <v>12.77</v>
       </c>
       <c r="L66" t="n">
-        <v>177.42</v>
+        <v>198.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.37</v>
+        <v>-4.93</v>
       </c>
       <c r="K67" t="n">
-        <v>-88.13</v>
+        <v>-99.27</v>
       </c>
       <c r="L67" t="n">
-        <v>88.23</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-82.56</v>
+        <v>-96.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-80.78</v>
+        <v>-94.72</v>
       </c>
       <c r="L68" t="n">
-        <v>115.5</v>
+        <v>135.43</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>53.82</v>
+        <v>63.2</v>
       </c>
       <c r="K69" t="n">
-        <v>169.17</v>
+        <v>198.65</v>
       </c>
       <c r="L69" t="n">
-        <v>177.53</v>
+        <v>208.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-228.76</v>
+        <v>-271.07</v>
       </c>
       <c r="K70" t="n">
-        <v>-46.62</v>
+        <v>-55.25</v>
       </c>
       <c r="L70" t="n">
-        <v>233.46</v>
+        <v>276.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-152.37</v>
+        <v>-182.23</v>
       </c>
       <c r="K71" t="n">
-        <v>58.47</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>163.2</v>
+        <v>195.18</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-7.69</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>362.22</v>
+        <v>430.52</v>
       </c>
       <c r="L72" t="n">
-        <v>362.3</v>
+        <v>430.62</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-103.74</v>
+        <v>-121.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-18.32</v>
+        <v>-21.52</v>
       </c>
       <c r="L73" t="n">
-        <v>105.35</v>
+        <v>123.73</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>57.07</v>
+        <v>58.35</v>
       </c>
       <c r="K74" t="n">
-        <v>27.86</v>
+        <v>28.49</v>
       </c>
       <c r="L74" t="n">
-        <v>63.51</v>
+        <v>64.94</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.4</v>
+        <v>-3.56</v>
       </c>
       <c r="K75" t="n">
-        <v>80.16</v>
+        <v>84.09</v>
       </c>
       <c r="L75" t="n">
-        <v>80.23</v>
+        <v>84.17</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>33.85</v>
+        <v>35.06</v>
       </c>
       <c r="K76" t="n">
-        <v>-20.58</v>
+        <v>-21.32</v>
       </c>
       <c r="L76" t="n">
-        <v>39.62</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>44.14</v>
+        <v>46.8</v>
       </c>
       <c r="K77" t="n">
-        <v>-95.19</v>
+        <v>-100.93</v>
       </c>
       <c r="L77" t="n">
-        <v>104.92</v>
+        <v>111.25</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>61.37</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-41.9</v>
+        <v>-45.06</v>
       </c>
       <c r="L78" t="n">
-        <v>74.31</v>
+        <v>79.93000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-80.89</v>
+        <v>-86.34</v>
       </c>
       <c r="K79" t="n">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="L79" t="n">
-        <v>80.93000000000001</v>
+        <v>86.38</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>135.19</v>
+        <v>155.26</v>
       </c>
       <c r="K80" t="n">
-        <v>83.95999999999999</v>
+        <v>96.42</v>
       </c>
       <c r="L80" t="n">
-        <v>159.14</v>
+        <v>182.77</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>58.75</v>
+        <v>65.91</v>
       </c>
       <c r="K81" t="n">
-        <v>-38.75</v>
+        <v>-43.47</v>
       </c>
       <c r="L81" t="n">
-        <v>70.38</v>
+        <v>78.95999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>132.42</v>
+        <v>152.18</v>
       </c>
       <c r="K82" t="n">
-        <v>155.21</v>
+        <v>178.37</v>
       </c>
       <c r="L82" t="n">
-        <v>204.02</v>
+        <v>234.46</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-31.87</v>
+        <v>-37.21</v>
       </c>
       <c r="K83" t="n">
-        <v>-234.2</v>
+        <v>-273.48</v>
       </c>
       <c r="L83" t="n">
-        <v>236.36</v>
+        <v>276</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-68.77</v>
+        <v>-81.56</v>
       </c>
       <c r="K84" t="n">
-        <v>57.11</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="L84" t="n">
-        <v>89.39</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-67.86</v>
+        <v>-78.92</v>
       </c>
       <c r="K85" t="n">
-        <v>184.1</v>
+        <v>214.11</v>
       </c>
       <c r="L85" t="n">
-        <v>196.2</v>
+        <v>228.19</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>100.7</v>
+        <v>120.2</v>
       </c>
       <c r="K86" t="n">
-        <v>-278.79</v>
+        <v>-332.78</v>
       </c>
       <c r="L86" t="n">
-        <v>296.42</v>
+        <v>353.83</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-9.42</v>
+        <v>-11.34</v>
       </c>
       <c r="K87" t="n">
-        <v>-230.03</v>
+        <v>-277.12</v>
       </c>
       <c r="L87" t="n">
-        <v>230.23</v>
+        <v>277.35</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>168.76</v>
+        <v>198.61</v>
       </c>
       <c r="K88" t="n">
-        <v>40.05</v>
+        <v>47.13</v>
       </c>
       <c r="L88" t="n">
-        <v>173.44</v>
+        <v>204.13</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-16.67</v>
+        <v>-12.5</v>
       </c>
       <c r="K14" t="n">
-        <v>52.32</v>
+        <v>39.24</v>
       </c>
       <c r="L14" t="n">
-        <v>54.91</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>61.09</v>
+        <v>45.82</v>
       </c>
       <c r="K15" t="n">
-        <v>80.75</v>
+        <v>60.56</v>
       </c>
       <c r="L15" t="n">
-        <v>101.25</v>
+        <v>75.94</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.06</v>
+        <v>-12.04</v>
       </c>
       <c r="K16" t="n">
-        <v>-52</v>
+        <v>-39</v>
       </c>
       <c r="L16" t="n">
-        <v>54.42</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-78.5</v>
+        <v>-58.87</v>
       </c>
       <c r="K17" t="n">
-        <v>114.6</v>
+        <v>85.95</v>
       </c>
       <c r="L17" t="n">
-        <v>138.91</v>
+        <v>104.18</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>14.65</v>
+        <v>10.99</v>
       </c>
       <c r="K18" t="n">
-        <v>-68.15000000000001</v>
+        <v>-51.11</v>
       </c>
       <c r="L18" t="n">
-        <v>69.7</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>6.46</v>
+        <v>4.84</v>
       </c>
       <c r="K19" t="n">
-        <v>116.23</v>
+        <v>87.17</v>
       </c>
       <c r="L19" t="n">
-        <v>116.41</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>19.03</v>
+        <v>14.27</v>
       </c>
       <c r="K20" t="n">
-        <v>-91.34999999999999</v>
+        <v>-68.51000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>93.31</v>
+        <v>69.98</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>99.98999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>253.48</v>
+        <v>190.11</v>
       </c>
       <c r="L21" t="n">
-        <v>272.49</v>
+        <v>204.37</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-12.5</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>101.77</v>
+        <v>76.33</v>
       </c>
       <c r="L22" t="n">
-        <v>102.53</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-165.46</v>
+        <v>-124.1</v>
       </c>
       <c r="K23" t="n">
-        <v>-214.99</v>
+        <v>-161.24</v>
       </c>
       <c r="L23" t="n">
-        <v>271.29</v>
+        <v>203.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>90.2</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-77.61</v>
+        <v>-58.2</v>
       </c>
       <c r="L24" t="n">
-        <v>118.99</v>
+        <v>89.23999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>59.97</v>
+        <v>44.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-225.59</v>
+        <v>-169.19</v>
       </c>
       <c r="L25" t="n">
-        <v>233.42</v>
+        <v>175.07</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-203.75</v>
+        <v>-152.81</v>
       </c>
       <c r="K26" t="n">
-        <v>42.2</v>
+        <v>31.65</v>
       </c>
       <c r="L26" t="n">
-        <v>208.07</v>
+        <v>156.05</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>177.85</v>
+        <v>133.39</v>
       </c>
       <c r="K27" t="n">
-        <v>-44.16</v>
+        <v>-33.12</v>
       </c>
       <c r="L27" t="n">
-        <v>183.25</v>
+        <v>137.44</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-67.98</v>
+        <v>-50.99</v>
       </c>
       <c r="K28" t="n">
-        <v>-152.38</v>
+        <v>-114.28</v>
       </c>
       <c r="L28" t="n">
-        <v>166.86</v>
+        <v>125.14</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-33.95</v>
+        <v>-25.46</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.32</v>
+        <v>-27.24</v>
       </c>
       <c r="L29" t="n">
-        <v>49.72</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>89.95</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>69.48</v>
+        <v>52.11</v>
       </c>
       <c r="L30" t="n">
-        <v>113.66</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-28.96</v>
+        <v>-21.72</v>
       </c>
       <c r="K31" t="n">
-        <v>52.13</v>
+        <v>39.09</v>
       </c>
       <c r="L31" t="n">
-        <v>59.63</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>25.2</v>
+        <v>18.9</v>
       </c>
       <c r="K32" t="n">
-        <v>-35.24</v>
+        <v>-26.43</v>
       </c>
       <c r="L32" t="n">
-        <v>43.33</v>
+        <v>32.49</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>99.23</v>
+        <v>74.42</v>
       </c>
       <c r="K33" t="n">
-        <v>25.72</v>
+        <v>19.29</v>
       </c>
       <c r="L33" t="n">
-        <v>102.51</v>
+        <v>76.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>38.14</v>
+        <v>28.61</v>
       </c>
       <c r="K34" t="n">
-        <v>-52.18</v>
+        <v>-39.13</v>
       </c>
       <c r="L34" t="n">
-        <v>64.63</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>123.41</v>
+        <v>92.56</v>
       </c>
       <c r="K35" t="n">
-        <v>-65.87</v>
+        <v>-49.41</v>
       </c>
       <c r="L35" t="n">
-        <v>139.89</v>
+        <v>104.92</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>51.15</v>
+        <v>38.36</v>
       </c>
       <c r="K36" t="n">
-        <v>-97.79000000000001</v>
+        <v>-73.34</v>
       </c>
       <c r="L36" t="n">
-        <v>110.36</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>9.880000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="K37" t="n">
-        <v>109.09</v>
+        <v>81.81</v>
       </c>
       <c r="L37" t="n">
-        <v>109.53</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>273.25</v>
+        <v>204.94</v>
       </c>
       <c r="K38" t="n">
-        <v>-162.16</v>
+        <v>-121.62</v>
       </c>
       <c r="L38" t="n">
-        <v>317.74</v>
+        <v>238.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>220.79</v>
+        <v>165.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-123.02</v>
+        <v>-92.27</v>
       </c>
       <c r="L39" t="n">
-        <v>252.75</v>
+        <v>189.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-181.36</v>
+        <v>-136.02</v>
       </c>
       <c r="K40" t="n">
-        <v>167.08</v>
+        <v>125.31</v>
       </c>
       <c r="L40" t="n">
-        <v>246.59</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-102.05</v>
+        <v>-76.54000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-104.98</v>
+        <v>-78.73999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>146.41</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-201.56</v>
+        <v>-151.17</v>
       </c>
       <c r="K42" t="n">
-        <v>324.82</v>
+        <v>243.62</v>
       </c>
       <c r="L42" t="n">
-        <v>382.28</v>
+        <v>286.71</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-217.81</v>
+        <v>-163.36</v>
       </c>
       <c r="K43" t="n">
-        <v>141.26</v>
+        <v>105.94</v>
       </c>
       <c r="L43" t="n">
-        <v>259.61</v>
+        <v>194.71</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-65.09999999999999</v>
+        <v>-48.82</v>
       </c>
       <c r="K44" t="n">
-        <v>-51.75</v>
+        <v>-38.81</v>
       </c>
       <c r="L44" t="n">
-        <v>83.16</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-46.63</v>
+        <v>-34.97</v>
       </c>
       <c r="K45" t="n">
-        <v>23.84</v>
+        <v>17.88</v>
       </c>
       <c r="L45" t="n">
-        <v>52.37</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>39.14</v>
+        <v>29.36</v>
       </c>
       <c r="K46" t="n">
-        <v>-23.36</v>
+        <v>-17.52</v>
       </c>
       <c r="L46" t="n">
-        <v>45.59</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-14.75</v>
+        <v>-11.07</v>
       </c>
       <c r="K47" t="n">
-        <v>-100.88</v>
+        <v>-75.66</v>
       </c>
       <c r="L47" t="n">
-        <v>101.95</v>
+        <v>76.45999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-65.88</v>
+        <v>-49.41</v>
       </c>
       <c r="K48" t="n">
-        <v>-26.64</v>
+        <v>-19.98</v>
       </c>
       <c r="L48" t="n">
-        <v>71.06</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>14.39</v>
+        <v>10.79</v>
       </c>
       <c r="K49" t="n">
-        <v>-51.43</v>
+        <v>-38.57</v>
       </c>
       <c r="L49" t="n">
-        <v>53.41</v>
+        <v>40.06</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.55</v>
+        <v>-3.41</v>
       </c>
       <c r="K50" t="n">
-        <v>-179.31</v>
+        <v>-134.49</v>
       </c>
       <c r="L50" t="n">
-        <v>179.37</v>
+        <v>134.53</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-174.36</v>
+        <v>-130.77</v>
       </c>
       <c r="K51" t="n">
-        <v>-64.73999999999999</v>
+        <v>-48.56</v>
       </c>
       <c r="L51" t="n">
-        <v>185.99</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.93</v>
+        <v>-4.44</v>
       </c>
       <c r="K52" t="n">
-        <v>114.26</v>
+        <v>85.7</v>
       </c>
       <c r="L52" t="n">
-        <v>114.42</v>
+        <v>85.81</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>50.77</v>
+        <v>10.3</v>
       </c>
       <c r="K53" t="n">
-        <v>65.83</v>
+        <v>13.36</v>
       </c>
       <c r="L53" t="n">
-        <v>83.14</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>146.83</v>
+        <v>110.12</v>
       </c>
       <c r="K54" t="n">
-        <v>-15.79</v>
+        <v>-11.85</v>
       </c>
       <c r="L54" t="n">
-        <v>147.68</v>
+        <v>110.76</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-82.02</v>
+        <v>-61.52</v>
       </c>
       <c r="K55" t="n">
-        <v>-65.65000000000001</v>
+        <v>-49.24</v>
       </c>
       <c r="L55" t="n">
-        <v>105.06</v>
+        <v>78.79000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-211.32</v>
+        <v>-158.49</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.55</v>
+        <v>-2.66</v>
       </c>
       <c r="L56" t="n">
-        <v>211.35</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>120.51</v>
+        <v>90.38</v>
       </c>
       <c r="K57" t="n">
-        <v>240.18</v>
+        <v>180.14</v>
       </c>
       <c r="L57" t="n">
-        <v>268.72</v>
+        <v>201.54</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-93.44</v>
+        <v>-68.23999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>-492.9</v>
+        <v>-359.97</v>
       </c>
       <c r="L58" t="n">
-        <v>501.68</v>
+        <v>366.38</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-58.44</v>
+        <v>-43.83</v>
       </c>
       <c r="K59" t="n">
-        <v>30.17</v>
+        <v>22.63</v>
       </c>
       <c r="L59" t="n">
-        <v>65.77</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>38.75</v>
+        <v>29.07</v>
       </c>
       <c r="K60" t="n">
-        <v>37.19</v>
+        <v>27.89</v>
       </c>
       <c r="L60" t="n">
-        <v>53.71</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>46.46</v>
+        <v>34.85</v>
       </c>
       <c r="K61" t="n">
-        <v>7.76</v>
+        <v>5.82</v>
       </c>
       <c r="L61" t="n">
-        <v>47.11</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>55.19</v>
+        <v>41.39</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.49</v>
+        <v>-3.37</v>
       </c>
       <c r="L62" t="n">
-        <v>55.38</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>45.53</v>
+        <v>34.15</v>
       </c>
       <c r="K63" t="n">
-        <v>58.6</v>
+        <v>43.95</v>
       </c>
       <c r="L63" t="n">
-        <v>74.20999999999999</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-12.11</v>
+        <v>-9.08</v>
       </c>
       <c r="K64" t="n">
-        <v>-86.75</v>
+        <v>-65.06</v>
       </c>
       <c r="L64" t="n">
-        <v>87.59</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-138.78</v>
+        <v>-104.09</v>
       </c>
       <c r="K65" t="n">
-        <v>29.32</v>
+        <v>21.99</v>
       </c>
       <c r="L65" t="n">
-        <v>141.84</v>
+        <v>106.38</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-197.72</v>
+        <v>-148.29</v>
       </c>
       <c r="K66" t="n">
-        <v>12.77</v>
+        <v>9.58</v>
       </c>
       <c r="L66" t="n">
-        <v>198.14</v>
+        <v>148.6</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.93</v>
+        <v>-3.69</v>
       </c>
       <c r="K67" t="n">
-        <v>-99.27</v>
+        <v>-74.45</v>
       </c>
       <c r="L67" t="n">
-        <v>99.39</v>
+        <v>74.54000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-96.81</v>
+        <v>-72.59999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-94.72</v>
+        <v>-71.04000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>135.43</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>63.2</v>
+        <v>47.4</v>
       </c>
       <c r="K69" t="n">
-        <v>198.65</v>
+        <v>148.99</v>
       </c>
       <c r="L69" t="n">
-        <v>208.46</v>
+        <v>156.34</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-271.07</v>
+        <v>-203.3</v>
       </c>
       <c r="K70" t="n">
-        <v>-55.25</v>
+        <v>-41.43</v>
       </c>
       <c r="L70" t="n">
-        <v>276.64</v>
+        <v>207.48</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-182.23</v>
+        <v>-136.67</v>
       </c>
       <c r="K71" t="n">
-        <v>69.93000000000001</v>
+        <v>52.44</v>
       </c>
       <c r="L71" t="n">
-        <v>195.18</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-9.140000000000001</v>
+        <v>-6.85</v>
       </c>
       <c r="K72" t="n">
-        <v>430.52</v>
+        <v>322.89</v>
       </c>
       <c r="L72" t="n">
-        <v>430.62</v>
+        <v>322.96</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-121.85</v>
+        <v>-50.14</v>
       </c>
       <c r="K73" t="n">
-        <v>-21.52</v>
+        <v>-8.85</v>
       </c>
       <c r="L73" t="n">
-        <v>123.73</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>58.35</v>
+        <v>43.77</v>
       </c>
       <c r="K74" t="n">
-        <v>28.49</v>
+        <v>21.36</v>
       </c>
       <c r="L74" t="n">
-        <v>64.94</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.56</v>
+        <v>-2.67</v>
       </c>
       <c r="K75" t="n">
-        <v>84.09</v>
+        <v>63.07</v>
       </c>
       <c r="L75" t="n">
-        <v>84.17</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>35.06</v>
+        <v>26.3</v>
       </c>
       <c r="K76" t="n">
-        <v>-21.32</v>
+        <v>-15.99</v>
       </c>
       <c r="L76" t="n">
-        <v>41.04</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>46.8</v>
+        <v>35.1</v>
       </c>
       <c r="K77" t="n">
-        <v>-100.93</v>
+        <v>-75.7</v>
       </c>
       <c r="L77" t="n">
-        <v>111.25</v>
+        <v>83.44</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>66.01000000000001</v>
+        <v>49.51</v>
       </c>
       <c r="K78" t="n">
-        <v>-45.06</v>
+        <v>-33.8</v>
       </c>
       <c r="L78" t="n">
-        <v>79.93000000000001</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-86.34</v>
+        <v>-64.75</v>
       </c>
       <c r="K79" t="n">
-        <v>2.78</v>
+        <v>2.09</v>
       </c>
       <c r="L79" t="n">
-        <v>86.38</v>
+        <v>64.79000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>155.26</v>
+        <v>116.45</v>
       </c>
       <c r="K80" t="n">
-        <v>96.42</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>182.77</v>
+        <v>137.07</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>65.91</v>
+        <v>49.43</v>
       </c>
       <c r="K81" t="n">
-        <v>-43.47</v>
+        <v>-32.6</v>
       </c>
       <c r="L81" t="n">
-        <v>78.95999999999999</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>152.18</v>
+        <v>114.13</v>
       </c>
       <c r="K82" t="n">
-        <v>178.37</v>
+        <v>133.77</v>
       </c>
       <c r="L82" t="n">
-        <v>234.46</v>
+        <v>175.85</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-37.21</v>
+        <v>-27.91</v>
       </c>
       <c r="K83" t="n">
-        <v>-273.48</v>
+        <v>-205.11</v>
       </c>
       <c r="L83" t="n">
-        <v>276</v>
+        <v>207</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-81.56</v>
+        <v>-61.17</v>
       </c>
       <c r="K84" t="n">
-        <v>67.73999999999999</v>
+        <v>50.8</v>
       </c>
       <c r="L84" t="n">
-        <v>106.02</v>
+        <v>79.51000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-78.92</v>
+        <v>-59.19</v>
       </c>
       <c r="K85" t="n">
-        <v>214.11</v>
+        <v>160.58</v>
       </c>
       <c r="L85" t="n">
-        <v>228.19</v>
+        <v>171.14</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>120.2</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>-332.78</v>
+        <v>-249.59</v>
       </c>
       <c r="L86" t="n">
-        <v>353.83</v>
+        <v>265.37</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-11.34</v>
+        <v>-8.51</v>
       </c>
       <c r="K87" t="n">
-        <v>-277.12</v>
+        <v>-207.84</v>
       </c>
       <c r="L87" t="n">
-        <v>277.35</v>
+        <v>208.01</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>198.61</v>
+        <v>148.96</v>
       </c>
       <c r="K88" t="n">
-        <v>47.13</v>
+        <v>35.35</v>
       </c>
       <c r="L88" t="n">
-        <v>204.13</v>
+        <v>153.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.5</v>
+        <v>-12.78</v>
       </c>
       <c r="K14" t="n">
-        <v>39.24</v>
+        <v>40.12</v>
       </c>
       <c r="L14" t="n">
-        <v>41.18</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>45.82</v>
+        <v>43.58</v>
       </c>
       <c r="K15" t="n">
-        <v>60.56</v>
+        <v>57.6</v>
       </c>
       <c r="L15" t="n">
-        <v>75.94</v>
+        <v>72.23</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.04</v>
+        <v>-12.25</v>
       </c>
       <c r="K16" t="n">
-        <v>-39</v>
+        <v>-39.65</v>
       </c>
       <c r="L16" t="n">
-        <v>40.82</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-58.87</v>
+        <v>-56.22</v>
       </c>
       <c r="K17" t="n">
-        <v>85.95</v>
+        <v>82.08</v>
       </c>
       <c r="L17" t="n">
-        <v>104.18</v>
+        <v>99.48999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>10.99</v>
+        <v>11.21</v>
       </c>
       <c r="K18" t="n">
-        <v>-51.11</v>
+        <v>-52.13</v>
       </c>
       <c r="L18" t="n">
-        <v>52.28</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>4.84</v>
+        <v>4.7</v>
       </c>
       <c r="K19" t="n">
-        <v>87.17</v>
+        <v>84.55</v>
       </c>
       <c r="L19" t="n">
-        <v>87.31</v>
+        <v>84.68000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>14.27</v>
+        <v>14.77</v>
       </c>
       <c r="K20" t="n">
-        <v>-68.51000000000001</v>
+        <v>-70.91</v>
       </c>
       <c r="L20" t="n">
-        <v>69.98</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>74.98999999999999</v>
+        <v>70.38</v>
       </c>
       <c r="K21" t="n">
-        <v>190.11</v>
+        <v>178.42</v>
       </c>
       <c r="L21" t="n">
-        <v>204.37</v>
+        <v>191.8</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-9.380000000000001</v>
+        <v>-9.67</v>
       </c>
       <c r="K22" t="n">
-        <v>76.33</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>76.90000000000001</v>
+        <v>79.34999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-124.1</v>
+        <v>-118.38</v>
       </c>
       <c r="K23" t="n">
-        <v>-161.24</v>
+        <v>-153.82</v>
       </c>
       <c r="L23" t="n">
-        <v>203.47</v>
+        <v>194.1</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>67.65000000000001</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-58.2</v>
+        <v>-61.79</v>
       </c>
       <c r="L24" t="n">
-        <v>89.23999999999999</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>44.98</v>
+        <v>43.77</v>
       </c>
       <c r="K25" t="n">
-        <v>-169.19</v>
+        <v>-164.66</v>
       </c>
       <c r="L25" t="n">
-        <v>175.07</v>
+        <v>170.38</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-152.81</v>
+        <v>-158.18</v>
       </c>
       <c r="K26" t="n">
-        <v>31.65</v>
+        <v>32.76</v>
       </c>
       <c r="L26" t="n">
-        <v>156.05</v>
+        <v>161.53</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>133.39</v>
+        <v>141.04</v>
       </c>
       <c r="K27" t="n">
-        <v>-33.12</v>
+        <v>-35.02</v>
       </c>
       <c r="L27" t="n">
-        <v>137.44</v>
+        <v>145.32</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-50.99</v>
+        <v>-54.38</v>
       </c>
       <c r="K28" t="n">
-        <v>-114.28</v>
+        <v>-121.88</v>
       </c>
       <c r="L28" t="n">
-        <v>125.14</v>
+        <v>133.46</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.46</v>
+        <v>-26.31</v>
       </c>
       <c r="K29" t="n">
-        <v>-27.24</v>
+        <v>-28.14</v>
       </c>
       <c r="L29" t="n">
-        <v>37.29</v>
+        <v>38.52</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>67.45999999999999</v>
+        <v>64.13</v>
       </c>
       <c r="K30" t="n">
-        <v>52.11</v>
+        <v>49.54</v>
       </c>
       <c r="L30" t="n">
-        <v>85.25</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.72</v>
+        <v>-22.09</v>
       </c>
       <c r="K31" t="n">
-        <v>39.09</v>
+        <v>39.75</v>
       </c>
       <c r="L31" t="n">
-        <v>44.72</v>
+        <v>45.48</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>18.9</v>
+        <v>19.99</v>
       </c>
       <c r="K32" t="n">
-        <v>-26.43</v>
+        <v>-27.95</v>
       </c>
       <c r="L32" t="n">
-        <v>32.49</v>
+        <v>34.36</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>74.42</v>
+        <v>73.08</v>
       </c>
       <c r="K33" t="n">
-        <v>19.29</v>
+        <v>18.94</v>
       </c>
       <c r="L33" t="n">
-        <v>76.88</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>28.61</v>
+        <v>29.98</v>
       </c>
       <c r="K34" t="n">
-        <v>-39.13</v>
+        <v>-41.01</v>
       </c>
       <c r="L34" t="n">
-        <v>48.48</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>92.56</v>
+        <v>91.45</v>
       </c>
       <c r="K35" t="n">
-        <v>-49.41</v>
+        <v>-48.81</v>
       </c>
       <c r="L35" t="n">
-        <v>104.92</v>
+        <v>103.66</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>38.36</v>
+        <v>39.63</v>
       </c>
       <c r="K36" t="n">
-        <v>-73.34</v>
+        <v>-75.78</v>
       </c>
       <c r="L36" t="n">
-        <v>82.77</v>
+        <v>85.52</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>7.41</v>
+        <v>7.59</v>
       </c>
       <c r="K37" t="n">
-        <v>81.81</v>
+        <v>83.8</v>
       </c>
       <c r="L37" t="n">
-        <v>82.15000000000001</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>204.94</v>
+        <v>193.59</v>
       </c>
       <c r="K38" t="n">
-        <v>-121.62</v>
+        <v>-114.88</v>
       </c>
       <c r="L38" t="n">
-        <v>238.31</v>
+        <v>225.11</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>165.59</v>
+        <v>134.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-92.27</v>
+        <v>-74.98999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>189.56</v>
+        <v>154.07</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-136.02</v>
+        <v>-131.03</v>
       </c>
       <c r="K40" t="n">
-        <v>125.31</v>
+        <v>120.71</v>
       </c>
       <c r="L40" t="n">
-        <v>184.94</v>
+        <v>178.15</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-76.54000000000001</v>
+        <v>-83.31</v>
       </c>
       <c r="K41" t="n">
-        <v>-78.73999999999999</v>
+        <v>-85.7</v>
       </c>
       <c r="L41" t="n">
-        <v>109.8</v>
+        <v>119.52</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-151.17</v>
+        <v>-145.06</v>
       </c>
       <c r="K42" t="n">
-        <v>243.62</v>
+        <v>233.76</v>
       </c>
       <c r="L42" t="n">
-        <v>286.71</v>
+        <v>275.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-163.36</v>
+        <v>-163.66</v>
       </c>
       <c r="K43" t="n">
-        <v>105.94</v>
+        <v>106.14</v>
       </c>
       <c r="L43" t="n">
-        <v>194.71</v>
+        <v>195.06</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.82</v>
+        <v>-47.56</v>
       </c>
       <c r="K44" t="n">
-        <v>-38.81</v>
+        <v>-37.81</v>
       </c>
       <c r="L44" t="n">
-        <v>62.37</v>
+        <v>60.76</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.97</v>
+        <v>-35.53</v>
       </c>
       <c r="K45" t="n">
-        <v>17.88</v>
+        <v>18.16</v>
       </c>
       <c r="L45" t="n">
-        <v>39.28</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>29.36</v>
+        <v>30.61</v>
       </c>
       <c r="K46" t="n">
-        <v>-17.52</v>
+        <v>-18.27</v>
       </c>
       <c r="L46" t="n">
-        <v>34.19</v>
+        <v>35.65</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-11.07</v>
+        <v>-10.97</v>
       </c>
       <c r="K47" t="n">
-        <v>-75.66</v>
+        <v>-74.98</v>
       </c>
       <c r="L47" t="n">
-        <v>76.45999999999999</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-49.41</v>
+        <v>-51.27</v>
       </c>
       <c r="K48" t="n">
-        <v>-19.98</v>
+        <v>-20.73</v>
       </c>
       <c r="L48" t="n">
-        <v>53.3</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>10.79</v>
+        <v>11.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-38.57</v>
+        <v>-41.35</v>
       </c>
       <c r="L49" t="n">
-        <v>40.06</v>
+        <v>42.93</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.41</v>
+        <v>-3.33</v>
       </c>
       <c r="K50" t="n">
-        <v>-134.49</v>
+        <v>-130.99</v>
       </c>
       <c r="L50" t="n">
-        <v>134.53</v>
+        <v>131.03</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-130.77</v>
+        <v>-125.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-48.56</v>
+        <v>-46.77</v>
       </c>
       <c r="L51" t="n">
-        <v>139.5</v>
+        <v>134.38</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.44</v>
+        <v>-4.49</v>
       </c>
       <c r="K52" t="n">
-        <v>85.7</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>85.81</v>
+        <v>86.61</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>10.3</v>
+        <v>10.13</v>
       </c>
       <c r="K53" t="n">
-        <v>13.36</v>
+        <v>13.14</v>
       </c>
       <c r="L53" t="n">
-        <v>16.87</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>110.12</v>
+        <v>112.61</v>
       </c>
       <c r="K54" t="n">
-        <v>-11.85</v>
+        <v>-12.11</v>
       </c>
       <c r="L54" t="n">
-        <v>110.76</v>
+        <v>113.26</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-61.52</v>
+        <v>-67.02</v>
       </c>
       <c r="K55" t="n">
-        <v>-49.24</v>
+        <v>-53.64</v>
       </c>
       <c r="L55" t="n">
-        <v>78.79000000000001</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-158.49</v>
+        <v>-164.87</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.66</v>
+        <v>-2.77</v>
       </c>
       <c r="L56" t="n">
-        <v>158.51</v>
+        <v>164.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>90.38</v>
+        <v>90.47</v>
       </c>
       <c r="K57" t="n">
-        <v>180.14</v>
+        <v>180.32</v>
       </c>
       <c r="L57" t="n">
-        <v>201.54</v>
+        <v>201.74</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-68.23999999999999</v>
+        <v>-64.91</v>
       </c>
       <c r="K58" t="n">
-        <v>-359.97</v>
+        <v>-342.38</v>
       </c>
       <c r="L58" t="n">
-        <v>366.38</v>
+        <v>348.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.83</v>
+        <v>-43.56</v>
       </c>
       <c r="K59" t="n">
-        <v>22.63</v>
+        <v>22.48</v>
       </c>
       <c r="L59" t="n">
-        <v>49.33</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>29.07</v>
+        <v>29.7</v>
       </c>
       <c r="K60" t="n">
-        <v>27.89</v>
+        <v>28.5</v>
       </c>
       <c r="L60" t="n">
-        <v>40.28</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>34.85</v>
+        <v>36.78</v>
       </c>
       <c r="K61" t="n">
-        <v>5.82</v>
+        <v>6.14</v>
       </c>
       <c r="L61" t="n">
-        <v>35.33</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>41.39</v>
+        <v>44.28</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.37</v>
+        <v>-3.6</v>
       </c>
       <c r="L62" t="n">
-        <v>41.53</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>34.15</v>
+        <v>34.58</v>
       </c>
       <c r="K63" t="n">
-        <v>43.95</v>
+        <v>44.5</v>
       </c>
       <c r="L63" t="n">
-        <v>55.66</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-9.08</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-65.06</v>
+        <v>-64.73999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>65.69</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-104.09</v>
+        <v>-103.02</v>
       </c>
       <c r="K65" t="n">
-        <v>21.99</v>
+        <v>21.77</v>
       </c>
       <c r="L65" t="n">
-        <v>106.38</v>
+        <v>105.29</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-148.29</v>
+        <v>-140.9</v>
       </c>
       <c r="K66" t="n">
-        <v>9.58</v>
+        <v>9.1</v>
       </c>
       <c r="L66" t="n">
-        <v>148.6</v>
+        <v>141.19</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.69</v>
+        <v>-3.81</v>
       </c>
       <c r="K67" t="n">
-        <v>-74.45</v>
+        <v>-76.81999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>74.54000000000001</v>
+        <v>76.91</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-72.59999999999999</v>
+        <v>-74.66</v>
       </c>
       <c r="K68" t="n">
-        <v>-71.04000000000001</v>
+        <v>-73.05</v>
       </c>
       <c r="L68" t="n">
-        <v>101.58</v>
+        <v>104.45</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>47.4</v>
+        <v>46.49</v>
       </c>
       <c r="K69" t="n">
-        <v>148.99</v>
+        <v>146.12</v>
       </c>
       <c r="L69" t="n">
-        <v>156.34</v>
+        <v>153.34</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-203.3</v>
+        <v>-194.53</v>
       </c>
       <c r="K70" t="n">
-        <v>-41.43</v>
+        <v>-39.65</v>
       </c>
       <c r="L70" t="n">
-        <v>207.48</v>
+        <v>198.53</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-136.67</v>
+        <v>-142.86</v>
       </c>
       <c r="K71" t="n">
-        <v>52.44</v>
+        <v>54.82</v>
       </c>
       <c r="L71" t="n">
-        <v>146.39</v>
+        <v>153.02</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-6.85</v>
+        <v>-6.49</v>
       </c>
       <c r="K72" t="n">
-        <v>322.89</v>
+        <v>306.03</v>
       </c>
       <c r="L72" t="n">
-        <v>322.96</v>
+        <v>306.1</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-50.14</v>
+        <v>-49.08</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.85</v>
+        <v>-8.67</v>
       </c>
       <c r="L73" t="n">
-        <v>50.92</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>43.77</v>
+        <v>43.63</v>
       </c>
       <c r="K74" t="n">
-        <v>21.36</v>
+        <v>21.3</v>
       </c>
       <c r="L74" t="n">
-        <v>48.7</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.67</v>
+        <v>-2.62</v>
       </c>
       <c r="K75" t="n">
-        <v>63.07</v>
+        <v>61.73</v>
       </c>
       <c r="L75" t="n">
-        <v>63.13</v>
+        <v>61.78</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>26.3</v>
+        <v>28.32</v>
       </c>
       <c r="K76" t="n">
-        <v>-15.99</v>
+        <v>-17.22</v>
       </c>
       <c r="L76" t="n">
-        <v>30.78</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>35.1</v>
+        <v>34.04</v>
       </c>
       <c r="K77" t="n">
-        <v>-75.7</v>
+        <v>-73.42</v>
       </c>
       <c r="L77" t="n">
-        <v>83.44</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>49.51</v>
+        <v>50.44</v>
       </c>
       <c r="K78" t="n">
-        <v>-33.8</v>
+        <v>-34.43</v>
       </c>
       <c r="L78" t="n">
-        <v>59.95</v>
+        <v>61.07</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-64.75</v>
+        <v>-64.83</v>
       </c>
       <c r="K79" t="n">
         <v>2.09</v>
       </c>
       <c r="L79" t="n">
-        <v>64.79000000000001</v>
+        <v>64.87</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>116.45</v>
+        <v>112.47</v>
       </c>
       <c r="K80" t="n">
-        <v>72.31999999999999</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>137.07</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>49.43</v>
+        <v>52.55</v>
       </c>
       <c r="K81" t="n">
-        <v>-32.6</v>
+        <v>-34.66</v>
       </c>
       <c r="L81" t="n">
-        <v>59.22</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>114.13</v>
+        <v>108.75</v>
       </c>
       <c r="K82" t="n">
-        <v>133.77</v>
+        <v>127.47</v>
       </c>
       <c r="L82" t="n">
-        <v>175.85</v>
+        <v>167.56</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-27.91</v>
+        <v>-26.62</v>
       </c>
       <c r="K83" t="n">
-        <v>-205.11</v>
+        <v>-195.64</v>
       </c>
       <c r="L83" t="n">
-        <v>207</v>
+        <v>197.44</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-61.17</v>
+        <v>-66.39</v>
       </c>
       <c r="K84" t="n">
-        <v>50.8</v>
+        <v>55.14</v>
       </c>
       <c r="L84" t="n">
-        <v>79.51000000000001</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-59.19</v>
+        <v>-57.37</v>
       </c>
       <c r="K85" t="n">
-        <v>160.58</v>
+        <v>155.64</v>
       </c>
       <c r="L85" t="n">
-        <v>171.14</v>
+        <v>165.88</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>90.15000000000001</v>
+        <v>87.44</v>
       </c>
       <c r="K86" t="n">
-        <v>-249.59</v>
+        <v>-242.09</v>
       </c>
       <c r="L86" t="n">
-        <v>265.37</v>
+        <v>257.4</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-8.51</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-207.84</v>
+        <v>-206.6</v>
       </c>
       <c r="L87" t="n">
-        <v>208.01</v>
+        <v>206.78</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>148.96</v>
+        <v>153.07</v>
       </c>
       <c r="K88" t="n">
-        <v>35.35</v>
+        <v>36.33</v>
       </c>
       <c r="L88" t="n">
-        <v>153.1</v>
+        <v>157.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.78</v>
+        <v>-13.1</v>
       </c>
       <c r="K14" t="n">
-        <v>40.12</v>
+        <v>41.13</v>
       </c>
       <c r="L14" t="n">
-        <v>42.11</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>43.58</v>
+        <v>41.02</v>
       </c>
       <c r="K15" t="n">
-        <v>57.6</v>
+        <v>54.21</v>
       </c>
       <c r="L15" t="n">
-        <v>72.23</v>
+        <v>67.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.25</v>
+        <v>-12.48</v>
       </c>
       <c r="K16" t="n">
-        <v>-39.65</v>
+        <v>-40.39</v>
       </c>
       <c r="L16" t="n">
-        <v>41.5</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.22</v>
+        <v>-53.19</v>
       </c>
       <c r="K17" t="n">
-        <v>82.08</v>
+        <v>77.66</v>
       </c>
       <c r="L17" t="n">
-        <v>99.48999999999999</v>
+        <v>94.13</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>11.21</v>
+        <v>11.46</v>
       </c>
       <c r="K18" t="n">
-        <v>-52.13</v>
+        <v>-53.29</v>
       </c>
       <c r="L18" t="n">
-        <v>53.32</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7</v>
+        <v>4.53</v>
       </c>
       <c r="K19" t="n">
-        <v>84.55</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>84.68000000000001</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>14.77</v>
+        <v>15.34</v>
       </c>
       <c r="K20" t="n">
-        <v>-70.91</v>
+        <v>-73.64</v>
       </c>
       <c r="L20" t="n">
-        <v>72.43000000000001</v>
+        <v>75.22</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>70.38</v>
+        <v>65.12</v>
       </c>
       <c r="K21" t="n">
-        <v>178.42</v>
+        <v>165.06</v>
       </c>
       <c r="L21" t="n">
-        <v>191.8</v>
+        <v>177.44</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-9.67</v>
+        <v>-10.02</v>
       </c>
       <c r="K22" t="n">
-        <v>78.76000000000001</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>79.34999999999999</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-118.38</v>
+        <v>-111.86</v>
       </c>
       <c r="K23" t="n">
-        <v>-153.82</v>
+        <v>-145.33</v>
       </c>
       <c r="L23" t="n">
-        <v>194.1</v>
+        <v>183.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>71.81999999999999</v>
+        <v>76.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-61.79</v>
+        <v>-65.89</v>
       </c>
       <c r="L24" t="n">
-        <v>94.73999999999999</v>
+        <v>101.03</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>43.77</v>
+        <v>42.4</v>
       </c>
       <c r="K25" t="n">
-        <v>-164.66</v>
+        <v>-159.48</v>
       </c>
       <c r="L25" t="n">
-        <v>170.38</v>
+        <v>165.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-158.18</v>
+        <v>-164.31</v>
       </c>
       <c r="K26" t="n">
-        <v>32.76</v>
+        <v>34.03</v>
       </c>
       <c r="L26" t="n">
-        <v>161.53</v>
+        <v>167.8</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>141.04</v>
+        <v>149.78</v>
       </c>
       <c r="K27" t="n">
-        <v>-35.02</v>
+        <v>-37.19</v>
       </c>
       <c r="L27" t="n">
-        <v>145.32</v>
+        <v>154.33</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-54.38</v>
+        <v>-58.25</v>
       </c>
       <c r="K28" t="n">
-        <v>-121.88</v>
+        <v>-130.56</v>
       </c>
       <c r="L28" t="n">
-        <v>133.46</v>
+        <v>142.96</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.31</v>
+        <v>-27.27</v>
       </c>
       <c r="K29" t="n">
-        <v>-28.14</v>
+        <v>-29.17</v>
       </c>
       <c r="L29" t="n">
-        <v>38.52</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>64.13</v>
+        <v>60.32</v>
       </c>
       <c r="K30" t="n">
-        <v>49.54</v>
+        <v>46.6</v>
       </c>
       <c r="L30" t="n">
-        <v>81.04000000000001</v>
+        <v>76.22</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.09</v>
+        <v>-22.51</v>
       </c>
       <c r="K31" t="n">
-        <v>39.75</v>
+        <v>40.5</v>
       </c>
       <c r="L31" t="n">
-        <v>45.48</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>19.99</v>
+        <v>22.02</v>
       </c>
       <c r="K32" t="n">
-        <v>-27.95</v>
+        <v>-30.78</v>
       </c>
       <c r="L32" t="n">
-        <v>34.36</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>73.08</v>
+        <v>71.56</v>
       </c>
       <c r="K33" t="n">
-        <v>18.94</v>
+        <v>18.55</v>
       </c>
       <c r="L33" t="n">
-        <v>75.5</v>
+        <v>73.92</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>29.98</v>
+        <v>31.55</v>
       </c>
       <c r="K34" t="n">
-        <v>-41.01</v>
+        <v>-43.16</v>
       </c>
       <c r="L34" t="n">
-        <v>50.8</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>91.45</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-48.81</v>
+        <v>-48.14</v>
       </c>
       <c r="L35" t="n">
-        <v>103.66</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>39.63</v>
+        <v>41.09</v>
       </c>
       <c r="K36" t="n">
-        <v>-75.78</v>
+        <v>-78.56999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>85.52</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>7.59</v>
+        <v>7.8</v>
       </c>
       <c r="K37" t="n">
-        <v>83.8</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>84.14</v>
+        <v>86.42</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>193.59</v>
+        <v>180.62</v>
       </c>
       <c r="K38" t="n">
-        <v>-114.88</v>
+        <v>-107.19</v>
       </c>
       <c r="L38" t="n">
-        <v>225.11</v>
+        <v>210.03</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>134.59</v>
+        <v>130.7</v>
       </c>
       <c r="K39" t="n">
-        <v>-74.98999999999999</v>
+        <v>-72.83</v>
       </c>
       <c r="L39" t="n">
-        <v>154.07</v>
+        <v>149.62</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-131.03</v>
+        <v>-125.32</v>
       </c>
       <c r="K40" t="n">
-        <v>120.71</v>
+        <v>115.45</v>
       </c>
       <c r="L40" t="n">
-        <v>178.15</v>
+        <v>170.39</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-83.31</v>
+        <v>-91.04000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-85.7</v>
+        <v>-93.66</v>
       </c>
       <c r="L41" t="n">
-        <v>119.52</v>
+        <v>130.61</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-145.06</v>
+        <v>-138.07</v>
       </c>
       <c r="K42" t="n">
-        <v>233.76</v>
+        <v>222.5</v>
       </c>
       <c r="L42" t="n">
-        <v>275.11</v>
+        <v>261.86</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-163.66</v>
+        <v>-164</v>
       </c>
       <c r="K43" t="n">
-        <v>106.14</v>
+        <v>106.36</v>
       </c>
       <c r="L43" t="n">
-        <v>195.06</v>
+        <v>195.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-47.56</v>
+        <v>-46.12</v>
       </c>
       <c r="K44" t="n">
-        <v>-37.81</v>
+        <v>-36.66</v>
       </c>
       <c r="L44" t="n">
-        <v>60.76</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-35.53</v>
+        <v>-36.16</v>
       </c>
       <c r="K45" t="n">
-        <v>18.16</v>
+        <v>18.49</v>
       </c>
       <c r="L45" t="n">
-        <v>39.9</v>
+        <v>40.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>30.61</v>
+        <v>32.04</v>
       </c>
       <c r="K46" t="n">
-        <v>-18.27</v>
+        <v>-19.13</v>
       </c>
       <c r="L46" t="n">
-        <v>35.65</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-10.97</v>
+        <v>-10.85</v>
       </c>
       <c r="K47" t="n">
-        <v>-74.98</v>
+        <v>-74.20999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>75.78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-51.27</v>
+        <v>-53.4</v>
       </c>
       <c r="K48" t="n">
-        <v>-20.73</v>
+        <v>-21.59</v>
       </c>
       <c r="L48" t="n">
-        <v>55.31</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>11.57</v>
+        <v>12.46</v>
       </c>
       <c r="K49" t="n">
-        <v>-41.35</v>
+        <v>-44.51</v>
       </c>
       <c r="L49" t="n">
-        <v>42.93</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.33</v>
+        <v>-3.22</v>
       </c>
       <c r="K50" t="n">
-        <v>-130.99</v>
+        <v>-127</v>
       </c>
       <c r="L50" t="n">
-        <v>131.03</v>
+        <v>127.04</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-125.97</v>
+        <v>-120.49</v>
       </c>
       <c r="K51" t="n">
-        <v>-46.77</v>
+        <v>-44.74</v>
       </c>
       <c r="L51" t="n">
-        <v>134.38</v>
+        <v>128.53</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.49</v>
+        <v>-4.53</v>
       </c>
       <c r="K52" t="n">
-        <v>86.48999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>86.61</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>10.13</v>
+        <v>10.8</v>
       </c>
       <c r="K53" t="n">
-        <v>13.14</v>
+        <v>14.01</v>
       </c>
       <c r="L53" t="n">
-        <v>16.59</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>112.61</v>
+        <v>115.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-12.11</v>
+        <v>-12.42</v>
       </c>
       <c r="L54" t="n">
-        <v>113.26</v>
+        <v>116.12</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-67.02</v>
+        <v>-73.31999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>-53.64</v>
+        <v>-58.68</v>
       </c>
       <c r="L55" t="n">
-        <v>85.84999999999999</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-164.87</v>
+        <v>-172.15</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.77</v>
+        <v>-2.89</v>
       </c>
       <c r="L56" t="n">
-        <v>164.89</v>
+        <v>172.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>90.47</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>180.32</v>
+        <v>180.52</v>
       </c>
       <c r="L57" t="n">
-        <v>201.74</v>
+        <v>201.96</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-64.91</v>
+        <v>-61.1</v>
       </c>
       <c r="K58" t="n">
-        <v>-342.38</v>
+        <v>-322.28</v>
       </c>
       <c r="L58" t="n">
-        <v>348.48</v>
+        <v>328.02</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.56</v>
+        <v>-43.24</v>
       </c>
       <c r="K59" t="n">
-        <v>22.48</v>
+        <v>22.32</v>
       </c>
       <c r="L59" t="n">
-        <v>49.02</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>29.7</v>
+        <v>30.43</v>
       </c>
       <c r="K60" t="n">
-        <v>28.5</v>
+        <v>29.2</v>
       </c>
       <c r="L60" t="n">
-        <v>41.17</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>36.78</v>
+        <v>38.98</v>
       </c>
       <c r="K61" t="n">
-        <v>6.14</v>
+        <v>6.51</v>
       </c>
       <c r="L61" t="n">
-        <v>37.29</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>44.28</v>
+        <v>47.57</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.6</v>
+        <v>-3.87</v>
       </c>
       <c r="L62" t="n">
-        <v>44.42</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>34.58</v>
+        <v>35.07</v>
       </c>
       <c r="K63" t="n">
-        <v>44.5</v>
+        <v>45.14</v>
       </c>
       <c r="L63" t="n">
-        <v>56.36</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-9.039999999999999</v>
+        <v>-8.99</v>
       </c>
       <c r="K64" t="n">
-        <v>-64.73999999999999</v>
+        <v>-64.37</v>
       </c>
       <c r="L64" t="n">
-        <v>65.37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-103.02</v>
+        <v>-101.8</v>
       </c>
       <c r="K65" t="n">
-        <v>21.77</v>
+        <v>21.51</v>
       </c>
       <c r="L65" t="n">
-        <v>105.29</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-140.9</v>
+        <v>-132.44</v>
       </c>
       <c r="K66" t="n">
-        <v>9.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>141.19</v>
+        <v>132.72</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.81</v>
+        <v>-3.95</v>
       </c>
       <c r="K67" t="n">
-        <v>-76.81999999999999</v>
+        <v>-79.52</v>
       </c>
       <c r="L67" t="n">
-        <v>76.91</v>
+        <v>79.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-74.66</v>
+        <v>-77.01000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-73.05</v>
+        <v>-75.34999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>104.45</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>46.49</v>
+        <v>45.45</v>
       </c>
       <c r="K69" t="n">
-        <v>146.12</v>
+        <v>142.85</v>
       </c>
       <c r="L69" t="n">
-        <v>153.34</v>
+        <v>149.91</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-194.53</v>
+        <v>-184.51</v>
       </c>
       <c r="K70" t="n">
-        <v>-39.65</v>
+        <v>-37.6</v>
       </c>
       <c r="L70" t="n">
-        <v>198.53</v>
+        <v>188.3</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-142.86</v>
+        <v>-149.94</v>
       </c>
       <c r="K71" t="n">
-        <v>54.82</v>
+        <v>57.54</v>
       </c>
       <c r="L71" t="n">
-        <v>153.02</v>
+        <v>160.6</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-6.49</v>
+        <v>-6.09</v>
       </c>
       <c r="K72" t="n">
-        <v>306.03</v>
+        <v>286.76</v>
       </c>
       <c r="L72" t="n">
-        <v>306.1</v>
+        <v>286.82</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-49.08</v>
+        <v>-53.26</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.67</v>
+        <v>-9.41</v>
       </c>
       <c r="L73" t="n">
-        <v>49.84</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>43.63</v>
+        <v>43.48</v>
       </c>
       <c r="K74" t="n">
-        <v>21.3</v>
+        <v>21.23</v>
       </c>
       <c r="L74" t="n">
-        <v>48.56</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.62</v>
+        <v>-2.55</v>
       </c>
       <c r="K75" t="n">
-        <v>61.73</v>
+        <v>60.19</v>
       </c>
       <c r="L75" t="n">
-        <v>61.78</v>
+        <v>60.24</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>28.32</v>
+        <v>30.63</v>
       </c>
       <c r="K76" t="n">
-        <v>-17.22</v>
+        <v>-18.62</v>
       </c>
       <c r="L76" t="n">
-        <v>33.14</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>34.04</v>
+        <v>32.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-73.42</v>
+        <v>-70.81999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>80.93000000000001</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>50.44</v>
+        <v>51.51</v>
       </c>
       <c r="K78" t="n">
-        <v>-34.43</v>
+        <v>-35.16</v>
       </c>
       <c r="L78" t="n">
-        <v>61.07</v>
+        <v>62.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-64.83</v>
+        <v>-64.92</v>
       </c>
       <c r="K79" t="n">
         <v>2.09</v>
       </c>
       <c r="L79" t="n">
-        <v>64.87</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>112.47</v>
+        <v>107.92</v>
       </c>
       <c r="K80" t="n">
-        <v>69.84999999999999</v>
+        <v>67.02</v>
       </c>
       <c r="L80" t="n">
-        <v>132.39</v>
+        <v>127.04</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>52.55</v>
+        <v>56.11</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.66</v>
+        <v>-37.01</v>
       </c>
       <c r="L81" t="n">
-        <v>62.95</v>
+        <v>67.22</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>108.75</v>
+        <v>102.6</v>
       </c>
       <c r="K82" t="n">
-        <v>127.47</v>
+        <v>120.26</v>
       </c>
       <c r="L82" t="n">
-        <v>167.56</v>
+        <v>158.08</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-26.62</v>
+        <v>-25.15</v>
       </c>
       <c r="K83" t="n">
-        <v>-195.64</v>
+        <v>-184.81</v>
       </c>
       <c r="L83" t="n">
-        <v>197.44</v>
+        <v>186.52</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-66.39</v>
+        <v>-72.36</v>
       </c>
       <c r="K84" t="n">
-        <v>55.14</v>
+        <v>60.1</v>
       </c>
       <c r="L84" t="n">
-        <v>86.3</v>
+        <v>94.06</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-57.37</v>
+        <v>-55.29</v>
       </c>
       <c r="K85" t="n">
-        <v>155.64</v>
+        <v>150</v>
       </c>
       <c r="L85" t="n">
-        <v>165.88</v>
+        <v>159.86</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>87.44</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>-242.09</v>
+        <v>-233.52</v>
       </c>
       <c r="L86" t="n">
-        <v>257.4</v>
+        <v>248.28</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="K87" t="n">
-        <v>-206.6</v>
+        <v>-205.19</v>
       </c>
       <c r="L87" t="n">
-        <v>206.78</v>
+        <v>205.36</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>153.07</v>
+        <v>157.77</v>
       </c>
       <c r="K88" t="n">
-        <v>36.33</v>
+        <v>37.44</v>
       </c>
       <c r="L88" t="n">
-        <v>157.32</v>
+        <v>162.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.43</v>
+        <v>0.88</v>
       </c>
       <c r="F14" t="n">
-        <v>7.33</v>
+        <v>8.16</v>
       </c>
       <c r="G14" t="n">
-        <v>235.5</v>
+        <v>244.7</v>
       </c>
       <c r="H14" t="n">
-        <v>77.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.1</v>
+        <v>-14.29</v>
       </c>
       <c r="K14" t="n">
-        <v>41.13</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>43.16</v>
+        <v>81.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:34:13</t>
+          <t>04:32:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.08</v>
+        <v>2.42</v>
       </c>
       <c r="F15" t="n">
-        <v>6.98</v>
+        <v>8.16</v>
       </c>
       <c r="G15" t="n">
-        <v>227.7</v>
+        <v>242.2</v>
       </c>
       <c r="H15" t="n">
-        <v>80.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>41.02</v>
+        <v>41.07</v>
       </c>
       <c r="K15" t="n">
-        <v>54.21</v>
+        <v>58.34</v>
       </c>
       <c r="L15" t="n">
-        <v>67.98</v>
+        <v>71.34999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:08</t>
+          <t>04:35:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="F16" t="n">
-        <v>7.82</v>
+        <v>1.18</v>
       </c>
       <c r="G16" t="n">
-        <v>240.1</v>
+        <v>243.8</v>
       </c>
       <c r="H16" t="n">
-        <v>76.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.48</v>
+        <v>-29.91</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.39</v>
+        <v>-2.75</v>
       </c>
       <c r="L16" t="n">
-        <v>42.28</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:39:55</t>
+          <t>04:40:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="F17" t="n">
-        <v>7.45</v>
+        <v>5.37</v>
       </c>
       <c r="G17" t="n">
-        <v>237.3</v>
+        <v>236.1</v>
       </c>
       <c r="H17" t="n">
-        <v>80.5</v>
+        <v>75.8</v>
       </c>
       <c r="I17" t="n">
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-53.19</v>
+        <v>-46.17</v>
       </c>
       <c r="K17" t="n">
-        <v>77.66</v>
+        <v>42.96</v>
       </c>
       <c r="L17" t="n">
-        <v>94.13</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:18</t>
+          <t>04:42:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.89</v>
+        <v>1.24</v>
       </c>
       <c r="F18" t="n">
-        <v>6.94</v>
+        <v>1.54</v>
       </c>
       <c r="G18" t="n">
-        <v>238.6</v>
+        <v>242.7</v>
       </c>
       <c r="H18" t="n">
-        <v>81.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>11.46</v>
+        <v>45.05</v>
       </c>
       <c r="K18" t="n">
-        <v>-53.29</v>
+        <v>-11.72</v>
       </c>
       <c r="L18" t="n">
-        <v>54.5</v>
+        <v>46.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:43:30</t>
+          <t>04:44:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="F19" t="n">
-        <v>6.93</v>
+        <v>8.06</v>
       </c>
       <c r="G19" t="n">
-        <v>233.4</v>
+        <v>242.4</v>
       </c>
       <c r="H19" t="n">
-        <v>77.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>4.53</v>
+        <v>-51</v>
       </c>
       <c r="K19" t="n">
-        <v>81.54000000000001</v>
+        <v>-34.03</v>
       </c>
       <c r="L19" t="n">
-        <v>81.67</v>
+        <v>61.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:47:24</t>
+          <t>04:48:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.71</v>
+        <v>1.51</v>
       </c>
       <c r="F20" t="n">
-        <v>7.39</v>
+        <v>8.16</v>
       </c>
       <c r="G20" t="n">
-        <v>249.1</v>
+        <v>247.6</v>
       </c>
       <c r="H20" t="n">
-        <v>80.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>15.34</v>
+        <v>-83.48999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-73.64</v>
+        <v>-107.03</v>
       </c>
       <c r="L20" t="n">
-        <v>75.22</v>
+        <v>135.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:48:23</t>
+          <t>04:51:10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="F21" t="n">
-        <v>7.01</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>238.7</v>
+        <v>242.9</v>
       </c>
       <c r="H21" t="n">
-        <v>80.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>65.12</v>
+        <v>-68.12</v>
       </c>
       <c r="K21" t="n">
-        <v>165.06</v>
+        <v>106.93</v>
       </c>
       <c r="L21" t="n">
-        <v>177.44</v>
+        <v>126.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:50:51</t>
+          <t>04:52:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="F22" t="n">
-        <v>6.73</v>
+        <v>4.1</v>
       </c>
       <c r="G22" t="n">
-        <v>248</v>
+        <v>242.3</v>
       </c>
       <c r="H22" t="n">
-        <v>83.2</v>
+        <v>76.2</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-10.02</v>
+        <v>-24.51</v>
       </c>
       <c r="K22" t="n">
-        <v>81.54000000000001</v>
+        <v>-87.42</v>
       </c>
       <c r="L22" t="n">
-        <v>82.16</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:55:25</t>
+          <t>04:55:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.86</v>
+        <v>1.32</v>
       </c>
       <c r="F23" t="n">
-        <v>6.54</v>
+        <v>8.16</v>
       </c>
       <c r="G23" t="n">
-        <v>253.9</v>
+        <v>229.1</v>
       </c>
       <c r="H23" t="n">
-        <v>80.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-111.86</v>
+        <v>-150.63</v>
       </c>
       <c r="K23" t="n">
-        <v>-145.33</v>
+        <v>-157.96</v>
       </c>
       <c r="L23" t="n">
-        <v>183.39</v>
+        <v>218.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:57:50</t>
+          <t>04:57:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="F24" t="n">
-        <v>7.02</v>
+        <v>8.16</v>
       </c>
       <c r="G24" t="n">
-        <v>242</v>
+        <v>242.2</v>
       </c>
       <c r="H24" t="n">
-        <v>80.5</v>
+        <v>81.3</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>76.58</v>
+        <v>131.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-65.89</v>
+        <v>-14.12</v>
       </c>
       <c r="L24" t="n">
-        <v>101.03</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:59:57</t>
+          <t>04:58:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="F25" t="n">
-        <v>6.59</v>
+        <v>1.37</v>
       </c>
       <c r="G25" t="n">
-        <v>241.2</v>
+        <v>245.4</v>
       </c>
       <c r="H25" t="n">
-        <v>73.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>42.4</v>
+        <v>88.64</v>
       </c>
       <c r="K25" t="n">
-        <v>-159.48</v>
+        <v>-90.41</v>
       </c>
       <c r="L25" t="n">
-        <v>165.02</v>
+        <v>126.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:04:18</t>
+          <t>05:03:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="F26" t="n">
-        <v>7.41</v>
+        <v>3.77</v>
       </c>
       <c r="G26" t="n">
-        <v>234.3</v>
+        <v>242.1</v>
       </c>
       <c r="H26" t="n">
-        <v>80.5</v>
+        <v>82.2</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-164.31</v>
+        <v>-75.04000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>34.03</v>
+        <v>-121.01</v>
       </c>
       <c r="L26" t="n">
-        <v>167.8</v>
+        <v>142.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:06:35</t>
+          <t>05:05:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="F27" t="n">
-        <v>7.52</v>
+        <v>1.84</v>
       </c>
       <c r="G27" t="n">
-        <v>242.6</v>
+        <v>234.4</v>
       </c>
       <c r="H27" t="n">
-        <v>82.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>149.78</v>
+        <v>147.32</v>
       </c>
       <c r="K27" t="n">
-        <v>-37.19</v>
+        <v>20.05</v>
       </c>
       <c r="L27" t="n">
-        <v>154.33</v>
+        <v>148.68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:07:40</t>
+          <t>05:07:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="F28" t="n">
-        <v>7.12</v>
+        <v>7.57</v>
       </c>
       <c r="G28" t="n">
-        <v>237.6</v>
+        <v>249</v>
       </c>
       <c r="H28" t="n">
-        <v>80.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-58.25</v>
+        <v>-276</v>
       </c>
       <c r="K28" t="n">
-        <v>-130.56</v>
+        <v>-100.85</v>
       </c>
       <c r="L28" t="n">
-        <v>142.96</v>
+        <v>293.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:16:11</t>
+          <t>05:18:29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.95</v>
+        <v>1.74</v>
       </c>
       <c r="F29" t="n">
-        <v>7.39</v>
+        <v>8.16</v>
       </c>
       <c r="G29" t="n">
-        <v>240.7</v>
+        <v>243.9</v>
       </c>
       <c r="H29" t="n">
-        <v>76.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.27</v>
+        <v>-52.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-29.17</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>39.93</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:17:41</t>
+          <t>05:20:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="F30" t="n">
-        <v>6.53</v>
+        <v>1.45</v>
       </c>
       <c r="G30" t="n">
-        <v>227.6</v>
+        <v>235.6</v>
       </c>
       <c r="H30" t="n">
-        <v>83.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>60.32</v>
+        <v>10.41</v>
       </c>
       <c r="K30" t="n">
-        <v>46.6</v>
+        <v>-40.08</v>
       </c>
       <c r="L30" t="n">
-        <v>76.22</v>
+        <v>41.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:19:48</t>
+          <t>05:23:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="F31" t="n">
-        <v>6.77</v>
+        <v>4.39</v>
       </c>
       <c r="G31" t="n">
-        <v>238.2</v>
+        <v>236.5</v>
       </c>
       <c r="H31" t="n">
-        <v>81.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.51</v>
+        <v>-17.92</v>
       </c>
       <c r="K31" t="n">
-        <v>40.5</v>
+        <v>-38.08</v>
       </c>
       <c r="L31" t="n">
-        <v>46.34</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:23:39</t>
+          <t>05:27:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.82</v>
+        <v>1.62</v>
       </c>
       <c r="F32" t="n">
-        <v>7.22</v>
+        <v>6.94</v>
       </c>
       <c r="G32" t="n">
-        <v>239.3</v>
+        <v>234.4</v>
       </c>
       <c r="H32" t="n">
-        <v>77.2</v>
+        <v>81.3</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>22.02</v>
+        <v>-21.75</v>
       </c>
       <c r="K32" t="n">
-        <v>-30.78</v>
+        <v>-78.26000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>37.85</v>
+        <v>81.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:25:51</t>
+          <t>05:29:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="F33" t="n">
-        <v>6.99</v>
+        <v>5.68</v>
       </c>
       <c r="G33" t="n">
-        <v>242.7</v>
+        <v>237.3</v>
       </c>
       <c r="H33" t="n">
-        <v>77.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>71.56</v>
+        <v>-85.94</v>
       </c>
       <c r="K33" t="n">
-        <v>18.55</v>
+        <v>39.11</v>
       </c>
       <c r="L33" t="n">
-        <v>73.92</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:26:53</t>
+          <t>05:31:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="F34" t="n">
-        <v>6.97</v>
+        <v>8.16</v>
       </c>
       <c r="G34" t="n">
-        <v>239.1</v>
+        <v>241.1</v>
       </c>
       <c r="H34" t="n">
-        <v>76.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>31.55</v>
+        <v>12.68</v>
       </c>
       <c r="K34" t="n">
-        <v>-43.16</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>53.46</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:31:57</t>
+          <t>05:38:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="F35" t="n">
-        <v>6.46</v>
+        <v>6.39</v>
       </c>
       <c r="G35" t="n">
-        <v>226.1</v>
+        <v>249.6</v>
       </c>
       <c r="H35" t="n">
-        <v>78</v>
+        <v>81.7</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>90.18000000000001</v>
+        <v>48.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-48.14</v>
+        <v>19.67</v>
       </c>
       <c r="L35" t="n">
-        <v>102.23</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:34:16</t>
+          <t>05:39:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="F36" t="n">
-        <v>7.17</v>
+        <v>8.16</v>
       </c>
       <c r="G36" t="n">
-        <v>240.5</v>
+        <v>245.7</v>
       </c>
       <c r="H36" t="n">
-        <v>79.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>41.09</v>
+        <v>-26.24</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.56999999999999</v>
+        <v>177.14</v>
       </c>
       <c r="L36" t="n">
-        <v>88.66</v>
+        <v>179.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:36:38</t>
+          <t>05:41:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="F37" t="n">
-        <v>7.32</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>249.6</v>
+        <v>234.9</v>
       </c>
       <c r="H37" t="n">
-        <v>75.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>7.8</v>
+        <v>-5.53</v>
       </c>
       <c r="K37" t="n">
-        <v>86.06999999999999</v>
+        <v>-75.63</v>
       </c>
       <c r="L37" t="n">
-        <v>86.42</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:40:58</t>
+          <t>05:47:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="F38" t="n">
-        <v>7.07</v>
+        <v>8.16</v>
       </c>
       <c r="G38" t="n">
-        <v>245.7</v>
+        <v>228.1</v>
       </c>
       <c r="H38" t="n">
-        <v>77.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>180.62</v>
+        <v>-160.55</v>
       </c>
       <c r="K38" t="n">
-        <v>-107.19</v>
+        <v>134.85</v>
       </c>
       <c r="L38" t="n">
-        <v>210.03</v>
+        <v>209.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:43:26</t>
+          <t>05:49:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>6.81</v>
+        <v>6.1</v>
       </c>
       <c r="G39" t="n">
-        <v>234.9</v>
+        <v>258.9</v>
       </c>
       <c r="H39" t="n">
-        <v>91</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>130.7</v>
+        <v>-95.81999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-72.83</v>
+        <v>-74.73</v>
       </c>
       <c r="L39" t="n">
-        <v>149.62</v>
+        <v>121.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:45:18</t>
+          <t>05:50:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="F40" t="n">
-        <v>6.38</v>
+        <v>4.79</v>
       </c>
       <c r="G40" t="n">
-        <v>232</v>
+        <v>240.8</v>
       </c>
       <c r="H40" t="n">
-        <v>83.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-125.32</v>
+        <v>-99.89</v>
       </c>
       <c r="K40" t="n">
-        <v>115.45</v>
+        <v>149.37</v>
       </c>
       <c r="L40" t="n">
-        <v>170.39</v>
+        <v>179.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:51:31</t>
+          <t>05:55:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="F41" t="n">
-        <v>7.92</v>
+        <v>2.07</v>
       </c>
       <c r="G41" t="n">
-        <v>230.5</v>
+        <v>234.8</v>
       </c>
       <c r="H41" t="n">
-        <v>78.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-91.04000000000001</v>
+        <v>-169.93</v>
       </c>
       <c r="K41" t="n">
-        <v>-93.66</v>
+        <v>90.88</v>
       </c>
       <c r="L41" t="n">
-        <v>130.61</v>
+        <v>192.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:53:04</t>
+          <t>05:56:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="F42" t="n">
-        <v>7.01</v>
+        <v>4.49</v>
       </c>
       <c r="G42" t="n">
-        <v>240</v>
+        <v>244.3</v>
       </c>
       <c r="H42" t="n">
-        <v>77.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-138.07</v>
+        <v>-214</v>
       </c>
       <c r="K42" t="n">
-        <v>222.5</v>
+        <v>-164.12</v>
       </c>
       <c r="L42" t="n">
-        <v>261.86</v>
+        <v>269.69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:55:20</t>
+          <t>05:58:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="F43" t="n">
-        <v>6.71</v>
+        <v>6.85</v>
       </c>
       <c r="G43" t="n">
-        <v>235.6</v>
+        <v>236</v>
       </c>
       <c r="H43" t="n">
-        <v>75.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-164</v>
+        <v>132.14</v>
       </c>
       <c r="K43" t="n">
-        <v>106.36</v>
+        <v>-147.87</v>
       </c>
       <c r="L43" t="n">
-        <v>195.47</v>
+        <v>198.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:08:46</t>
+          <t>06:06:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.13</v>
+        <v>1.78</v>
       </c>
       <c r="F44" t="n">
-        <v>7.19</v>
+        <v>8.16</v>
       </c>
       <c r="G44" t="n">
-        <v>250.5</v>
+        <v>239.2</v>
       </c>
       <c r="H44" t="n">
-        <v>79.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-46.12</v>
+        <v>-14.6</v>
       </c>
       <c r="K44" t="n">
-        <v>-36.66</v>
+        <v>64.12</v>
       </c>
       <c r="L44" t="n">
-        <v>58.91</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:10:00</t>
+          <t>06:08:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="F45" t="n">
-        <v>6.87</v>
+        <v>7.62</v>
       </c>
       <c r="G45" t="n">
-        <v>235.7</v>
+        <v>257.3</v>
       </c>
       <c r="H45" t="n">
-        <v>81.7</v>
+        <v>75</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.16</v>
+        <v>-61.08</v>
       </c>
       <c r="K45" t="n">
-        <v>18.49</v>
+        <v>-32.44</v>
       </c>
       <c r="L45" t="n">
-        <v>40.61</v>
+        <v>69.16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:11:36</t>
+          <t>06:09:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>7.37</v>
+        <v>1.57</v>
       </c>
       <c r="G46" t="n">
-        <v>253.1</v>
+        <v>251.7</v>
       </c>
       <c r="H46" t="n">
-        <v>85.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>32.04</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-19.13</v>
+        <v>-41.45</v>
       </c>
       <c r="L46" t="n">
-        <v>37.32</v>
+        <v>42.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:17:10</t>
+          <t>06:14:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="F47" t="n">
-        <v>6.53</v>
+        <v>8.16</v>
       </c>
       <c r="G47" t="n">
-        <v>256.5</v>
+        <v>242.3</v>
       </c>
       <c r="H47" t="n">
-        <v>81.2</v>
+        <v>78.3</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-10.85</v>
+        <v>-53.08</v>
       </c>
       <c r="K47" t="n">
-        <v>-74.20999999999999</v>
+        <v>61.35</v>
       </c>
       <c r="L47" t="n">
-        <v>75</v>
+        <v>81.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:18:08</t>
+          <t>06:16:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="F48" t="n">
-        <v>7.17</v>
+        <v>6.86</v>
       </c>
       <c r="G48" t="n">
-        <v>234.3</v>
+        <v>248.4</v>
       </c>
       <c r="H48" t="n">
-        <v>83.3</v>
+        <v>76</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-53.4</v>
+        <v>-119.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-21.59</v>
+        <v>6.41</v>
       </c>
       <c r="L48" t="n">
-        <v>57.6</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:20:33</t>
+          <t>06:18:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>6.86</v>
+        <v>4.09</v>
       </c>
       <c r="G49" t="n">
-        <v>240.5</v>
+        <v>234.1</v>
       </c>
       <c r="H49" t="n">
-        <v>83.8</v>
+        <v>85</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>12.46</v>
+        <v>-44.68</v>
       </c>
       <c r="K49" t="n">
-        <v>-44.51</v>
+        <v>-71.28</v>
       </c>
       <c r="L49" t="n">
-        <v>46.22</v>
+        <v>84.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:23:41</t>
+          <t>06:23:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="F50" t="n">
-        <v>6.63</v>
+        <v>8.16</v>
       </c>
       <c r="G50" t="n">
-        <v>245.6</v>
+        <v>241.2</v>
       </c>
       <c r="H50" t="n">
-        <v>76.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.22</v>
+        <v>110.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-127</v>
+        <v>28.32</v>
       </c>
       <c r="L50" t="n">
-        <v>127.04</v>
+        <v>113.88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:24:58</t>
+          <t>06:24:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="F51" t="n">
-        <v>7.53</v>
+        <v>4.74</v>
       </c>
       <c r="G51" t="n">
-        <v>257.4</v>
+        <v>247.7</v>
       </c>
       <c r="H51" t="n">
-        <v>79.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-120.49</v>
+        <v>7.43</v>
       </c>
       <c r="K51" t="n">
-        <v>-44.74</v>
+        <v>-83.98999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>128.53</v>
+        <v>84.31999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:26:28</t>
+          <t>06:25:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="F52" t="n">
-        <v>6.99</v>
+        <v>7.71</v>
       </c>
       <c r="G52" t="n">
-        <v>250.1</v>
+        <v>240.8</v>
       </c>
       <c r="H52" t="n">
-        <v>80.7</v>
+        <v>83.3</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.53</v>
+        <v>-28.4</v>
       </c>
       <c r="K52" t="n">
-        <v>87.40000000000001</v>
+        <v>-106.97</v>
       </c>
       <c r="L52" t="n">
-        <v>87.52</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:31:25</t>
+          <t>06:30:52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="F53" t="n">
-        <v>5.97</v>
+        <v>7.94</v>
       </c>
       <c r="G53" t="n">
-        <v>239</v>
+        <v>226.5</v>
       </c>
       <c r="H53" t="n">
-        <v>79.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>10.8</v>
+        <v>175.1</v>
       </c>
       <c r="K53" t="n">
-        <v>14.01</v>
+        <v>-25.14</v>
       </c>
       <c r="L53" t="n">
-        <v>17.69</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:33:05</t>
+          <t>06:32:12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="F54" t="n">
-        <v>7.36</v>
+        <v>8.16</v>
       </c>
       <c r="G54" t="n">
-        <v>246.3</v>
+        <v>237.6</v>
       </c>
       <c r="H54" t="n">
-        <v>79.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>115.45</v>
+        <v>-119.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-12.42</v>
+        <v>-100.45</v>
       </c>
       <c r="L54" t="n">
-        <v>116.12</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:35:07</t>
+          <t>06:33:11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="F55" t="n">
-        <v>6.69</v>
+        <v>2.95</v>
       </c>
       <c r="G55" t="n">
-        <v>230.3</v>
+        <v>247.4</v>
       </c>
       <c r="H55" t="n">
-        <v>81.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-73.31999999999999</v>
+        <v>186.72</v>
       </c>
       <c r="K55" t="n">
-        <v>-58.68</v>
+        <v>-38.65</v>
       </c>
       <c r="L55" t="n">
-        <v>93.91</v>
+        <v>190.68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:40:05</t>
+          <t>06:36:43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="F56" t="n">
-        <v>7.26</v>
+        <v>4.39</v>
       </c>
       <c r="G56" t="n">
-        <v>261.4</v>
+        <v>239.3</v>
       </c>
       <c r="H56" t="n">
-        <v>83.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-172.15</v>
+        <v>-21.04</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.89</v>
+        <v>-148.14</v>
       </c>
       <c r="L56" t="n">
-        <v>172.17</v>
+        <v>149.62</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:41:15</t>
+          <t>06:38:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="F57" t="n">
-        <v>6.77</v>
+        <v>4.58</v>
       </c>
       <c r="G57" t="n">
-        <v>229.4</v>
+        <v>232.9</v>
       </c>
       <c r="H57" t="n">
-        <v>84.8</v>
+        <v>72.3</v>
       </c>
       <c r="I57" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>90.56999999999999</v>
+        <v>-91.28</v>
       </c>
       <c r="K57" t="n">
-        <v>180.52</v>
+        <v>158.91</v>
       </c>
       <c r="L57" t="n">
-        <v>201.96</v>
+        <v>183.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:42:31</t>
+          <t>06:39:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="F58" t="n">
-        <v>6.83</v>
+        <v>8.16</v>
       </c>
       <c r="G58" t="n">
-        <v>247.3</v>
+        <v>247.7</v>
       </c>
       <c r="H58" t="n">
-        <v>79</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-61.1</v>
+        <v>-107.8</v>
       </c>
       <c r="K58" t="n">
-        <v>-322.28</v>
+        <v>219.35</v>
       </c>
       <c r="L58" t="n">
-        <v>328.02</v>
+        <v>244.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:54:52</t>
+          <t>06:50:05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="F59" t="n">
-        <v>7</v>
+        <v>8.16</v>
       </c>
       <c r="G59" t="n">
-        <v>232.6</v>
+        <v>243.4</v>
       </c>
       <c r="H59" t="n">
-        <v>80.7</v>
+        <v>83</v>
       </c>
       <c r="I59" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.24</v>
+        <v>-7.35</v>
       </c>
       <c r="K59" t="n">
-        <v>22.32</v>
+        <v>5.04</v>
       </c>
       <c r="L59" t="n">
-        <v>48.66</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:52</t>
+          <t>06:51:50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="F60" t="n">
-        <v>6.91</v>
+        <v>5.53</v>
       </c>
       <c r="G60" t="n">
-        <v>240.7</v>
+        <v>242.4</v>
       </c>
       <c r="H60" t="n">
-        <v>72.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>30.43</v>
+        <v>-3.95</v>
       </c>
       <c r="K60" t="n">
-        <v>29.2</v>
+        <v>62.86</v>
       </c>
       <c r="L60" t="n">
-        <v>42.17</v>
+        <v>62.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:59:02</t>
+          <t>06:53:52</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.71</v>
+        <v>1.26</v>
       </c>
       <c r="F61" t="n">
-        <v>7.4</v>
+        <v>1.56</v>
       </c>
       <c r="G61" t="n">
-        <v>234</v>
+        <v>249.3</v>
       </c>
       <c r="H61" t="n">
-        <v>76.5</v>
+        <v>83.3</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>38.98</v>
+        <v>48.15</v>
       </c>
       <c r="K61" t="n">
-        <v>6.51</v>
+        <v>3.23</v>
       </c>
       <c r="L61" t="n">
-        <v>39.52</v>
+        <v>48.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:03:33</t>
+          <t>06:58:23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="F62" t="n">
-        <v>6.83</v>
+        <v>8.16</v>
       </c>
       <c r="G62" t="n">
-        <v>246.7</v>
+        <v>255.2</v>
       </c>
       <c r="H62" t="n">
-        <v>80.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>47.57</v>
+        <v>-84.97</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.87</v>
+        <v>40.68</v>
       </c>
       <c r="L62" t="n">
-        <v>47.73</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:05:17</t>
+          <t>06:59:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="F63" t="n">
-        <v>6.42</v>
+        <v>8.16</v>
       </c>
       <c r="G63" t="n">
-        <v>238.8</v>
+        <v>244.4</v>
       </c>
       <c r="H63" t="n">
-        <v>78.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>35.07</v>
+        <v>29.14</v>
       </c>
       <c r="K63" t="n">
-        <v>45.14</v>
+        <v>-60.67</v>
       </c>
       <c r="L63" t="n">
-        <v>57.16</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:05:59</t>
+          <t>07:00:42</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="F64" t="n">
-        <v>7.49</v>
+        <v>8.16</v>
       </c>
       <c r="G64" t="n">
-        <v>251.5</v>
+        <v>250.1</v>
       </c>
       <c r="H64" t="n">
-        <v>83.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.99</v>
+        <v>11.59</v>
       </c>
       <c r="K64" t="n">
-        <v>-64.37</v>
+        <v>87.95</v>
       </c>
       <c r="L64" t="n">
-        <v>65</v>
+        <v>88.70999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:11:04</t>
+          <t>07:05:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="F65" t="n">
-        <v>7.35</v>
+        <v>8.16</v>
       </c>
       <c r="G65" t="n">
-        <v>258.2</v>
+        <v>246.8</v>
       </c>
       <c r="H65" t="n">
-        <v>85.8</v>
+        <v>80.7</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-101.8</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>21.51</v>
+        <v>-62.18</v>
       </c>
       <c r="L65" t="n">
-        <v>104.05</v>
+        <v>116.36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:12:49</t>
+          <t>07:06:38</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="F66" t="n">
-        <v>7.06</v>
+        <v>5.99</v>
       </c>
       <c r="G66" t="n">
-        <v>246.4</v>
+        <v>238.1</v>
       </c>
       <c r="H66" t="n">
-        <v>80.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-132.44</v>
+        <v>64.13</v>
       </c>
       <c r="K66" t="n">
-        <v>8.550000000000001</v>
+        <v>-103.66</v>
       </c>
       <c r="L66" t="n">
-        <v>132.72</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:14:51</t>
+          <t>07:08:13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="F67" t="n">
-        <v>7.1</v>
+        <v>1.41</v>
       </c>
       <c r="G67" t="n">
-        <v>244</v>
+        <v>255.6</v>
       </c>
       <c r="H67" t="n">
-        <v>87.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.95</v>
+        <v>17.85</v>
       </c>
       <c r="K67" t="n">
-        <v>-79.52</v>
+        <v>70.39</v>
       </c>
       <c r="L67" t="n">
-        <v>79.62</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:19:21</t>
+          <t>07:13:31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="F68" t="n">
-        <v>6.96</v>
+        <v>1.84</v>
       </c>
       <c r="G68" t="n">
-        <v>242.7</v>
+        <v>249.4</v>
       </c>
       <c r="H68" t="n">
-        <v>82.8</v>
+        <v>78.8</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-77.01000000000001</v>
+        <v>117.61</v>
       </c>
       <c r="K68" t="n">
-        <v>-75.34999999999999</v>
+        <v>-10.35</v>
       </c>
       <c r="L68" t="n">
-        <v>107.74</v>
+        <v>118.06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:20:27</t>
+          <t>07:15:44</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="F69" t="n">
-        <v>7.48</v>
+        <v>5.88</v>
       </c>
       <c r="G69" t="n">
-        <v>232.3</v>
+        <v>236.4</v>
       </c>
       <c r="H69" t="n">
-        <v>74.7</v>
+        <v>81.8</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>45.45</v>
+        <v>63.45</v>
       </c>
       <c r="K69" t="n">
-        <v>142.85</v>
+        <v>121.69</v>
       </c>
       <c r="L69" t="n">
-        <v>149.91</v>
+        <v>137.24</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:21:41</t>
+          <t>07:17:14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="F70" t="n">
-        <v>7.38</v>
+        <v>6.02</v>
       </c>
       <c r="G70" t="n">
-        <v>248.5</v>
+        <v>252.7</v>
       </c>
       <c r="H70" t="n">
-        <v>81.7</v>
+        <v>92.3</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-184.51</v>
+        <v>55.48</v>
       </c>
       <c r="K70" t="n">
-        <v>-37.6</v>
+        <v>123.13</v>
       </c>
       <c r="L70" t="n">
-        <v>188.3</v>
+        <v>135.05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:25:59</t>
+          <t>07:21:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="F71" t="n">
-        <v>6.99</v>
+        <v>5.26</v>
       </c>
       <c r="G71" t="n">
-        <v>243.7</v>
+        <v>251.8</v>
       </c>
       <c r="H71" t="n">
-        <v>80.5</v>
+        <v>80.8</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-149.94</v>
+        <v>-255.56</v>
       </c>
       <c r="K71" t="n">
-        <v>57.54</v>
+        <v>37.3</v>
       </c>
       <c r="L71" t="n">
-        <v>160.6</v>
+        <v>258.27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:27:36</t>
+          <t>07:23:24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.22</v>
+        <v>0.92</v>
       </c>
       <c r="F72" t="n">
-        <v>6.65</v>
+        <v>8.16</v>
       </c>
       <c r="G72" t="n">
-        <v>251.4</v>
+        <v>250.9</v>
       </c>
       <c r="H72" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-6.09</v>
+        <v>358.9</v>
       </c>
       <c r="K72" t="n">
-        <v>286.76</v>
+        <v>-99.84</v>
       </c>
       <c r="L72" t="n">
-        <v>286.82</v>
+        <v>372.53</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:29:12</t>
+          <t>07:25:19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.68</v>
+        <v>3.21</v>
       </c>
       <c r="F73" t="n">
-        <v>7.65</v>
+        <v>8.16</v>
       </c>
       <c r="G73" t="n">
-        <v>231.7</v>
+        <v>253.9</v>
       </c>
       <c r="H73" t="n">
-        <v>83.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-53.26</v>
+        <v>-119.45</v>
       </c>
       <c r="K73" t="n">
-        <v>-9.41</v>
+        <v>123.68</v>
       </c>
       <c r="L73" t="n">
-        <v>54.09</v>
+        <v>171.94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:39:38</t>
+          <t>07:36:42</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="F74" t="n">
-        <v>6.28</v>
+        <v>7.22</v>
       </c>
       <c r="G74" t="n">
-        <v>245.2</v>
+        <v>239.9</v>
       </c>
       <c r="H74" t="n">
-        <v>73.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I74" t="n">
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>43.48</v>
+        <v>38.08</v>
       </c>
       <c r="K74" t="n">
-        <v>21.23</v>
+        <v>-57.4</v>
       </c>
       <c r="L74" t="n">
-        <v>48.39</v>
+        <v>68.88</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:41:25</t>
+          <t>07:38:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.64</v>
+        <v>3.13</v>
       </c>
       <c r="F75" t="n">
-        <v>6.92</v>
+        <v>8.16</v>
       </c>
       <c r="G75" t="n">
-        <v>245.8</v>
+        <v>243</v>
       </c>
       <c r="H75" t="n">
-        <v>78.3</v>
+        <v>82.5</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.55</v>
+        <v>-39.43</v>
       </c>
       <c r="K75" t="n">
-        <v>60.19</v>
+        <v>-95.04000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>60.24</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:44:03</t>
+          <t>07:40:46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="F76" t="n">
-        <v>7.32</v>
+        <v>3.04</v>
       </c>
       <c r="G76" t="n">
-        <v>242.3</v>
+        <v>252.4</v>
       </c>
       <c r="H76" t="n">
-        <v>83.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>30.63</v>
+        <v>59.97</v>
       </c>
       <c r="K76" t="n">
-        <v>-18.62</v>
+        <v>-21.85</v>
       </c>
       <c r="L76" t="n">
-        <v>35.85</v>
+        <v>63.83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:47:51</t>
+          <t>07:46:56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="F77" t="n">
-        <v>7.01</v>
+        <v>7.88</v>
       </c>
       <c r="G77" t="n">
-        <v>232.7</v>
+        <v>265.2</v>
       </c>
       <c r="H77" t="n">
-        <v>84.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>32.84</v>
+        <v>-40.11</v>
       </c>
       <c r="K77" t="n">
-        <v>-70.81999999999999</v>
+        <v>73.09</v>
       </c>
       <c r="L77" t="n">
-        <v>78.06</v>
+        <v>83.37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:49:36</t>
+          <t>07:48:21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="F78" t="n">
-        <v>6.77</v>
+        <v>6.08</v>
       </c>
       <c r="G78" t="n">
-        <v>253.4</v>
+        <v>227.5</v>
       </c>
       <c r="H78" t="n">
-        <v>80.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>51.51</v>
+        <v>-88.87</v>
       </c>
       <c r="K78" t="n">
-        <v>-35.16</v>
+        <v>-44.41</v>
       </c>
       <c r="L78" t="n">
-        <v>62.36</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:51:21</t>
+          <t>07:49:08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="F79" t="n">
-        <v>6.76</v>
+        <v>6.82</v>
       </c>
       <c r="G79" t="n">
-        <v>261.3</v>
+        <v>247.8</v>
       </c>
       <c r="H79" t="n">
-        <v>75.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-64.92</v>
+        <v>90.41</v>
       </c>
       <c r="K79" t="n">
-        <v>2.09</v>
+        <v>-44.28</v>
       </c>
       <c r="L79" t="n">
-        <v>64.95</v>
+        <v>100.67</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:56:04</t>
+          <t>07:53:14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="F80" t="n">
-        <v>6.9</v>
+        <v>8.16</v>
       </c>
       <c r="G80" t="n">
-        <v>238.6</v>
+        <v>217.9</v>
       </c>
       <c r="H80" t="n">
-        <v>92</v>
+        <v>84.8</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>107.92</v>
+        <v>94.05</v>
       </c>
       <c r="K80" t="n">
-        <v>67.02</v>
+        <v>76.12</v>
       </c>
       <c r="L80" t="n">
-        <v>127.04</v>
+        <v>121</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:58:09</t>
+          <t>07:55:08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="F81" t="n">
-        <v>6.78</v>
+        <v>1.44</v>
       </c>
       <c r="G81" t="n">
-        <v>229.5</v>
+        <v>251.6</v>
       </c>
       <c r="H81" t="n">
-        <v>84.3</v>
+        <v>73.2</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>56.11</v>
+        <v>-55.41</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.01</v>
+        <v>51.12</v>
       </c>
       <c r="L81" t="n">
-        <v>67.22</v>
+        <v>75.39</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:00:07</t>
+          <t>07:56:33</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.77</v>
+        <v>1.37</v>
       </c>
       <c r="F82" t="n">
-        <v>7.78</v>
+        <v>3.83</v>
       </c>
       <c r="G82" t="n">
-        <v>232.8</v>
+        <v>229.5</v>
       </c>
       <c r="H82" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>102.6</v>
+        <v>-42.86</v>
       </c>
       <c r="K82" t="n">
-        <v>120.26</v>
+        <v>-61.28</v>
       </c>
       <c r="L82" t="n">
-        <v>158.08</v>
+        <v>74.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:06:18</t>
+          <t>08:02:22</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="F83" t="n">
-        <v>7.47</v>
+        <v>8.16</v>
       </c>
       <c r="G83" t="n">
-        <v>251.4</v>
+        <v>244.2</v>
       </c>
       <c r="H83" t="n">
-        <v>79.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-25.15</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-184.81</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>186.52</v>
+        <v>129.29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:07:42</t>
+          <t>08:03:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="F84" t="n">
-        <v>6.91</v>
+        <v>3.04</v>
       </c>
       <c r="G84" t="n">
-        <v>252.1</v>
+        <v>241</v>
       </c>
       <c r="H84" t="n">
-        <v>85.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-72.36</v>
+        <v>-23.82</v>
       </c>
       <c r="K84" t="n">
-        <v>60.1</v>
+        <v>95.62</v>
       </c>
       <c r="L84" t="n">
-        <v>94.06</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:08:30</t>
+          <t>08:05:37</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="F85" t="n">
-        <v>7.02</v>
+        <v>1.99</v>
       </c>
       <c r="G85" t="n">
-        <v>241.6</v>
+        <v>245.4</v>
       </c>
       <c r="H85" t="n">
-        <v>73.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-55.29</v>
+        <v>-53.28</v>
       </c>
       <c r="K85" t="n">
-        <v>150</v>
+        <v>91.63</v>
       </c>
       <c r="L85" t="n">
-        <v>159.86</v>
+        <v>105.99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:12:35</t>
+          <t>08:10:21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="F86" t="n">
-        <v>7.33</v>
+        <v>3.36</v>
       </c>
       <c r="G86" t="n">
-        <v>250.6</v>
+        <v>243.5</v>
       </c>
       <c r="H86" t="n">
-        <v>81.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>84.34999999999999</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>-233.52</v>
+        <v>149.28</v>
       </c>
       <c r="L86" t="n">
-        <v>248.28</v>
+        <v>165.41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:14:29</t>
+          <t>08:12:13</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="F87" t="n">
-        <v>7.33</v>
+        <v>8.16</v>
       </c>
       <c r="G87" t="n">
-        <v>242.8</v>
+        <v>243.3</v>
       </c>
       <c r="H87" t="n">
-        <v>83</v>
+        <v>77.3</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-8.4</v>
+        <v>296.27</v>
       </c>
       <c r="K87" t="n">
-        <v>-205.19</v>
+        <v>-166.94</v>
       </c>
       <c r="L87" t="n">
-        <v>205.36</v>
+        <v>340.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:15:55</t>
+          <t>08:14:16</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="F88" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="G88" t="n">
-        <v>245.4</v>
+        <v>249.4</v>
       </c>
       <c r="H88" t="n">
-        <v>84.3</v>
+        <v>79.3</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>157.77</v>
+        <v>-115.29</v>
       </c>
       <c r="K88" t="n">
-        <v>37.44</v>
+        <v>-148.93</v>
       </c>
       <c r="L88" t="n">
-        <v>162.15</v>
+        <v>188.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-14.29</v>
+        <v>-14</v>
       </c>
       <c r="K14" t="n">
-        <v>80.45999999999999</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>81.72</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>41.07</v>
+        <v>42.65</v>
       </c>
       <c r="K15" t="n">
-        <v>58.34</v>
+        <v>60.58</v>
       </c>
       <c r="L15" t="n">
-        <v>71.34999999999999</v>
+        <v>74.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-29.91</v>
+        <v>-29.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.75</v>
+        <v>-2.69</v>
       </c>
       <c r="L16" t="n">
-        <v>30.04</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-46.17</v>
+        <v>-47.95</v>
       </c>
       <c r="K17" t="n">
-        <v>42.96</v>
+        <v>44.61</v>
       </c>
       <c r="L17" t="n">
-        <v>63.07</v>
+        <v>65.48999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>45.05</v>
+        <v>42.18</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.72</v>
+        <v>-10.97</v>
       </c>
       <c r="L18" t="n">
-        <v>46.55</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-51</v>
+        <v>-48.87</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.03</v>
+        <v>-32.62</v>
       </c>
       <c r="L19" t="n">
-        <v>61.31</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-83.48999999999999</v>
+        <v>-81.78</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.03</v>
+        <v>-104.85</v>
       </c>
       <c r="L20" t="n">
-        <v>135.74</v>
+        <v>132.97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.12</v>
+        <v>-69.45999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>106.93</v>
+        <v>109.03</v>
       </c>
       <c r="L21" t="n">
-        <v>126.79</v>
+        <v>129.27</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-24.51</v>
+        <v>-22.95</v>
       </c>
       <c r="K22" t="n">
-        <v>-87.42</v>
+        <v>-81.84</v>
       </c>
       <c r="L22" t="n">
-        <v>90.8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>22</v>
       </c>
       <c r="J23" t="n">
-        <v>-150.63</v>
+        <v>-156.42</v>
       </c>
       <c r="K23" t="n">
-        <v>-157.96</v>
+        <v>-164.03</v>
       </c>
       <c r="L23" t="n">
-        <v>218.26</v>
+        <v>226.66</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>131.85</v>
+        <v>123.43</v>
       </c>
       <c r="K24" t="n">
-        <v>-14.12</v>
+        <v>-13.22</v>
       </c>
       <c r="L24" t="n">
-        <v>132.6</v>
+        <v>124.14</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>88.64</v>
+        <v>93.66</v>
       </c>
       <c r="K25" t="n">
-        <v>-90.41</v>
+        <v>-95.52</v>
       </c>
       <c r="L25" t="n">
-        <v>126.61</v>
+        <v>133.78</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-75.04000000000001</v>
+        <v>-79.29000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-121.01</v>
+        <v>-127.86</v>
       </c>
       <c r="L26" t="n">
-        <v>142.39</v>
+        <v>150.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>147.32</v>
+        <v>155.66</v>
       </c>
       <c r="K27" t="n">
-        <v>20.05</v>
+        <v>21.18</v>
       </c>
       <c r="L27" t="n">
-        <v>148.68</v>
+        <v>157.09</v>
       </c>
     </row>
     <row r="28">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.92</v>
+        <v>-17.56</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.08</v>
+        <v>-37.31</v>
       </c>
       <c r="L31" t="n">
-        <v>42.09</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-21.75</v>
+        <v>-21.3</v>
       </c>
       <c r="K32" t="n">
-        <v>-78.26000000000001</v>
+        <v>-76.67</v>
       </c>
       <c r="L32" t="n">
-        <v>81.23</v>
+        <v>79.56999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-85.94</v>
+        <v>-89.25</v>
       </c>
       <c r="K33" t="n">
-        <v>39.11</v>
+        <v>40.62</v>
       </c>
       <c r="L33" t="n">
-        <v>94.43000000000001</v>
+        <v>98.06</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>12.68</v>
+        <v>12.42</v>
       </c>
       <c r="K34" t="n">
-        <v>74.29000000000001</v>
+        <v>72.78</v>
       </c>
       <c r="L34" t="n">
-        <v>75.37</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>48.2</v>
+        <v>45.13</v>
       </c>
       <c r="K35" t="n">
-        <v>19.67</v>
+        <v>18.42</v>
       </c>
       <c r="L35" t="n">
-        <v>52.06</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="36">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.53</v>
+        <v>-5.18</v>
       </c>
       <c r="K37" t="n">
-        <v>-75.63</v>
+        <v>-70.8</v>
       </c>
       <c r="L37" t="n">
-        <v>75.83</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-160.55</v>
+        <v>-157.28</v>
       </c>
       <c r="K38" t="n">
-        <v>134.85</v>
+        <v>132.1</v>
       </c>
       <c r="L38" t="n">
-        <v>209.67</v>
+        <v>205.39</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-95.81999999999999</v>
+        <v>-89.7</v>
       </c>
       <c r="K39" t="n">
-        <v>-74.73</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>121.52</v>
+        <v>113.76</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-99.89</v>
+        <v>-95.73</v>
       </c>
       <c r="K40" t="n">
-        <v>149.37</v>
+        <v>143.15</v>
       </c>
       <c r="L40" t="n">
-        <v>179.7</v>
+        <v>172.21</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-169.93</v>
+        <v>-179.55</v>
       </c>
       <c r="K41" t="n">
-        <v>90.88</v>
+        <v>96.02</v>
       </c>
       <c r="L41" t="n">
-        <v>192.7</v>
+        <v>203.61</v>
       </c>
     </row>
     <row r="42">
@@ -1858,13 +1858,13 @@
         <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>132.14</v>
+        <v>126.64</v>
       </c>
       <c r="K43" t="n">
-        <v>-147.87</v>
+        <v>-141.71</v>
       </c>
       <c r="L43" t="n">
-        <v>198.31</v>
+        <v>190.05</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-14.6</v>
+        <v>-13.67</v>
       </c>
       <c r="K44" t="n">
-        <v>64.12</v>
+        <v>60.03</v>
       </c>
       <c r="L44" t="n">
-        <v>65.76000000000001</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="45">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="K46" t="n">
-        <v>-41.45</v>
+        <v>-39.72</v>
       </c>
       <c r="L46" t="n">
-        <v>42.38</v>
+        <v>40.62</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-53.08</v>
+        <v>-56.09</v>
       </c>
       <c r="K47" t="n">
-        <v>61.35</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>81.12</v>
+        <v>85.72</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-119.63</v>
+        <v>-124.23</v>
       </c>
       <c r="K48" t="n">
-        <v>6.41</v>
+        <v>6.66</v>
       </c>
       <c r="L48" t="n">
-        <v>119.8</v>
+        <v>124.41</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-44.68</v>
+        <v>-47.21</v>
       </c>
       <c r="K49" t="n">
-        <v>-71.28</v>
+        <v>-75.31</v>
       </c>
       <c r="L49" t="n">
-        <v>84.12</v>
+        <v>88.88</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>110.3</v>
+        <v>105.71</v>
       </c>
       <c r="K50" t="n">
-        <v>28.32</v>
+        <v>27.14</v>
       </c>
       <c r="L50" t="n">
-        <v>113.88</v>
+        <v>109.14</v>
       </c>
     </row>
     <row r="51">
@@ -2236,13 +2236,13 @@
         <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-28.4</v>
+        <v>-29.49</v>
       </c>
       <c r="K52" t="n">
-        <v>-106.97</v>
+        <v>-111.08</v>
       </c>
       <c r="L52" t="n">
-        <v>110.67</v>
+        <v>114.93</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>175.1</v>
+        <v>163.92</v>
       </c>
       <c r="K53" t="n">
-        <v>-25.14</v>
+        <v>-23.53</v>
       </c>
       <c r="L53" t="n">
-        <v>176.9</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-119.63</v>
+        <v>-117.19</v>
       </c>
       <c r="K54" t="n">
-        <v>-100.45</v>
+        <v>-98.40000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>156.21</v>
+        <v>153.02</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>186.72</v>
+        <v>197.29</v>
       </c>
       <c r="K55" t="n">
-        <v>-38.65</v>
+        <v>-40.83</v>
       </c>
       <c r="L55" t="n">
-        <v>190.68</v>
+        <v>201.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-21.04</v>
+        <v>-20.16</v>
       </c>
       <c r="K56" t="n">
-        <v>-148.14</v>
+        <v>-141.97</v>
       </c>
       <c r="L56" t="n">
-        <v>149.62</v>
+        <v>143.39</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-91.28</v>
+        <v>-89.42</v>
       </c>
       <c r="K57" t="n">
-        <v>158.91</v>
+        <v>155.67</v>
       </c>
       <c r="L57" t="n">
-        <v>183.26</v>
+        <v>179.52</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-107.8</v>
+        <v>-100.92</v>
       </c>
       <c r="K58" t="n">
-        <v>219.35</v>
+        <v>205.35</v>
       </c>
       <c r="L58" t="n">
-        <v>244.41</v>
+        <v>228.81</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.35</v>
+        <v>-7.63</v>
       </c>
       <c r="K59" t="n">
-        <v>5.04</v>
+        <v>5.23</v>
       </c>
       <c r="L59" t="n">
-        <v>8.91</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.95</v>
+        <v>-4.17</v>
       </c>
       <c r="K60" t="n">
-        <v>62.86</v>
+        <v>66.42</v>
       </c>
       <c r="L60" t="n">
-        <v>62.99</v>
+        <v>66.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>48.15</v>
+        <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="L61" t="n">
-        <v>48.26</v>
+        <v>50.11</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-84.97</v>
+        <v>-86.63</v>
       </c>
       <c r="K62" t="n">
-        <v>40.68</v>
+        <v>41.48</v>
       </c>
       <c r="L62" t="n">
-        <v>94.2</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>29.14</v>
+        <v>27.93</v>
       </c>
       <c r="K63" t="n">
-        <v>-60.67</v>
+        <v>-58.14</v>
       </c>
       <c r="L63" t="n">
-        <v>67.3</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>11.59</v>
+        <v>12.03</v>
       </c>
       <c r="K64" t="n">
-        <v>87.95</v>
+        <v>91.34</v>
       </c>
       <c r="L64" t="n">
-        <v>88.70999999999999</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-98.34999999999999</v>
+        <v>-100.28</v>
       </c>
       <c r="K65" t="n">
-        <v>-62.18</v>
+        <v>-63.4</v>
       </c>
       <c r="L65" t="n">
-        <v>116.36</v>
+        <v>118.64</v>
       </c>
     </row>
     <row r="66">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>117.61</v>
+        <v>122.13</v>
       </c>
       <c r="K68" t="n">
-        <v>-10.35</v>
+        <v>-10.74</v>
       </c>
       <c r="L68" t="n">
-        <v>118.06</v>
+        <v>122.6</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>63.45</v>
+        <v>59.4</v>
       </c>
       <c r="K69" t="n">
-        <v>121.69</v>
+        <v>113.92</v>
       </c>
       <c r="L69" t="n">
-        <v>137.24</v>
+        <v>128.48</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>55.48</v>
+        <v>53.16</v>
       </c>
       <c r="K70" t="n">
-        <v>123.13</v>
+        <v>118</v>
       </c>
       <c r="L70" t="n">
-        <v>135.05</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>-255.56</v>
+        <v>-239.25</v>
       </c>
       <c r="K71" t="n">
-        <v>37.3</v>
+        <v>34.92</v>
       </c>
       <c r="L71" t="n">
-        <v>258.27</v>
+        <v>241.79</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>358.9</v>
+        <v>335.99</v>
       </c>
       <c r="K72" t="n">
-        <v>-99.84</v>
+        <v>-93.45999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>372.53</v>
+        <v>348.75</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-119.45</v>
+        <v>-114.47</v>
       </c>
       <c r="K73" t="n">
-        <v>123.68</v>
+        <v>118.52</v>
       </c>
       <c r="L73" t="n">
-        <v>171.94</v>
+        <v>164.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>38.08</v>
+        <v>40.23</v>
       </c>
       <c r="K74" t="n">
-        <v>-57.4</v>
+        <v>-60.65</v>
       </c>
       <c r="L74" t="n">
-        <v>68.88</v>
+        <v>72.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-39.43</v>
+        <v>-41.66</v>
       </c>
       <c r="K75" t="n">
-        <v>-95.04000000000001</v>
+        <v>-100.42</v>
       </c>
       <c r="L75" t="n">
-        <v>102.89</v>
+        <v>108.72</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>59.97</v>
+        <v>58.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-21.85</v>
+        <v>-21.41</v>
       </c>
       <c r="L76" t="n">
-        <v>63.83</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="77">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>-88.87</v>
+        <v>-93.90000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-44.41</v>
+        <v>-46.93</v>
       </c>
       <c r="L78" t="n">
-        <v>99.34999999999999</v>
+        <v>104.98</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>90.41</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-44.28</v>
+        <v>-45.15</v>
       </c>
       <c r="L79" t="n">
-        <v>100.67</v>
+        <v>102.65</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>94.05</v>
+        <v>88.05</v>
       </c>
       <c r="K80" t="n">
-        <v>76.12</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>121</v>
+        <v>113.27</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-55.41</v>
+        <v>-56.49</v>
       </c>
       <c r="K81" t="n">
-        <v>51.12</v>
+        <v>52.13</v>
       </c>
       <c r="L81" t="n">
-        <v>75.39</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="82">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>98.09999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="K83" t="n">
-        <v>84.20999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="L83" t="n">
-        <v>129.29</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-23.82</v>
+        <v>-23.34</v>
       </c>
       <c r="K84" t="n">
-        <v>95.62</v>
+        <v>93.67</v>
       </c>
       <c r="L84" t="n">
-        <v>98.54000000000001</v>
+        <v>96.53</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-53.28</v>
+        <v>-49.88</v>
       </c>
       <c r="K85" t="n">
-        <v>91.63</v>
+        <v>85.78</v>
       </c>
       <c r="L85" t="n">
-        <v>105.99</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>71.26000000000001</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>149.28</v>
+        <v>157.73</v>
       </c>
       <c r="L86" t="n">
-        <v>165.41</v>
+        <v>174.78</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>296.27</v>
+        <v>283.93</v>
       </c>
       <c r="K87" t="n">
-        <v>-166.94</v>
+        <v>-159.98</v>
       </c>
       <c r="L87" t="n">
-        <v>340.07</v>
+        <v>325.9</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-115.29</v>
+        <v>-110.49</v>
       </c>
       <c r="K88" t="n">
-        <v>-148.93</v>
+        <v>-142.73</v>
       </c>
       <c r="L88" t="n">
-        <v>188.34</v>
+        <v>180.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="F14" t="n">
-        <v>8.16</v>
+        <v>5.05</v>
       </c>
       <c r="G14" t="n">
-        <v>244.7</v>
+        <v>245</v>
       </c>
       <c r="H14" t="n">
-        <v>76.5</v>
+        <v>79.5</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>-14</v>
+        <v>-17.6</v>
       </c>
       <c r="K14" t="n">
-        <v>78.81999999999999</v>
+        <v>-21.41</v>
       </c>
       <c r="L14" t="n">
-        <v>80.05</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:32:59</t>
+          <t>04:34:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.42</v>
+        <v>1.18</v>
       </c>
       <c r="F15" t="n">
         <v>8.16</v>
       </c>
       <c r="G15" t="n">
-        <v>242.2</v>
+        <v>240.2</v>
       </c>
       <c r="H15" t="n">
-        <v>78.90000000000001</v>
+        <v>36.8</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>42.65</v>
+        <v>7.45</v>
       </c>
       <c r="K15" t="n">
-        <v>60.58</v>
+        <v>19.99</v>
       </c>
       <c r="L15" t="n">
-        <v>74.09</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:27</t>
+          <t>04:35:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.88</v>
+        <v>1.24</v>
       </c>
       <c r="F16" t="n">
-        <v>1.18</v>
+        <v>8.16</v>
       </c>
       <c r="G16" t="n">
-        <v>243.8</v>
+        <v>227.9</v>
       </c>
       <c r="H16" t="n">
-        <v>85.90000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-29.3</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.69</v>
+        <v>22.57</v>
       </c>
       <c r="L16" t="n">
-        <v>29.43</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:00</t>
+          <t>04:40:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.25</v>
+        <v>0.97</v>
       </c>
       <c r="F17" t="n">
-        <v>5.37</v>
+        <v>4.82</v>
       </c>
       <c r="G17" t="n">
-        <v>236.1</v>
+        <v>239.8</v>
       </c>
       <c r="H17" t="n">
-        <v>75.8</v>
+        <v>29.3</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>-47.95</v>
+        <v>40.58</v>
       </c>
       <c r="K17" t="n">
-        <v>44.61</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>65.48999999999999</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:26</t>
+          <t>04:42:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="F18" t="n">
-        <v>1.54</v>
+        <v>6.54</v>
       </c>
       <c r="G18" t="n">
-        <v>242.7</v>
+        <v>234.3</v>
       </c>
       <c r="H18" t="n">
-        <v>82.59999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>42.18</v>
+        <v>-58.2</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.97</v>
+        <v>1.73</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58</v>
+        <v>58.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:44:32</t>
+          <t>04:43:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="F19" t="n">
-        <v>8.06</v>
+        <v>4.61</v>
       </c>
       <c r="G19" t="n">
-        <v>242.4</v>
+        <v>257.1</v>
       </c>
       <c r="H19" t="n">
-        <v>83.8</v>
+        <v>74</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-48.87</v>
+        <v>23.12</v>
       </c>
       <c r="K19" t="n">
-        <v>-32.62</v>
+        <v>-35.96</v>
       </c>
       <c r="L19" t="n">
-        <v>58.75</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:48:53</t>
+          <t>04:47:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="F20" t="n">
         <v>8.16</v>
       </c>
       <c r="G20" t="n">
-        <v>247.6</v>
+        <v>242.2</v>
       </c>
       <c r="H20" t="n">
-        <v>78.40000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>-81.78</v>
+        <v>2.72</v>
       </c>
       <c r="K20" t="n">
-        <v>-104.85</v>
+        <v>49.44</v>
       </c>
       <c r="L20" t="n">
-        <v>132.97</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:51:10</t>
+          <t>04:49:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>8.16</v>
       </c>
       <c r="G21" t="n">
-        <v>242.9</v>
+        <v>257.5</v>
       </c>
       <c r="H21" t="n">
-        <v>83</v>
+        <v>80.2</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>-69.45999999999999</v>
+        <v>24.42</v>
       </c>
       <c r="K21" t="n">
-        <v>109.03</v>
+        <v>-3.37</v>
       </c>
       <c r="L21" t="n">
-        <v>129.27</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:52:16</t>
+          <t>04:51:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.87</v>
+        <v>1.27</v>
       </c>
       <c r="F22" t="n">
-        <v>4.1</v>
+        <v>4.37</v>
       </c>
       <c r="G22" t="n">
-        <v>242.3</v>
+        <v>233.8</v>
       </c>
       <c r="H22" t="n">
-        <v>76.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.95</v>
+        <v>-52.27</v>
       </c>
       <c r="K22" t="n">
-        <v>-81.84</v>
+        <v>-7.23</v>
       </c>
       <c r="L22" t="n">
-        <v>85</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:55:35</t>
+          <t>04:56:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="F23" t="n">
-        <v>8.16</v>
+        <v>1.44</v>
       </c>
       <c r="G23" t="n">
-        <v>229.1</v>
+        <v>246.6</v>
       </c>
       <c r="H23" t="n">
-        <v>76.8</v>
+        <v>59.1</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>-156.42</v>
+        <v>80.31</v>
       </c>
       <c r="K23" t="n">
-        <v>-164.03</v>
+        <v>-114.47</v>
       </c>
       <c r="L23" t="n">
-        <v>226.66</v>
+        <v>139.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:57:28</t>
+          <t>04:58:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="F24" t="n">
-        <v>8.16</v>
+        <v>2.52</v>
       </c>
       <c r="G24" t="n">
-        <v>242.2</v>
+        <v>222.1</v>
       </c>
       <c r="H24" t="n">
-        <v>81.3</v>
+        <v>58.4</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>123.43</v>
+        <v>46.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-13.22</v>
+        <v>72.89</v>
       </c>
       <c r="L24" t="n">
-        <v>124.14</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:58:59</t>
+          <t>04:59:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="F25" t="n">
-        <v>1.37</v>
+        <v>8.16</v>
       </c>
       <c r="G25" t="n">
-        <v>245.4</v>
+        <v>251.3</v>
       </c>
       <c r="H25" t="n">
-        <v>76.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>93.66</v>
+        <v>-114.16</v>
       </c>
       <c r="K25" t="n">
-        <v>-95.52</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>133.78</v>
+        <v>134.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:03:32</t>
+          <t>05:04:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.36</v>
+        <v>0.82</v>
       </c>
       <c r="F26" t="n">
-        <v>3.77</v>
+        <v>1.12</v>
       </c>
       <c r="G26" t="n">
-        <v>242.1</v>
+        <v>244.1</v>
       </c>
       <c r="H26" t="n">
-        <v>82.2</v>
+        <v>25.2</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>-79.29000000000001</v>
+        <v>-151.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-127.86</v>
+        <v>-3.74</v>
       </c>
       <c r="L26" t="n">
-        <v>150.45</v>
+        <v>151.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:05:46</t>
+          <t>05:05:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="F27" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="G27" t="n">
-        <v>234.4</v>
+        <v>250.4</v>
       </c>
       <c r="H27" t="n">
-        <v>77.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>155.66</v>
+        <v>-137.79</v>
       </c>
       <c r="K27" t="n">
-        <v>21.18</v>
+        <v>-85.05</v>
       </c>
       <c r="L27" t="n">
-        <v>157.09</v>
+        <v>161.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:07:41</t>
+          <t>05:07:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.12</v>
+        <v>0.92</v>
       </c>
       <c r="F28" t="n">
-        <v>7.57</v>
+        <v>6.57</v>
       </c>
       <c r="G28" t="n">
-        <v>249</v>
+        <v>241.9</v>
       </c>
       <c r="H28" t="n">
-        <v>71.09999999999999</v>
+        <v>42</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-276</v>
+        <v>131.56</v>
       </c>
       <c r="K28" t="n">
-        <v>-100.85</v>
+        <v>28.35</v>
       </c>
       <c r="L28" t="n">
-        <v>293.85</v>
+        <v>134.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:18:29</t>
+          <t>05:19:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="F29" t="n">
-        <v>8.16</v>
+        <v>7.03</v>
       </c>
       <c r="G29" t="n">
-        <v>243.9</v>
+        <v>229.4</v>
       </c>
       <c r="H29" t="n">
-        <v>73.3</v>
+        <v>84.3</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-52.26</v>
+        <v>-11.49</v>
       </c>
       <c r="K29" t="n">
-        <v>9.050000000000001</v>
+        <v>-25.18</v>
       </c>
       <c r="L29" t="n">
-        <v>53.04</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:20:48</t>
+          <t>05:21:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="F30" t="n">
-        <v>1.45</v>
+        <v>5.02</v>
       </c>
       <c r="G30" t="n">
-        <v>235.6</v>
+        <v>240.1</v>
       </c>
       <c r="H30" t="n">
-        <v>81</v>
+        <v>23.6</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>10.41</v>
+        <v>29.4</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.08</v>
+        <v>15.43</v>
       </c>
       <c r="L30" t="n">
-        <v>41.41</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:23:11</t>
+          <t>05:23:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="F31" t="n">
-        <v>4.39</v>
+        <v>3.41</v>
       </c>
       <c r="G31" t="n">
-        <v>236.5</v>
+        <v>244.6</v>
       </c>
       <c r="H31" t="n">
-        <v>80.09999999999999</v>
+        <v>51.7</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.56</v>
+        <v>13.08</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.31</v>
+        <v>-18.83</v>
       </c>
       <c r="L31" t="n">
-        <v>41.23</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:27:30</t>
+          <t>05:28:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="F32" t="n">
-        <v>6.94</v>
+        <v>8.16</v>
       </c>
       <c r="G32" t="n">
-        <v>234.4</v>
+        <v>242.1</v>
       </c>
       <c r="H32" t="n">
-        <v>81.3</v>
+        <v>61.6</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-21.3</v>
+        <v>-23.67</v>
       </c>
       <c r="K32" t="n">
-        <v>-76.67</v>
+        <v>-28.24</v>
       </c>
       <c r="L32" t="n">
-        <v>79.56999999999999</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:29:59</t>
+          <t>05:30:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.35</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>5.68</v>
+        <v>3.86</v>
       </c>
       <c r="G33" t="n">
-        <v>237.3</v>
+        <v>238.6</v>
       </c>
       <c r="H33" t="n">
-        <v>92.5</v>
+        <v>82.7</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-89.25</v>
+        <v>3.69</v>
       </c>
       <c r="K33" t="n">
-        <v>40.62</v>
+        <v>47.63</v>
       </c>
       <c r="L33" t="n">
-        <v>98.06</v>
+        <v>47.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:31:51</t>
+          <t>05:31:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="F34" t="n">
-        <v>8.16</v>
+        <v>1.49</v>
       </c>
       <c r="G34" t="n">
-        <v>241.1</v>
+        <v>231.7</v>
       </c>
       <c r="H34" t="n">
-        <v>83.7</v>
+        <v>61.5</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>12.42</v>
+        <v>11.35</v>
       </c>
       <c r="K34" t="n">
-        <v>72.78</v>
+        <v>48.62</v>
       </c>
       <c r="L34" t="n">
-        <v>73.83</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:38:04</t>
+          <t>05:36:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>6.39</v>
+        <v>6.02</v>
       </c>
       <c r="G35" t="n">
-        <v>249.6</v>
+        <v>237.2</v>
       </c>
       <c r="H35" t="n">
         <v>81.7</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>45.13</v>
+        <v>6.23</v>
       </c>
       <c r="K35" t="n">
-        <v>18.42</v>
+        <v>61.93</v>
       </c>
       <c r="L35" t="n">
-        <v>48.74</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:39:37</t>
+          <t>05:37:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="F36" t="n">
-        <v>8.16</v>
+        <v>1.6</v>
       </c>
       <c r="G36" t="n">
-        <v>245.7</v>
+        <v>243.9</v>
       </c>
       <c r="H36" t="n">
-        <v>77.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-26.24</v>
+        <v>-38.03</v>
       </c>
       <c r="K36" t="n">
-        <v>177.14</v>
+        <v>-55.5</v>
       </c>
       <c r="L36" t="n">
-        <v>179.07</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:41:52</t>
+          <t>05:39:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>4.94</v>
       </c>
       <c r="G37" t="n">
-        <v>234.9</v>
+        <v>249.6</v>
       </c>
       <c r="H37" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.18</v>
+        <v>-49.95</v>
       </c>
       <c r="K37" t="n">
-        <v>-70.8</v>
+        <v>-22.01</v>
       </c>
       <c r="L37" t="n">
-        <v>70.98999999999999</v>
+        <v>54.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:47:32</t>
+          <t>05:45:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.49</v>
+        <v>0.91</v>
       </c>
       <c r="F38" t="n">
         <v>8.16</v>
       </c>
       <c r="G38" t="n">
-        <v>228.1</v>
+        <v>251.3</v>
       </c>
       <c r="H38" t="n">
-        <v>75.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>-157.28</v>
+        <v>69.17</v>
       </c>
       <c r="K38" t="n">
-        <v>132.1</v>
+        <v>85.8</v>
       </c>
       <c r="L38" t="n">
-        <v>205.39</v>
+        <v>110.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:49:47</t>
+          <t>05:46:38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.54</v>
       </c>
       <c r="F39" t="n">
-        <v>6.1</v>
+        <v>5.16</v>
       </c>
       <c r="G39" t="n">
-        <v>258.9</v>
+        <v>243.2</v>
       </c>
       <c r="H39" t="n">
-        <v>74.59999999999999</v>
+        <v>47.6</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-89.7</v>
+        <v>78.62</v>
       </c>
       <c r="K39" t="n">
-        <v>-69.95999999999999</v>
+        <v>-100.94</v>
       </c>
       <c r="L39" t="n">
-        <v>113.76</v>
+        <v>127.94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:50:55</t>
+          <t>05:48:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="F40" t="n">
-        <v>4.79</v>
+        <v>5.35</v>
       </c>
       <c r="G40" t="n">
-        <v>240.8</v>
+        <v>240.7</v>
       </c>
       <c r="H40" t="n">
-        <v>79.40000000000001</v>
+        <v>21.8</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>-95.73</v>
+        <v>-42.15</v>
       </c>
       <c r="K40" t="n">
-        <v>143.15</v>
+        <v>-99.25</v>
       </c>
       <c r="L40" t="n">
-        <v>172.21</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:55:42</t>
+          <t>05:51:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="F41" t="n">
-        <v>2.07</v>
+        <v>6.42</v>
       </c>
       <c r="G41" t="n">
-        <v>234.8</v>
+        <v>243.1</v>
       </c>
       <c r="H41" t="n">
-        <v>77.2</v>
+        <v>57.9</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-179.55</v>
+        <v>1.38</v>
       </c>
       <c r="K41" t="n">
-        <v>96.02</v>
+        <v>-154.5</v>
       </c>
       <c r="L41" t="n">
-        <v>203.61</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:56:58</t>
+          <t>05:52:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="F42" t="n">
-        <v>4.49</v>
+        <v>4.95</v>
       </c>
       <c r="G42" t="n">
-        <v>244.3</v>
+        <v>248.1</v>
       </c>
       <c r="H42" t="n">
-        <v>84.7</v>
+        <v>38.3</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J42" t="n">
-        <v>-214</v>
+        <v>-84.67</v>
       </c>
       <c r="K42" t="n">
-        <v>-164.12</v>
+        <v>-125.21</v>
       </c>
       <c r="L42" t="n">
-        <v>269.69</v>
+        <v>151.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:58:52</t>
+          <t>05:54:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="F43" t="n">
-        <v>6.85</v>
+        <v>7.36</v>
       </c>
       <c r="G43" t="n">
-        <v>236</v>
+        <v>248.6</v>
       </c>
       <c r="H43" t="n">
-        <v>78.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>126.64</v>
+        <v>-67.55</v>
       </c>
       <c r="K43" t="n">
-        <v>-141.71</v>
+        <v>130</v>
       </c>
       <c r="L43" t="n">
-        <v>190.05</v>
+        <v>146.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:53</t>
+          <t>06:04:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="F44" t="n">
         <v>8.16</v>
       </c>
       <c r="G44" t="n">
-        <v>239.2</v>
+        <v>246.9</v>
       </c>
       <c r="H44" t="n">
-        <v>83.40000000000001</v>
+        <v>41.3</v>
       </c>
       <c r="I44" t="n">
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-13.67</v>
+        <v>25.8</v>
       </c>
       <c r="K44" t="n">
-        <v>60.03</v>
+        <v>14.73</v>
       </c>
       <c r="L44" t="n">
-        <v>61.56</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:08:09</t>
+          <t>06:05:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="F45" t="n">
-        <v>7.62</v>
+        <v>8.16</v>
       </c>
       <c r="G45" t="n">
-        <v>257.3</v>
+        <v>239.8</v>
       </c>
       <c r="H45" t="n">
-        <v>75</v>
+        <v>83.8</v>
       </c>
       <c r="I45" t="n">
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-61.08</v>
+        <v>-32.65</v>
       </c>
       <c r="K45" t="n">
-        <v>-32.44</v>
+        <v>-11</v>
       </c>
       <c r="L45" t="n">
-        <v>69.16</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:09:39</t>
+          <t>06:06:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F46" t="n">
-        <v>1.57</v>
+        <v>8.16</v>
       </c>
       <c r="G46" t="n">
-        <v>251.7</v>
+        <v>243.1</v>
       </c>
       <c r="H46" t="n">
-        <v>81.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.5</v>
+        <v>5.22</v>
       </c>
       <c r="K46" t="n">
-        <v>-39.72</v>
+        <v>-30.03</v>
       </c>
       <c r="L46" t="n">
-        <v>40.62</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:14:37</t>
+          <t>06:11:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="F47" t="n">
         <v>8.16</v>
       </c>
       <c r="G47" t="n">
-        <v>242.3</v>
+        <v>245</v>
       </c>
       <c r="H47" t="n">
-        <v>78.3</v>
+        <v>52.5</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J47" t="n">
-        <v>-56.09</v>
+        <v>-29.84</v>
       </c>
       <c r="K47" t="n">
-        <v>64.81999999999999</v>
+        <v>-29.39</v>
       </c>
       <c r="L47" t="n">
-        <v>85.72</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:16:17</t>
+          <t>06:11:56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="F48" t="n">
-        <v>6.86</v>
+        <v>7.19</v>
       </c>
       <c r="G48" t="n">
-        <v>248.4</v>
+        <v>249.3</v>
       </c>
       <c r="H48" t="n">
-        <v>76</v>
+        <v>55.1</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-124.23</v>
+        <v>-5.17</v>
       </c>
       <c r="K48" t="n">
-        <v>6.66</v>
+        <v>38.83</v>
       </c>
       <c r="L48" t="n">
-        <v>124.41</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:18:18</t>
+          <t>06:13:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F49" t="n">
-        <v>4.09</v>
+        <v>2.45</v>
       </c>
       <c r="G49" t="n">
-        <v>234.1</v>
+        <v>251.8</v>
       </c>
       <c r="H49" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-47.21</v>
+        <v>37.79</v>
       </c>
       <c r="K49" t="n">
-        <v>-75.31</v>
+        <v>12.42</v>
       </c>
       <c r="L49" t="n">
-        <v>88.88</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:23:16</t>
+          <t>06:17:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="F50" t="n">
-        <v>8.16</v>
+        <v>1.59</v>
       </c>
       <c r="G50" t="n">
-        <v>241.2</v>
+        <v>233.6</v>
       </c>
       <c r="H50" t="n">
-        <v>79.59999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J50" t="n">
-        <v>105.71</v>
+        <v>71.03</v>
       </c>
       <c r="K50" t="n">
-        <v>27.14</v>
+        <v>0.7</v>
       </c>
       <c r="L50" t="n">
-        <v>109.14</v>
+        <v>71.03</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:24:26</t>
+          <t>06:19:08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="F51" t="n">
-        <v>4.74</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>247.7</v>
+        <v>249.8</v>
       </c>
       <c r="H51" t="n">
-        <v>69.40000000000001</v>
+        <v>47.1</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>7.43</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-83.98999999999999</v>
+        <v>-12.49</v>
       </c>
       <c r="L51" t="n">
-        <v>84.31999999999999</v>
+        <v>70.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:25:42</t>
+          <t>06:20:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="F52" t="n">
-        <v>7.71</v>
+        <v>8.16</v>
       </c>
       <c r="G52" t="n">
-        <v>240.8</v>
+        <v>247.2</v>
       </c>
       <c r="H52" t="n">
-        <v>83.3</v>
+        <v>46.4</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>-29.49</v>
+        <v>-53.55</v>
       </c>
       <c r="K52" t="n">
-        <v>-111.08</v>
+        <v>15.56</v>
       </c>
       <c r="L52" t="n">
-        <v>114.93</v>
+        <v>55.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:30:52</t>
+          <t>06:25:10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="F53" t="n">
-        <v>7.94</v>
+        <v>2.26</v>
       </c>
       <c r="G53" t="n">
-        <v>226.5</v>
+        <v>263.5</v>
       </c>
       <c r="H53" t="n">
-        <v>76.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>163.92</v>
+        <v>-104.67</v>
       </c>
       <c r="K53" t="n">
-        <v>-23.53</v>
+        <v>14.88</v>
       </c>
       <c r="L53" t="n">
-        <v>165.6</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:32:12</t>
+          <t>06:27:23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="F54" t="n">
-        <v>8.16</v>
+        <v>5.88</v>
       </c>
       <c r="G54" t="n">
-        <v>237.6</v>
+        <v>233.4</v>
       </c>
       <c r="H54" t="n">
-        <v>77.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-117.19</v>
+        <v>63.63</v>
       </c>
       <c r="K54" t="n">
-        <v>-98.40000000000001</v>
+        <v>-58.35</v>
       </c>
       <c r="L54" t="n">
-        <v>153.02</v>
+        <v>86.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:33:11</t>
+          <t>06:28:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="F55" t="n">
-        <v>2.95</v>
+        <v>4.09</v>
       </c>
       <c r="G55" t="n">
-        <v>247.4</v>
+        <v>246.2</v>
       </c>
       <c r="H55" t="n">
-        <v>78.8</v>
+        <v>46</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>197.29</v>
+        <v>121.57</v>
       </c>
       <c r="K55" t="n">
-        <v>-40.83</v>
+        <v>3.5</v>
       </c>
       <c r="L55" t="n">
-        <v>201.47</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:36:43</t>
+          <t>06:32:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2392,31 +2392,31 @@
         <v>1.25</v>
       </c>
       <c r="F56" t="n">
-        <v>4.39</v>
+        <v>5.21</v>
       </c>
       <c r="G56" t="n">
-        <v>239.3</v>
+        <v>238.9</v>
       </c>
       <c r="H56" t="n">
-        <v>80.09999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-20.16</v>
+        <v>-121.56</v>
       </c>
       <c r="K56" t="n">
-        <v>-141.97</v>
+        <v>-43.1</v>
       </c>
       <c r="L56" t="n">
-        <v>143.39</v>
+        <v>128.97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:38:16</t>
+          <t>06:34:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="F57" t="n">
-        <v>4.58</v>
+        <v>5.58</v>
       </c>
       <c r="G57" t="n">
-        <v>232.9</v>
+        <v>236.4</v>
       </c>
       <c r="H57" t="n">
-        <v>72.3</v>
+        <v>85.5</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-89.42</v>
+        <v>113.7</v>
       </c>
       <c r="K57" t="n">
-        <v>155.67</v>
+        <v>-41.38</v>
       </c>
       <c r="L57" t="n">
-        <v>179.52</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:44</t>
+          <t>06:36:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="F58" t="n">
         <v>8.16</v>
       </c>
       <c r="G58" t="n">
-        <v>247.7</v>
+        <v>242.7</v>
       </c>
       <c r="H58" t="n">
-        <v>83.40000000000001</v>
+        <v>33.9</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>-100.92</v>
+        <v>-54.9</v>
       </c>
       <c r="K58" t="n">
-        <v>205.35</v>
+        <v>133.62</v>
       </c>
       <c r="L58" t="n">
-        <v>228.81</v>
+        <v>144.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:50:05</t>
+          <t>06:46:58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="F59" t="n">
-        <v>8.16</v>
+        <v>4.09</v>
       </c>
       <c r="G59" t="n">
-        <v>243.4</v>
+        <v>248.4</v>
       </c>
       <c r="H59" t="n">
-        <v>83</v>
+        <v>50.8</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.63</v>
+        <v>10.93</v>
       </c>
       <c r="K59" t="n">
-        <v>5.23</v>
+        <v>27.42</v>
       </c>
       <c r="L59" t="n">
-        <v>9.26</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:51:50</t>
+          <t>06:49:36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="F60" t="n">
-        <v>5.53</v>
+        <v>7.67</v>
       </c>
       <c r="G60" t="n">
-        <v>242.4</v>
+        <v>243.4</v>
       </c>
       <c r="H60" t="n">
-        <v>82.59999999999999</v>
+        <v>58.5</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.17</v>
+        <v>6.12</v>
       </c>
       <c r="K60" t="n">
-        <v>66.42</v>
+        <v>-28.84</v>
       </c>
       <c r="L60" t="n">
-        <v>66.55</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:53:52</t>
+          <t>06:51:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="F61" t="n">
-        <v>1.56</v>
+        <v>6.61</v>
       </c>
       <c r="G61" t="n">
-        <v>249.3</v>
+        <v>243.6</v>
       </c>
       <c r="H61" t="n">
-        <v>83.3</v>
+        <v>69.5</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>50</v>
+        <v>18.56</v>
       </c>
       <c r="K61" t="n">
-        <v>3.35</v>
+        <v>-12.87</v>
       </c>
       <c r="L61" t="n">
-        <v>50.11</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:58:23</t>
+          <t>06:56:33</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="F62" t="n">
-        <v>8.16</v>
+        <v>5.65</v>
       </c>
       <c r="G62" t="n">
-        <v>255.2</v>
+        <v>241.6</v>
       </c>
       <c r="H62" t="n">
-        <v>84.59999999999999</v>
+        <v>42.9</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>-86.63</v>
+        <v>-50.91</v>
       </c>
       <c r="K62" t="n">
-        <v>41.48</v>
+        <v>-3.94</v>
       </c>
       <c r="L62" t="n">
-        <v>96.05</v>
+        <v>51.06</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:59:28</t>
+          <t>06:58:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2689,28 +2689,28 @@
         <v>8.16</v>
       </c>
       <c r="G63" t="n">
-        <v>244.4</v>
+        <v>233.8</v>
       </c>
       <c r="H63" t="n">
-        <v>83.2</v>
+        <v>47.2</v>
       </c>
       <c r="I63" t="n">
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>27.93</v>
+        <v>6.72</v>
       </c>
       <c r="K63" t="n">
-        <v>-58.14</v>
+        <v>44.64</v>
       </c>
       <c r="L63" t="n">
-        <v>64.5</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:00:42</t>
+          <t>06:59:14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.41</v>
+        <v>0.99</v>
       </c>
       <c r="F64" t="n">
-        <v>8.16</v>
+        <v>2.24</v>
       </c>
       <c r="G64" t="n">
-        <v>250.1</v>
+        <v>244.7</v>
       </c>
       <c r="H64" t="n">
-        <v>80.3</v>
+        <v>36.6</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>12.03</v>
+        <v>-26.77</v>
       </c>
       <c r="K64" t="n">
-        <v>91.34</v>
+        <v>-43.87</v>
       </c>
       <c r="L64" t="n">
-        <v>92.13</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:05:00</t>
+          <t>07:04:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.79</v>
+        <v>2.88</v>
       </c>
       <c r="F65" t="n">
         <v>8.16</v>
       </c>
       <c r="G65" t="n">
-        <v>246.8</v>
+        <v>246.5</v>
       </c>
       <c r="H65" t="n">
-        <v>80.7</v>
+        <v>37.2</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-100.28</v>
+        <v>-100.64</v>
       </c>
       <c r="K65" t="n">
-        <v>-63.4</v>
+        <v>-23.8</v>
       </c>
       <c r="L65" t="n">
-        <v>118.64</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:06:38</t>
+          <t>07:06:05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="F66" t="n">
-        <v>5.99</v>
+        <v>5.65</v>
       </c>
       <c r="G66" t="n">
-        <v>238.1</v>
+        <v>230.5</v>
       </c>
       <c r="H66" t="n">
-        <v>79.3</v>
+        <v>59.4</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>64.13</v>
+        <v>24.19</v>
       </c>
       <c r="K66" t="n">
-        <v>-103.66</v>
+        <v>116.08</v>
       </c>
       <c r="L66" t="n">
-        <v>121.9</v>
+        <v>118.58</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:08:13</t>
+          <t>07:07:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="F67" t="n">
-        <v>1.41</v>
+        <v>4.39</v>
       </c>
       <c r="G67" t="n">
-        <v>255.6</v>
+        <v>237.6</v>
       </c>
       <c r="H67" t="n">
-        <v>87.2</v>
+        <v>21.2</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>17.85</v>
+        <v>-53.08</v>
       </c>
       <c r="K67" t="n">
-        <v>70.39</v>
+        <v>-25.34</v>
       </c>
       <c r="L67" t="n">
-        <v>72.62</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:13:31</t>
+          <t>07:10:43</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="F68" t="n">
-        <v>1.84</v>
+        <v>6.98</v>
       </c>
       <c r="G68" t="n">
-        <v>249.4</v>
+        <v>243.6</v>
       </c>
       <c r="H68" t="n">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>122.13</v>
+        <v>22.31</v>
       </c>
       <c r="K68" t="n">
-        <v>-10.74</v>
+        <v>-69.06</v>
       </c>
       <c r="L68" t="n">
-        <v>122.6</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:15:44</t>
+          <t>07:11:49</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="F69" t="n">
-        <v>5.88</v>
+        <v>8.16</v>
       </c>
       <c r="G69" t="n">
-        <v>236.4</v>
+        <v>238.5</v>
       </c>
       <c r="H69" t="n">
-        <v>81.8</v>
+        <v>39.1</v>
       </c>
       <c r="I69" t="n">
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>59.4</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>113.92</v>
+        <v>-68.84999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>128.48</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:17:14</t>
+          <t>07:13:44</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="F70" t="n">
-        <v>6.02</v>
+        <v>6.31</v>
       </c>
       <c r="G70" t="n">
-        <v>252.7</v>
+        <v>252.5</v>
       </c>
       <c r="H70" t="n">
-        <v>92.3</v>
+        <v>53.1</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>53.16</v>
+        <v>-1.84</v>
       </c>
       <c r="K70" t="n">
-        <v>118</v>
+        <v>98.87</v>
       </c>
       <c r="L70" t="n">
-        <v>129.42</v>
+        <v>98.89</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:21:54</t>
+          <t>07:18:47</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="F71" t="n">
-        <v>5.26</v>
+        <v>5.64</v>
       </c>
       <c r="G71" t="n">
-        <v>251.8</v>
+        <v>245.4</v>
       </c>
       <c r="H71" t="n">
-        <v>80.8</v>
+        <v>46.7</v>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-239.25</v>
+        <v>-133.41</v>
       </c>
       <c r="K71" t="n">
-        <v>34.92</v>
+        <v>81.67</v>
       </c>
       <c r="L71" t="n">
-        <v>241.79</v>
+        <v>156.43</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:23:24</t>
+          <t>07:21:12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="F72" t="n">
-        <v>8.16</v>
+        <v>5.46</v>
       </c>
       <c r="G72" t="n">
-        <v>250.9</v>
+        <v>250.7</v>
       </c>
       <c r="H72" t="n">
-        <v>83</v>
+        <v>39.6</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>335.99</v>
+        <v>141.97</v>
       </c>
       <c r="K72" t="n">
-        <v>-93.45999999999999</v>
+        <v>-96.48</v>
       </c>
       <c r="L72" t="n">
-        <v>348.75</v>
+        <v>171.66</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:25:19</t>
+          <t>07:22:12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.21</v>
+        <v>1.44</v>
       </c>
       <c r="F73" t="n">
-        <v>8.16</v>
+        <v>4.8</v>
       </c>
       <c r="G73" t="n">
-        <v>253.9</v>
+        <v>240.8</v>
       </c>
       <c r="H73" t="n">
-        <v>78.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-114.47</v>
+        <v>107.29</v>
       </c>
       <c r="K73" t="n">
-        <v>118.52</v>
+        <v>-144.57</v>
       </c>
       <c r="L73" t="n">
-        <v>164.78</v>
+        <v>180.03</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:36:42</t>
+          <t>07:33:20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.46</v>
+        <v>0.86</v>
       </c>
       <c r="F74" t="n">
-        <v>7.22</v>
+        <v>8.16</v>
       </c>
       <c r="G74" t="n">
-        <v>239.9</v>
+        <v>248.9</v>
       </c>
       <c r="H74" t="n">
-        <v>77.90000000000001</v>
+        <v>44.6</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>40.23</v>
+        <v>-8.67</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.65</v>
+        <v>-30.53</v>
       </c>
       <c r="L74" t="n">
-        <v>72.78</v>
+        <v>31.73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:38:47</t>
+          <t>07:35:08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.13</v>
+        <v>1.41</v>
       </c>
       <c r="F75" t="n">
-        <v>8.16</v>
+        <v>8.02</v>
       </c>
       <c r="G75" t="n">
-        <v>243</v>
+        <v>255.4</v>
       </c>
       <c r="H75" t="n">
-        <v>82.5</v>
+        <v>49.1</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>-41.66</v>
+        <v>-4.73</v>
       </c>
       <c r="K75" t="n">
-        <v>-100.42</v>
+        <v>-25</v>
       </c>
       <c r="L75" t="n">
-        <v>108.72</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:40:46</t>
+          <t>07:36:31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="F76" t="n">
-        <v>3.04</v>
+        <v>8.16</v>
       </c>
       <c r="G76" t="n">
-        <v>252.4</v>
+        <v>236</v>
       </c>
       <c r="H76" t="n">
-        <v>80.09999999999999</v>
+        <v>44.3</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>58.75</v>
+        <v>-31.39</v>
       </c>
       <c r="K76" t="n">
-        <v>-21.41</v>
+        <v>6.37</v>
       </c>
       <c r="L76" t="n">
-        <v>62.52</v>
+        <v>32.03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:46:56</t>
+          <t>07:39:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="F77" t="n">
-        <v>7.88</v>
+        <v>8.16</v>
       </c>
       <c r="G77" t="n">
-        <v>265.2</v>
+        <v>245.5</v>
       </c>
       <c r="H77" t="n">
-        <v>74.7</v>
+        <v>41.2</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J77" t="n">
-        <v>-40.11</v>
+        <v>3.47</v>
       </c>
       <c r="K77" t="n">
-        <v>73.09</v>
+        <v>58.14</v>
       </c>
       <c r="L77" t="n">
-        <v>83.37</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:48:21</t>
+          <t>07:41:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="F78" t="n">
-        <v>6.08</v>
+        <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>227.5</v>
+        <v>241.1</v>
       </c>
       <c r="H78" t="n">
-        <v>81.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-93.90000000000001</v>
+        <v>36.32</v>
       </c>
       <c r="K78" t="n">
-        <v>-46.93</v>
+        <v>-21.36</v>
       </c>
       <c r="L78" t="n">
-        <v>104.98</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:49:08</t>
+          <t>07:42:27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.41</v>
+        <v>0.97</v>
       </c>
       <c r="F79" t="n">
-        <v>6.82</v>
+        <v>5.75</v>
       </c>
       <c r="G79" t="n">
-        <v>247.8</v>
+        <v>231.5</v>
       </c>
       <c r="H79" t="n">
-        <v>83.59999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J79" t="n">
-        <v>92.18000000000001</v>
+        <v>-37.62</v>
       </c>
       <c r="K79" t="n">
-        <v>-45.15</v>
+        <v>3.93</v>
       </c>
       <c r="L79" t="n">
-        <v>102.65</v>
+        <v>37.83</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:53:14</t>
+          <t>07:46:54</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="F80" t="n">
         <v>8.16</v>
       </c>
       <c r="G80" t="n">
-        <v>217.9</v>
+        <v>244.1</v>
       </c>
       <c r="H80" t="n">
-        <v>84.8</v>
+        <v>50.8</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>88.05</v>
+        <v>-33.06</v>
       </c>
       <c r="K80" t="n">
-        <v>71.26000000000001</v>
+        <v>-72.61</v>
       </c>
       <c r="L80" t="n">
-        <v>113.27</v>
+        <v>79.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:55:08</t>
+          <t>07:48:47</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="F81" t="n">
-        <v>1.44</v>
+        <v>8.16</v>
       </c>
       <c r="G81" t="n">
-        <v>251.6</v>
+        <v>246.9</v>
       </c>
       <c r="H81" t="n">
-        <v>73.2</v>
+        <v>39.1</v>
       </c>
       <c r="I81" t="n">
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-56.49</v>
+        <v>-69.20999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>52.13</v>
+        <v>-45.12</v>
       </c>
       <c r="L81" t="n">
-        <v>76.87</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:56:33</t>
+          <t>07:51:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="F82" t="n">
-        <v>3.83</v>
+        <v>5.34</v>
       </c>
       <c r="G82" t="n">
-        <v>229.5</v>
+        <v>238.4</v>
       </c>
       <c r="H82" t="n">
-        <v>83.2</v>
+        <v>61</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>-42.86</v>
+        <v>-21.19</v>
       </c>
       <c r="K82" t="n">
-        <v>-61.28</v>
+        <v>82.98</v>
       </c>
       <c r="L82" t="n">
-        <v>74.78</v>
+        <v>85.65000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:02:22</t>
+          <t>07:56:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.49</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>8.16</v>
+        <v>3</v>
       </c>
       <c r="G83" t="n">
-        <v>244.2</v>
+        <v>235.4</v>
       </c>
       <c r="H83" t="n">
-        <v>81.59999999999999</v>
+        <v>22.3</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J83" t="n">
-        <v>91.84</v>
+        <v>-32.05</v>
       </c>
       <c r="K83" t="n">
-        <v>78.84</v>
+        <v>102.63</v>
       </c>
       <c r="L83" t="n">
-        <v>121.04</v>
+        <v>107.52</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:03:25</t>
+          <t>07:57:31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="F84" t="n">
-        <v>3.04</v>
+        <v>6.07</v>
       </c>
       <c r="G84" t="n">
-        <v>241</v>
+        <v>242.4</v>
       </c>
       <c r="H84" t="n">
-        <v>80.40000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-23.34</v>
+        <v>8.57</v>
       </c>
       <c r="K84" t="n">
-        <v>93.67</v>
+        <v>110.83</v>
       </c>
       <c r="L84" t="n">
-        <v>96.53</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:05:37</t>
+          <t>07:58:22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="F85" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="G85" t="n">
-        <v>245.4</v>
+        <v>242.3</v>
       </c>
       <c r="H85" t="n">
-        <v>73.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-49.88</v>
+        <v>37.75</v>
       </c>
       <c r="K85" t="n">
-        <v>85.78</v>
+        <v>-115.8</v>
       </c>
       <c r="L85" t="n">
-        <v>99.23</v>
+        <v>121.79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:10:21</t>
+          <t>08:02:43</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="F86" t="n">
-        <v>3.36</v>
+        <v>8.16</v>
       </c>
       <c r="G86" t="n">
-        <v>243.5</v>
+        <v>240.8</v>
       </c>
       <c r="H86" t="n">
-        <v>73.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>75.29000000000001</v>
+        <v>81.89</v>
       </c>
       <c r="K86" t="n">
-        <v>157.73</v>
+        <v>-166.11</v>
       </c>
       <c r="L86" t="n">
-        <v>174.78</v>
+        <v>185.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:12:13</t>
+          <t>08:03:28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.98</v>
+        <v>1.56</v>
       </c>
       <c r="F87" t="n">
         <v>8.16</v>
       </c>
       <c r="G87" t="n">
-        <v>243.3</v>
+        <v>254.8</v>
       </c>
       <c r="H87" t="n">
-        <v>77.3</v>
+        <v>46.3</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>283.93</v>
+        <v>-95.13</v>
       </c>
       <c r="K87" t="n">
-        <v>-159.98</v>
+        <v>-174.29</v>
       </c>
       <c r="L87" t="n">
-        <v>325.9</v>
+        <v>198.56</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:14:16</t>
+          <t>08:05:04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="F88" t="n">
-        <v>6.5</v>
+        <v>7.59</v>
       </c>
       <c r="G88" t="n">
-        <v>249.4</v>
+        <v>235.6</v>
       </c>
       <c r="H88" t="n">
-        <v>79.3</v>
+        <v>32.2</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>-110.49</v>
+        <v>226.9</v>
       </c>
       <c r="K88" t="n">
-        <v>-142.73</v>
+        <v>-129.65</v>
       </c>
       <c r="L88" t="n">
-        <v>180.49</v>
+        <v>261.33</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.97</v>
+        <v>1.56</v>
       </c>
       <c r="F14" t="n">
-        <v>5.05</v>
+        <v>7.82</v>
       </c>
       <c r="G14" t="n">
-        <v>245</v>
+        <v>241.8</v>
       </c>
       <c r="H14" t="n">
-        <v>79.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.6</v>
+        <v>-3.07</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.41</v>
+        <v>44.67</v>
       </c>
       <c r="L14" t="n">
-        <v>27.72</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:34:02</t>
+          <t>04:33:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="F15" t="n">
         <v>8.16</v>
       </c>
       <c r="G15" t="n">
-        <v>240.2</v>
+        <v>238.4</v>
       </c>
       <c r="H15" t="n">
-        <v>36.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>7.45</v>
+        <v>-0.34</v>
       </c>
       <c r="K15" t="n">
-        <v>19.99</v>
+        <v>-22.81</v>
       </c>
       <c r="L15" t="n">
-        <v>21.34</v>
+        <v>22.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:40</t>
+          <t>04:36:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="F16" t="n">
         <v>8.16</v>
       </c>
       <c r="G16" t="n">
-        <v>227.9</v>
+        <v>239.3</v>
       </c>
       <c r="H16" t="n">
-        <v>55.1</v>
+        <v>57.5</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>22</v>
+        <v>14.47</v>
       </c>
       <c r="K16" t="n">
-        <v>22.57</v>
+        <v>-32.3</v>
       </c>
       <c r="L16" t="n">
-        <v>31.52</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:14</t>
+          <t>04:39:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="F17" t="n">
-        <v>4.82</v>
+        <v>6.52</v>
       </c>
       <c r="G17" t="n">
-        <v>239.8</v>
+        <v>247.2</v>
       </c>
       <c r="H17" t="n">
-        <v>29.3</v>
+        <v>84.3</v>
       </c>
       <c r="I17" t="n">
         <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>40.58</v>
+        <v>-45.71</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="L17" t="n">
-        <v>41.71</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:07</t>
+          <t>04:40:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="F18" t="n">
-        <v>6.54</v>
+        <v>8.16</v>
       </c>
       <c r="G18" t="n">
-        <v>234.3</v>
+        <v>247.1</v>
       </c>
       <c r="H18" t="n">
-        <v>56.2</v>
+        <v>82</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.2</v>
+        <v>8.31</v>
       </c>
       <c r="K18" t="n">
-        <v>1.73</v>
+        <v>-52.82</v>
       </c>
       <c r="L18" t="n">
-        <v>58.22</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:43:41</t>
+          <t>04:43:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="F19" t="n">
-        <v>4.61</v>
+        <v>7.18</v>
       </c>
       <c r="G19" t="n">
-        <v>257.1</v>
+        <v>251.8</v>
       </c>
       <c r="H19" t="n">
-        <v>74</v>
+        <v>31.3</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>23.12</v>
+        <v>-27.03</v>
       </c>
       <c r="K19" t="n">
-        <v>-35.96</v>
+        <v>-36.74</v>
       </c>
       <c r="L19" t="n">
-        <v>42.75</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:47:46</t>
+          <t>04:47:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="F20" t="n">
-        <v>8.16</v>
+        <v>4.6</v>
       </c>
       <c r="G20" t="n">
-        <v>242.2</v>
+        <v>244.1</v>
       </c>
       <c r="H20" t="n">
-        <v>61.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>2.72</v>
+        <v>57.47</v>
       </c>
       <c r="K20" t="n">
-        <v>49.44</v>
+        <v>-54.57</v>
       </c>
       <c r="L20" t="n">
-        <v>49.51</v>
+        <v>79.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:49:47</t>
+          <t>04:49:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="F21" t="n">
         <v>8.16</v>
       </c>
       <c r="G21" t="n">
-        <v>257.5</v>
+        <v>242.7</v>
       </c>
       <c r="H21" t="n">
-        <v>80.2</v>
+        <v>49.5</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>24.42</v>
+        <v>-33.61</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.37</v>
+        <v>-76.25</v>
       </c>
       <c r="L21" t="n">
-        <v>24.65</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:51:57</t>
+          <t>04:50:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="F22" t="n">
-        <v>4.37</v>
+        <v>4.19</v>
       </c>
       <c r="G22" t="n">
-        <v>233.8</v>
+        <v>275.8</v>
       </c>
       <c r="H22" t="n">
-        <v>90.09999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="I22" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-52.27</v>
+        <v>51.78</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.23</v>
+        <v>-56.91</v>
       </c>
       <c r="L22" t="n">
-        <v>52.77</v>
+        <v>76.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:56:36</t>
+          <t>04:53:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.14</v>
+        <v>0.95</v>
       </c>
       <c r="F23" t="n">
-        <v>1.44</v>
+        <v>7.76</v>
       </c>
       <c r="G23" t="n">
-        <v>246.6</v>
+        <v>242.5</v>
       </c>
       <c r="H23" t="n">
-        <v>59.1</v>
+        <v>59.7</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>80.31</v>
+        <v>-59.89</v>
       </c>
       <c r="K23" t="n">
-        <v>-114.47</v>
+        <v>-127.6</v>
       </c>
       <c r="L23" t="n">
-        <v>139.83</v>
+        <v>140.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:58:18</t>
+          <t>04:54:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="F24" t="n">
-        <v>2.52</v>
+        <v>7.3</v>
       </c>
       <c r="G24" t="n">
-        <v>222.1</v>
+        <v>232.3</v>
       </c>
       <c r="H24" t="n">
-        <v>58.4</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>46.58</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>72.89</v>
+        <v>-2.4</v>
       </c>
       <c r="L24" t="n">
-        <v>86.5</v>
+        <v>95.95999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:59:05</t>
+          <t>04:56:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="F25" t="n">
-        <v>8.16</v>
+        <v>7.66</v>
       </c>
       <c r="G25" t="n">
-        <v>251.3</v>
+        <v>243.3</v>
       </c>
       <c r="H25" t="n">
-        <v>72.59999999999999</v>
+        <v>59</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-114.16</v>
+        <v>19.66</v>
       </c>
       <c r="K25" t="n">
-        <v>70.65000000000001</v>
+        <v>-130.99</v>
       </c>
       <c r="L25" t="n">
-        <v>134.25</v>
+        <v>132.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:04:23</t>
+          <t>04:59:23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.82</v>
+        <v>1.18</v>
       </c>
       <c r="F26" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="G26" t="n">
-        <v>244.1</v>
+        <v>239.7</v>
       </c>
       <c r="H26" t="n">
-        <v>25.2</v>
+        <v>44.3</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-151.2</v>
+        <v>125.2</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.74</v>
+        <v>128.59</v>
       </c>
       <c r="L26" t="n">
-        <v>151.25</v>
+        <v>179.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:05:36</t>
+          <t>05:01:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="F27" t="n">
-        <v>2.28</v>
+        <v>8.16</v>
       </c>
       <c r="G27" t="n">
-        <v>250.4</v>
+        <v>219.6</v>
       </c>
       <c r="H27" t="n">
-        <v>79.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="I27" t="n">
         <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>-137.79</v>
+        <v>-21</v>
       </c>
       <c r="K27" t="n">
-        <v>-85.05</v>
+        <v>-150.99</v>
       </c>
       <c r="L27" t="n">
-        <v>161.92</v>
+        <v>152.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:07:06</t>
+          <t>05:03:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="F28" t="n">
-        <v>6.57</v>
+        <v>3.41</v>
       </c>
       <c r="G28" t="n">
-        <v>241.9</v>
+        <v>236.5</v>
       </c>
       <c r="H28" t="n">
-        <v>42</v>
+        <v>45.1</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>131.56</v>
+        <v>-29.26</v>
       </c>
       <c r="K28" t="n">
-        <v>28.35</v>
+        <v>153.77</v>
       </c>
       <c r="L28" t="n">
-        <v>134.58</v>
+        <v>156.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:19:19</t>
+          <t>05:11:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.37</v>
+        <v>0.95</v>
       </c>
       <c r="F29" t="n">
-        <v>7.03</v>
+        <v>2.43</v>
       </c>
       <c r="G29" t="n">
-        <v>229.4</v>
+        <v>231.8</v>
       </c>
       <c r="H29" t="n">
-        <v>84.3</v>
+        <v>99</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.49</v>
+        <v>11.83</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.18</v>
+        <v>-28.4</v>
       </c>
       <c r="L29" t="n">
-        <v>27.68</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:21:16</t>
+          <t>05:12:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="F30" t="n">
-        <v>5.02</v>
+        <v>8.16</v>
       </c>
       <c r="G30" t="n">
-        <v>240.1</v>
+        <v>242.2</v>
       </c>
       <c r="H30" t="n">
-        <v>23.6</v>
+        <v>54.9</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>29.4</v>
+        <v>-15.95</v>
       </c>
       <c r="K30" t="n">
-        <v>15.43</v>
+        <v>22.96</v>
       </c>
       <c r="L30" t="n">
-        <v>33.2</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:23:24</t>
+          <t>05:13:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.36</v>
+        <v>0.96</v>
       </c>
       <c r="F31" t="n">
-        <v>3.41</v>
+        <v>1.26</v>
       </c>
       <c r="G31" t="n">
-        <v>244.6</v>
+        <v>244.9</v>
       </c>
       <c r="H31" t="n">
-        <v>51.7</v>
+        <v>46.4</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J31" t="n">
-        <v>13.08</v>
+        <v>37.81</v>
       </c>
       <c r="K31" t="n">
-        <v>-18.83</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>22.93</v>
+        <v>38.93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:28:47</t>
+          <t>05:19:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="F32" t="n">
-        <v>8.16</v>
+        <v>7.57</v>
       </c>
       <c r="G32" t="n">
-        <v>242.1</v>
+        <v>244.4</v>
       </c>
       <c r="H32" t="n">
-        <v>61.6</v>
+        <v>57.6</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J32" t="n">
-        <v>-23.67</v>
+        <v>-31.01</v>
       </c>
       <c r="K32" t="n">
-        <v>-28.24</v>
+        <v>-51.05</v>
       </c>
       <c r="L32" t="n">
-        <v>36.85</v>
+        <v>59.73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:30:36</t>
+          <t>05:20:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>3.86</v>
+        <v>2.42</v>
       </c>
       <c r="G33" t="n">
-        <v>238.6</v>
+        <v>241.9</v>
       </c>
       <c r="H33" t="n">
-        <v>82.7</v>
+        <v>50.3</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J33" t="n">
-        <v>3.69</v>
+        <v>47.93</v>
       </c>
       <c r="K33" t="n">
-        <v>47.63</v>
+        <v>-7.52</v>
       </c>
       <c r="L33" t="n">
-        <v>47.77</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:31:33</t>
+          <t>05:22:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.19</v>
+        <v>1.69</v>
       </c>
       <c r="F34" t="n">
-        <v>1.49</v>
+        <v>8.16</v>
       </c>
       <c r="G34" t="n">
-        <v>231.7</v>
+        <v>239.4</v>
       </c>
       <c r="H34" t="n">
-        <v>61.5</v>
+        <v>33.4</v>
       </c>
       <c r="I34" t="n">
         <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>11.35</v>
+        <v>-51.5</v>
       </c>
       <c r="K34" t="n">
-        <v>48.62</v>
+        <v>7.26</v>
       </c>
       <c r="L34" t="n">
-        <v>49.93</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:36:46</t>
+          <t>05:26:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="F35" t="n">
-        <v>6.02</v>
+        <v>2.9</v>
       </c>
       <c r="G35" t="n">
-        <v>237.2</v>
+        <v>241.9</v>
       </c>
       <c r="H35" t="n">
-        <v>81.7</v>
+        <v>45.8</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J35" t="n">
-        <v>6.23</v>
+        <v>53.46</v>
       </c>
       <c r="K35" t="n">
-        <v>61.93</v>
+        <v>-63.44</v>
       </c>
       <c r="L35" t="n">
-        <v>62.24</v>
+        <v>82.95999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:37:40</t>
+          <t>05:28:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="F36" t="n">
-        <v>1.6</v>
+        <v>8.16</v>
       </c>
       <c r="G36" t="n">
-        <v>243.9</v>
+        <v>228</v>
       </c>
       <c r="H36" t="n">
-        <v>65.5</v>
+        <v>64.7</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J36" t="n">
-        <v>-38.03</v>
+        <v>-42.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-55.5</v>
+        <v>41.21</v>
       </c>
       <c r="L36" t="n">
-        <v>67.28</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:39:28</t>
+          <t>05:29:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="F37" t="n">
-        <v>4.94</v>
+        <v>3.7</v>
       </c>
       <c r="G37" t="n">
-        <v>249.6</v>
+        <v>246.1</v>
       </c>
       <c r="H37" t="n">
-        <v>98</v>
+        <v>55.9</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>-49.95</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-22.01</v>
+        <v>-21.22</v>
       </c>
       <c r="L37" t="n">
-        <v>54.59</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:45:11</t>
+          <t>05:35:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="F38" t="n">
-        <v>8.16</v>
+        <v>1.35</v>
       </c>
       <c r="G38" t="n">
-        <v>251.3</v>
+        <v>247.7</v>
       </c>
       <c r="H38" t="n">
-        <v>83.3</v>
+        <v>54.9</v>
       </c>
       <c r="I38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>69.17</v>
+        <v>-112.64</v>
       </c>
       <c r="K38" t="n">
-        <v>85.8</v>
+        <v>-14.22</v>
       </c>
       <c r="L38" t="n">
-        <v>110.21</v>
+        <v>113.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:46:38</t>
+          <t>05:37:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="F39" t="n">
-        <v>5.16</v>
+        <v>7.14</v>
       </c>
       <c r="G39" t="n">
-        <v>243.2</v>
+        <v>252.8</v>
       </c>
       <c r="H39" t="n">
-        <v>47.6</v>
+        <v>58.8</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J39" t="n">
-        <v>78.62</v>
+        <v>-38.65</v>
       </c>
       <c r="K39" t="n">
-        <v>-100.94</v>
+        <v>-122.97</v>
       </c>
       <c r="L39" t="n">
-        <v>127.94</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:48:08</t>
+          <t>05:39:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.26</v>
+        <v>0.88</v>
       </c>
       <c r="F40" t="n">
-        <v>5.35</v>
+        <v>6.08</v>
       </c>
       <c r="G40" t="n">
-        <v>240.7</v>
+        <v>237.9</v>
       </c>
       <c r="H40" t="n">
-        <v>21.8</v>
+        <v>40.4</v>
       </c>
       <c r="I40" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-42.15</v>
+        <v>-49.41</v>
       </c>
       <c r="K40" t="n">
-        <v>-99.25</v>
+        <v>-126.56</v>
       </c>
       <c r="L40" t="n">
-        <v>107.83</v>
+        <v>135.87</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:51:36</t>
+          <t>05:43:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="F41" t="n">
-        <v>6.42</v>
+        <v>7.33</v>
       </c>
       <c r="G41" t="n">
-        <v>243.1</v>
+        <v>242.4</v>
       </c>
       <c r="H41" t="n">
-        <v>57.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>1.38</v>
+        <v>145.83</v>
       </c>
       <c r="K41" t="n">
-        <v>-154.5</v>
+        <v>-47.1</v>
       </c>
       <c r="L41" t="n">
-        <v>154.5</v>
+        <v>153.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:52:23</t>
+          <t>05:44:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.23</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>4.95</v>
+        <v>4.79</v>
       </c>
       <c r="G42" t="n">
-        <v>248.1</v>
+        <v>239.5</v>
       </c>
       <c r="H42" t="n">
-        <v>38.3</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-84.67</v>
+        <v>-133.95</v>
       </c>
       <c r="K42" t="n">
-        <v>-125.21</v>
+        <v>97.84</v>
       </c>
       <c r="L42" t="n">
-        <v>151.15</v>
+        <v>165.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:54:11</t>
+          <t>05:46:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="F43" t="n">
-        <v>7.36</v>
+        <v>3.7</v>
       </c>
       <c r="G43" t="n">
-        <v>248.6</v>
+        <v>253.3</v>
       </c>
       <c r="H43" t="n">
-        <v>88.90000000000001</v>
+        <v>29.2</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J43" t="n">
-        <v>-67.55</v>
+        <v>-68.81</v>
       </c>
       <c r="K43" t="n">
-        <v>130</v>
+        <v>-176.53</v>
       </c>
       <c r="L43" t="n">
-        <v>146.51</v>
+        <v>189.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:04:00</t>
+          <t>05:57:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="F44" t="n">
         <v>8.16</v>
       </c>
       <c r="G44" t="n">
-        <v>246.9</v>
+        <v>240</v>
       </c>
       <c r="H44" t="n">
-        <v>41.3</v>
+        <v>55.7</v>
       </c>
       <c r="I44" t="n">
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>25.8</v>
+        <v>-29.47</v>
       </c>
       <c r="K44" t="n">
-        <v>14.73</v>
+        <v>15.32</v>
       </c>
       <c r="L44" t="n">
-        <v>29.71</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:05:52</t>
+          <t>05:59:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="F45" t="n">
-        <v>8.16</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>239.8</v>
+        <v>239.2</v>
       </c>
       <c r="H45" t="n">
-        <v>83.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I45" t="n">
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-32.65</v>
+        <v>-33.69</v>
       </c>
       <c r="K45" t="n">
-        <v>-11</v>
+        <v>-0.98</v>
       </c>
       <c r="L45" t="n">
-        <v>34.45</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:06:38</t>
+          <t>06:01:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="F46" t="n">
-        <v>8.16</v>
+        <v>3.48</v>
       </c>
       <c r="G46" t="n">
-        <v>243.1</v>
+        <v>250.5</v>
       </c>
       <c r="H46" t="n">
-        <v>79.59999999999999</v>
+        <v>57.8</v>
       </c>
       <c r="I46" t="n">
         <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>5.22</v>
+        <v>32.97</v>
       </c>
       <c r="K46" t="n">
-        <v>-30.03</v>
+        <v>-4.58</v>
       </c>
       <c r="L46" t="n">
-        <v>30.49</v>
+        <v>33.29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:11:14</t>
+          <t>06:07:29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="F47" t="n">
-        <v>8.16</v>
+        <v>7.14</v>
       </c>
       <c r="G47" t="n">
-        <v>245</v>
+        <v>244.6</v>
       </c>
       <c r="H47" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="I47" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>-29.84</v>
+        <v>5.83</v>
       </c>
       <c r="K47" t="n">
-        <v>-29.39</v>
+        <v>45.48</v>
       </c>
       <c r="L47" t="n">
-        <v>41.88</v>
+        <v>45.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:11:56</t>
+          <t>06:08:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="F48" t="n">
-        <v>7.19</v>
+        <v>4.07</v>
       </c>
       <c r="G48" t="n">
-        <v>249.3</v>
+        <v>242.9</v>
       </c>
       <c r="H48" t="n">
-        <v>55.1</v>
+        <v>51.2</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.17</v>
+        <v>-58.82</v>
       </c>
       <c r="K48" t="n">
-        <v>38.83</v>
+        <v>-14.55</v>
       </c>
       <c r="L48" t="n">
-        <v>39.17</v>
+        <v>60.59</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:13:49</t>
+          <t>06:10:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2098,31 +2098,31 @@
         <v>1.36</v>
       </c>
       <c r="F49" t="n">
-        <v>2.45</v>
+        <v>7.25</v>
       </c>
       <c r="G49" t="n">
-        <v>251.8</v>
+        <v>239</v>
       </c>
       <c r="H49" t="n">
-        <v>45</v>
+        <v>50.6</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J49" t="n">
-        <v>37.79</v>
+        <v>41.68</v>
       </c>
       <c r="K49" t="n">
-        <v>12.42</v>
+        <v>6.82</v>
       </c>
       <c r="L49" t="n">
-        <v>39.78</v>
+        <v>42.23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:17:41</t>
+          <t>06:16:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="F50" t="n">
-        <v>1.59</v>
+        <v>8.16</v>
       </c>
       <c r="G50" t="n">
-        <v>233.6</v>
+        <v>261.2</v>
       </c>
       <c r="H50" t="n">
-        <v>56.6</v>
+        <v>59.7</v>
       </c>
       <c r="I50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J50" t="n">
-        <v>71.03</v>
+        <v>29.51</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7</v>
+        <v>-21.67</v>
       </c>
       <c r="L50" t="n">
-        <v>71.03</v>
+        <v>36.61</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:19:08</t>
+          <t>06:18:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.24</v>
+        <v>0.91</v>
       </c>
       <c r="F51" t="n">
-        <v>8.130000000000001</v>
+        <v>3.91</v>
       </c>
       <c r="G51" t="n">
-        <v>249.8</v>
+        <v>226.1</v>
       </c>
       <c r="H51" t="n">
-        <v>47.1</v>
+        <v>56.2</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>69.26000000000001</v>
+        <v>-49.59</v>
       </c>
       <c r="K51" t="n">
-        <v>-12.49</v>
+        <v>58.15</v>
       </c>
       <c r="L51" t="n">
-        <v>70.38</v>
+        <v>76.43000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:20:15</t>
+          <t>06:20:31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="F52" t="n">
-        <v>8.16</v>
+        <v>4.06</v>
       </c>
       <c r="G52" t="n">
-        <v>247.2</v>
+        <v>244.7</v>
       </c>
       <c r="H52" t="n">
-        <v>46.4</v>
+        <v>63</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-53.55</v>
+        <v>31.54</v>
       </c>
       <c r="K52" t="n">
-        <v>15.56</v>
+        <v>66.98</v>
       </c>
       <c r="L52" t="n">
-        <v>55.77</v>
+        <v>74.04000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:25:10</t>
+          <t>06:24:32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="F53" t="n">
-        <v>2.26</v>
+        <v>5.9</v>
       </c>
       <c r="G53" t="n">
-        <v>263.5</v>
+        <v>228.6</v>
       </c>
       <c r="H53" t="n">
-        <v>59.8</v>
+        <v>38</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J53" t="n">
-        <v>-104.67</v>
+        <v>117.34</v>
       </c>
       <c r="K53" t="n">
-        <v>14.88</v>
+        <v>-31.71</v>
       </c>
       <c r="L53" t="n">
-        <v>105.72</v>
+        <v>121.55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:27:23</t>
+          <t>06:26:13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.29</v>
+        <v>2.98</v>
       </c>
       <c r="F54" t="n">
-        <v>5.88</v>
+        <v>8.16</v>
       </c>
       <c r="G54" t="n">
-        <v>233.4</v>
+        <v>242.6</v>
       </c>
       <c r="H54" t="n">
-        <v>68.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>63.63</v>
+        <v>111.39</v>
       </c>
       <c r="K54" t="n">
-        <v>-58.35</v>
+        <v>112.05</v>
       </c>
       <c r="L54" t="n">
-        <v>86.34</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:28:50</t>
+          <t>06:27:36</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="F55" t="n">
-        <v>4.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>246.2</v>
+        <v>243.8</v>
       </c>
       <c r="H55" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>121.57</v>
+        <v>-65.16</v>
       </c>
       <c r="K55" t="n">
-        <v>3.5</v>
+        <v>126.71</v>
       </c>
       <c r="L55" t="n">
-        <v>121.62</v>
+        <v>142.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:32:45</t>
+          <t>06:32:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="F56" t="n">
-        <v>5.21</v>
+        <v>7.79</v>
       </c>
       <c r="G56" t="n">
-        <v>238.9</v>
+        <v>244.5</v>
       </c>
       <c r="H56" t="n">
-        <v>32.6</v>
+        <v>60.9</v>
       </c>
       <c r="I56" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J56" t="n">
-        <v>-121.56</v>
+        <v>-170.7</v>
       </c>
       <c r="K56" t="n">
-        <v>-43.1</v>
+        <v>-78.90000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>128.97</v>
+        <v>188.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:34:14</t>
+          <t>06:34:42</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="F57" t="n">
-        <v>5.58</v>
+        <v>2.28</v>
       </c>
       <c r="G57" t="n">
-        <v>236.4</v>
+        <v>232.5</v>
       </c>
       <c r="H57" t="n">
-        <v>85.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>113.7</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>-41.38</v>
+        <v>-136.75</v>
       </c>
       <c r="L57" t="n">
-        <v>121</v>
+        <v>156.24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:36:17</t>
+          <t>06:36:36</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="F58" t="n">
-        <v>8.16</v>
+        <v>3.09</v>
       </c>
       <c r="G58" t="n">
-        <v>242.7</v>
+        <v>239.3</v>
       </c>
       <c r="H58" t="n">
-        <v>33.9</v>
+        <v>73.5</v>
       </c>
       <c r="I58" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-54.9</v>
+        <v>-145.03</v>
       </c>
       <c r="K58" t="n">
-        <v>133.62</v>
+        <v>-64.47</v>
       </c>
       <c r="L58" t="n">
-        <v>144.45</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:46:58</t>
+          <t>06:47:29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="F59" t="n">
-        <v>4.09</v>
+        <v>2.82</v>
       </c>
       <c r="G59" t="n">
-        <v>248.4</v>
+        <v>236.5</v>
       </c>
       <c r="H59" t="n">
-        <v>50.8</v>
+        <v>61.3</v>
       </c>
       <c r="I59" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>10.93</v>
+        <v>-28</v>
       </c>
       <c r="K59" t="n">
-        <v>27.42</v>
+        <v>1.72</v>
       </c>
       <c r="L59" t="n">
-        <v>29.51</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:49:36</t>
+          <t>06:49:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="F60" t="n">
-        <v>7.67</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>243.4</v>
+        <v>241.6</v>
       </c>
       <c r="H60" t="n">
-        <v>58.5</v>
+        <v>34.9</v>
       </c>
       <c r="I60" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>6.12</v>
+        <v>7.75</v>
       </c>
       <c r="K60" t="n">
-        <v>-28.84</v>
+        <v>-29.62</v>
       </c>
       <c r="L60" t="n">
-        <v>29.48</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:51:11</t>
+          <t>06:50:53</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="F61" t="n">
-        <v>6.61</v>
+        <v>8.16</v>
       </c>
       <c r="G61" t="n">
-        <v>243.6</v>
+        <v>265.2</v>
       </c>
       <c r="H61" t="n">
-        <v>69.5</v>
+        <v>50.7</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J61" t="n">
-        <v>18.56</v>
+        <v>31.79</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.87</v>
+        <v>-15.46</v>
       </c>
       <c r="L61" t="n">
-        <v>22.59</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:56:33</t>
+          <t>06:56:42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.4</v>
+        <v>0.89</v>
       </c>
       <c r="F62" t="n">
-        <v>5.65</v>
+        <v>4.06</v>
       </c>
       <c r="G62" t="n">
-        <v>241.6</v>
+        <v>226.3</v>
       </c>
       <c r="H62" t="n">
-        <v>42.9</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-50.91</v>
+        <v>-47.84</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.94</v>
+        <v>-16.6</v>
       </c>
       <c r="L62" t="n">
-        <v>51.06</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:58:13</t>
+          <t>06:59:02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="F63" t="n">
         <v>8.16</v>
       </c>
       <c r="G63" t="n">
-        <v>233.8</v>
+        <v>232.4</v>
       </c>
       <c r="H63" t="n">
-        <v>47.2</v>
+        <v>60.7</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>6.72</v>
+        <v>23.25</v>
       </c>
       <c r="K63" t="n">
-        <v>44.64</v>
+        <v>-53.09</v>
       </c>
       <c r="L63" t="n">
-        <v>45.14</v>
+        <v>57.96</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:59:14</t>
+          <t>07:00:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>0.99</v>
+        <v>1.38</v>
       </c>
       <c r="F64" t="n">
-        <v>2.24</v>
+        <v>6.74</v>
       </c>
       <c r="G64" t="n">
-        <v>244.7</v>
+        <v>240.5</v>
       </c>
       <c r="H64" t="n">
-        <v>36.6</v>
+        <v>48.5</v>
       </c>
       <c r="I64" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-26.77</v>
+        <v>-30.37</v>
       </c>
       <c r="K64" t="n">
-        <v>-43.87</v>
+        <v>45.46</v>
       </c>
       <c r="L64" t="n">
-        <v>51.4</v>
+        <v>54.67</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:04:12</t>
+          <t>07:04:22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.88</v>
+        <v>1.02</v>
       </c>
       <c r="F65" t="n">
-        <v>8.16</v>
+        <v>3.61</v>
       </c>
       <c r="G65" t="n">
-        <v>246.5</v>
+        <v>225.4</v>
       </c>
       <c r="H65" t="n">
-        <v>37.2</v>
+        <v>44</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-100.64</v>
+        <v>-35.62</v>
       </c>
       <c r="K65" t="n">
-        <v>-23.8</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>103.42</v>
+        <v>81.09</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:06:05</t>
+          <t>07:06:06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="F66" t="n">
-        <v>5.65</v>
+        <v>5.05</v>
       </c>
       <c r="G66" t="n">
-        <v>230.5</v>
+        <v>239.3</v>
       </c>
       <c r="H66" t="n">
-        <v>59.4</v>
+        <v>44.5</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>24.19</v>
+        <v>-33.44</v>
       </c>
       <c r="K66" t="n">
-        <v>116.08</v>
+        <v>-61.05</v>
       </c>
       <c r="L66" t="n">
-        <v>118.58</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:07:17</t>
+          <t>07:07:03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="F67" t="n">
-        <v>4.39</v>
+        <v>5.6</v>
       </c>
       <c r="G67" t="n">
-        <v>237.6</v>
+        <v>245.7</v>
       </c>
       <c r="H67" t="n">
-        <v>21.2</v>
+        <v>48.3</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-53.08</v>
+        <v>-72.94</v>
       </c>
       <c r="K67" t="n">
-        <v>-25.34</v>
+        <v>9.68</v>
       </c>
       <c r="L67" t="n">
-        <v>58.82</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:10:43</t>
+          <t>07:11:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="F68" t="n">
-        <v>6.98</v>
+        <v>7.83</v>
       </c>
       <c r="G68" t="n">
-        <v>243.6</v>
+        <v>247</v>
       </c>
       <c r="H68" t="n">
-        <v>79</v>
+        <v>58.3</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>22.31</v>
+        <v>-104.94</v>
       </c>
       <c r="K68" t="n">
-        <v>-69.06</v>
+        <v>88.27</v>
       </c>
       <c r="L68" t="n">
-        <v>72.56999999999999</v>
+        <v>137.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:11:49</t>
+          <t>07:13:08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="F69" t="n">
-        <v>8.16</v>
+        <v>4.39</v>
       </c>
       <c r="G69" t="n">
-        <v>238.5</v>
+        <v>228.9</v>
       </c>
       <c r="H69" t="n">
-        <v>39.1</v>
+        <v>42.2</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>82.04000000000001</v>
+        <v>-56.16</v>
       </c>
       <c r="K69" t="n">
-        <v>-68.84999999999999</v>
+        <v>104.02</v>
       </c>
       <c r="L69" t="n">
-        <v>107.1</v>
+        <v>118.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:13:44</t>
+          <t>07:15:37</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="F70" t="n">
-        <v>6.31</v>
+        <v>8.16</v>
       </c>
       <c r="G70" t="n">
-        <v>252.5</v>
+        <v>243.7</v>
       </c>
       <c r="H70" t="n">
-        <v>53.1</v>
+        <v>92.5</v>
       </c>
       <c r="I70" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.84</v>
+        <v>-39.12</v>
       </c>
       <c r="K70" t="n">
-        <v>98.87</v>
+        <v>-149.57</v>
       </c>
       <c r="L70" t="n">
-        <v>98.89</v>
+        <v>154.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:18:47</t>
+          <t>07:20:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="F71" t="n">
-        <v>5.64</v>
+        <v>7.57</v>
       </c>
       <c r="G71" t="n">
-        <v>245.4</v>
+        <v>226.5</v>
       </c>
       <c r="H71" t="n">
-        <v>46.7</v>
+        <v>53.4</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>-133.41</v>
+        <v>-119.65</v>
       </c>
       <c r="K71" t="n">
-        <v>81.67</v>
+        <v>-55.08</v>
       </c>
       <c r="L71" t="n">
-        <v>156.43</v>
+        <v>131.72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:21:12</t>
+          <t>07:22:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="F72" t="n">
-        <v>5.46</v>
+        <v>7.9</v>
       </c>
       <c r="G72" t="n">
-        <v>250.7</v>
+        <v>238.1</v>
       </c>
       <c r="H72" t="n">
-        <v>39.6</v>
+        <v>49.6</v>
       </c>
       <c r="I72" t="n">
         <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>141.97</v>
+        <v>-50.12</v>
       </c>
       <c r="K72" t="n">
-        <v>-96.48</v>
+        <v>-134.39</v>
       </c>
       <c r="L72" t="n">
-        <v>171.66</v>
+        <v>143.43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:22:12</t>
+          <t>07:24:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="F73" t="n">
-        <v>4.8</v>
+        <v>8.16</v>
       </c>
       <c r="G73" t="n">
-        <v>240.8</v>
+        <v>237.9</v>
       </c>
       <c r="H73" t="n">
-        <v>94.8</v>
+        <v>60.4</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>107.29</v>
+        <v>139.12</v>
       </c>
       <c r="K73" t="n">
-        <v>-144.57</v>
+        <v>19.78</v>
       </c>
       <c r="L73" t="n">
-        <v>180.03</v>
+        <v>140.52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:33:20</t>
+          <t>07:31:26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.86</v>
+        <v>1.22</v>
       </c>
       <c r="F74" t="n">
         <v>8.16</v>
       </c>
       <c r="G74" t="n">
-        <v>248.9</v>
+        <v>242.5</v>
       </c>
       <c r="H74" t="n">
-        <v>44.6</v>
+        <v>24.4</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.67</v>
+        <v>-7.7</v>
       </c>
       <c r="K74" t="n">
-        <v>-30.53</v>
+        <v>-31.02</v>
       </c>
       <c r="L74" t="n">
-        <v>31.73</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:35:08</t>
+          <t>07:33:33</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="F75" t="n">
-        <v>8.02</v>
+        <v>4.02</v>
       </c>
       <c r="G75" t="n">
-        <v>255.4</v>
+        <v>254.6</v>
       </c>
       <c r="H75" t="n">
-        <v>49.1</v>
+        <v>52</v>
       </c>
       <c r="I75" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.73</v>
+        <v>25.07</v>
       </c>
       <c r="K75" t="n">
-        <v>-25</v>
+        <v>10.2</v>
       </c>
       <c r="L75" t="n">
-        <v>25.44</v>
+        <v>27.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:36:31</t>
+          <t>07:34:46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="F76" t="n">
         <v>8.16</v>
       </c>
       <c r="G76" t="n">
-        <v>236</v>
+        <v>240.9</v>
       </c>
       <c r="H76" t="n">
-        <v>44.3</v>
+        <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.39</v>
+        <v>-13.46</v>
       </c>
       <c r="K76" t="n">
-        <v>6.37</v>
+        <v>-28.48</v>
       </c>
       <c r="L76" t="n">
-        <v>32.03</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:39:45</t>
+          <t>07:39:47</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="F77" t="n">
         <v>8.16</v>
       </c>
       <c r="G77" t="n">
-        <v>245.5</v>
+        <v>241.2</v>
       </c>
       <c r="H77" t="n">
-        <v>41.2</v>
+        <v>52.8</v>
       </c>
       <c r="I77" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>3.47</v>
+        <v>-36.72</v>
       </c>
       <c r="K77" t="n">
-        <v>58.14</v>
+        <v>-10.42</v>
       </c>
       <c r="L77" t="n">
-        <v>58.24</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:41:31</t>
+          <t>07:42:24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>5.22</v>
       </c>
       <c r="G78" t="n">
-        <v>241.1</v>
+        <v>238.4</v>
       </c>
       <c r="H78" t="n">
-        <v>62.6</v>
+        <v>56.7</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>36.32</v>
+        <v>37.1</v>
       </c>
       <c r="K78" t="n">
-        <v>-21.36</v>
+        <v>3.28</v>
       </c>
       <c r="L78" t="n">
-        <v>42.14</v>
+        <v>37.24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:42:27</t>
+          <t>07:44:34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>0.97</v>
+        <v>1.27</v>
       </c>
       <c r="F79" t="n">
-        <v>5.75</v>
+        <v>1.57</v>
       </c>
       <c r="G79" t="n">
-        <v>231.5</v>
+        <v>235.1</v>
       </c>
       <c r="H79" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="I79" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>-37.62</v>
+        <v>36.4</v>
       </c>
       <c r="K79" t="n">
-        <v>3.93</v>
+        <v>38.8</v>
       </c>
       <c r="L79" t="n">
-        <v>37.83</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:46:54</t>
+          <t>07:49:18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="F80" t="n">
-        <v>8.16</v>
+        <v>7.51</v>
       </c>
       <c r="G80" t="n">
-        <v>244.1</v>
+        <v>246.9</v>
       </c>
       <c r="H80" t="n">
-        <v>50.8</v>
+        <v>59.5</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>-33.06</v>
+        <v>-39.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-72.61</v>
+        <v>60.63</v>
       </c>
       <c r="L80" t="n">
-        <v>79.78</v>
+        <v>72.12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:48:47</t>
+          <t>07:51:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="F81" t="n">
-        <v>8.16</v>
+        <v>5.19</v>
       </c>
       <c r="G81" t="n">
-        <v>246.9</v>
+        <v>235.6</v>
       </c>
       <c r="H81" t="n">
-        <v>39.1</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-69.20999999999999</v>
+        <v>61.32</v>
       </c>
       <c r="K81" t="n">
-        <v>-45.12</v>
+        <v>-13.55</v>
       </c>
       <c r="L81" t="n">
-        <v>82.62</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:51:13</t>
+          <t>07:52:05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="F82" t="n">
-        <v>5.34</v>
+        <v>8.16</v>
       </c>
       <c r="G82" t="n">
-        <v>238.4</v>
+        <v>242.8</v>
       </c>
       <c r="H82" t="n">
-        <v>61</v>
+        <v>58.2</v>
       </c>
       <c r="I82" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-21.19</v>
+        <v>-82.04000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>82.98</v>
+        <v>-20.32</v>
       </c>
       <c r="L82" t="n">
-        <v>85.65000000000001</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:56:00</t>
+          <t>07:56:52</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>8.16</v>
       </c>
       <c r="G83" t="n">
-        <v>235.4</v>
+        <v>235.6</v>
       </c>
       <c r="H83" t="n">
-        <v>22.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I83" t="n">
         <v>32</v>
       </c>
       <c r="J83" t="n">
-        <v>-32.05</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>102.63</v>
+        <v>58.11</v>
       </c>
       <c r="L83" t="n">
-        <v>107.52</v>
+        <v>98.01000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:57:31</t>
+          <t>07:58:31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="F84" t="n">
-        <v>6.07</v>
+        <v>8.16</v>
       </c>
       <c r="G84" t="n">
-        <v>242.4</v>
+        <v>245.6</v>
       </c>
       <c r="H84" t="n">
-        <v>55.7</v>
+        <v>15.4</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>8.57</v>
+        <v>25.06</v>
       </c>
       <c r="K84" t="n">
-        <v>110.83</v>
+        <v>-103.54</v>
       </c>
       <c r="L84" t="n">
-        <v>111.16</v>
+        <v>106.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:58:22</t>
+          <t>08:00:28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="F85" t="n">
-        <v>2.24</v>
+        <v>8.16</v>
       </c>
       <c r="G85" t="n">
-        <v>242.3</v>
+        <v>249.9</v>
       </c>
       <c r="H85" t="n">
-        <v>86.59999999999999</v>
+        <v>43.4</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>37.75</v>
+        <v>122.14</v>
       </c>
       <c r="K85" t="n">
-        <v>-115.8</v>
+        <v>-11.83</v>
       </c>
       <c r="L85" t="n">
-        <v>121.79</v>
+        <v>122.71</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:02:43</t>
+          <t>08:05:45</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3652,31 +3652,31 @@
         <v>1.46</v>
       </c>
       <c r="F86" t="n">
-        <v>8.16</v>
+        <v>4.11</v>
       </c>
       <c r="G86" t="n">
-        <v>240.8</v>
+        <v>239.5</v>
       </c>
       <c r="H86" t="n">
-        <v>81.59999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>81.89</v>
+        <v>158.13</v>
       </c>
       <c r="K86" t="n">
-        <v>-166.11</v>
+        <v>41.24</v>
       </c>
       <c r="L86" t="n">
-        <v>185.2</v>
+        <v>163.42</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:03:28</t>
+          <t>08:07:51</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="F87" t="n">
-        <v>8.16</v>
+        <v>7.23</v>
       </c>
       <c r="G87" t="n">
-        <v>254.8</v>
+        <v>239.7</v>
       </c>
       <c r="H87" t="n">
-        <v>46.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-95.13</v>
+        <v>-169.75</v>
       </c>
       <c r="K87" t="n">
-        <v>-174.29</v>
+        <v>-12.11</v>
       </c>
       <c r="L87" t="n">
-        <v>198.56</v>
+        <v>170.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:05:04</t>
+          <t>08:08:56</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="F88" t="n">
-        <v>7.59</v>
+        <v>8.16</v>
       </c>
       <c r="G88" t="n">
-        <v>235.6</v>
+        <v>245.1</v>
       </c>
       <c r="H88" t="n">
-        <v>32.2</v>
+        <v>71.5</v>
       </c>
       <c r="I88" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>226.9</v>
+        <v>104.48</v>
       </c>
       <c r="K88" t="n">
-        <v>-129.65</v>
+        <v>-157.28</v>
       </c>
       <c r="L88" t="n">
-        <v>261.33</v>
+        <v>188.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-06-06.xlsx
+++ b/output/2024-06-06.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.1</v>
+        <v>-14.42</v>
       </c>
       <c r="K14" t="n">
-        <v>41.13</v>
+        <v>45.27</v>
       </c>
       <c r="L14" t="n">
-        <v>43.16</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>41.02</v>
+        <v>40.03</v>
       </c>
       <c r="K15" t="n">
-        <v>54.21</v>
+        <v>52.9</v>
       </c>
       <c r="L15" t="n">
-        <v>67.98</v>
+        <v>66.34</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.48</v>
+        <v>-13.45</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.39</v>
+        <v>-43.54</v>
       </c>
       <c r="L16" t="n">
-        <v>42.28</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-53.19</v>
+        <v>-52.93</v>
       </c>
       <c r="K17" t="n">
-        <v>77.66</v>
+        <v>77.27</v>
       </c>
       <c r="L17" t="n">
-        <v>94.13</v>
+        <v>93.66</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>11.46</v>
+        <v>12.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-53.29</v>
+        <v>-57.39</v>
       </c>
       <c r="L18" t="n">
-        <v>54.5</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>4.53</v>
+        <v>4.58</v>
       </c>
       <c r="K19" t="n">
-        <v>81.54000000000001</v>
+        <v>82.47</v>
       </c>
       <c r="L19" t="n">
-        <v>81.67</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>15.34</v>
+        <v>17.76</v>
       </c>
       <c r="K20" t="n">
-        <v>-73.64</v>
+        <v>-85.25</v>
       </c>
       <c r="L20" t="n">
-        <v>75.22</v>
+        <v>87.08</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>65.12</v>
+        <v>66.27</v>
       </c>
       <c r="K21" t="n">
-        <v>165.06</v>
+        <v>168</v>
       </c>
       <c r="L21" t="n">
-        <v>177.44</v>
+        <v>180.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-10.02</v>
+        <v>-11.82</v>
       </c>
       <c r="K22" t="n">
-        <v>81.54000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="L22" t="n">
-        <v>82.16</v>
+        <v>96.98</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-111.86</v>
+        <v>-122.64</v>
       </c>
       <c r="K23" t="n">
-        <v>-145.33</v>
+        <v>-159.34</v>
       </c>
       <c r="L23" t="n">
-        <v>183.39</v>
+        <v>201.07</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>76.58</v>
+        <v>98.37</v>
       </c>
       <c r="K24" t="n">
-        <v>-65.89</v>
+        <v>-84.63</v>
       </c>
       <c r="L24" t="n">
-        <v>101.03</v>
+        <v>129.77</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>42.4</v>
+        <v>48.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-159.48</v>
+        <v>-181.99</v>
       </c>
       <c r="L25" t="n">
-        <v>165.02</v>
+        <v>188.31</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-164.31</v>
+        <v>-210.49</v>
       </c>
       <c r="K26" t="n">
-        <v>34.03</v>
+        <v>43.59</v>
       </c>
       <c r="L26" t="n">
-        <v>167.8</v>
+        <v>214.96</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>149.78</v>
+        <v>195.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-37.19</v>
+        <v>-48.52</v>
       </c>
       <c r="L27" t="n">
-        <v>154.33</v>
+        <v>201.33</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-58.25</v>
+        <v>-76.43000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-130.56</v>
+        <v>-171.32</v>
       </c>
       <c r="L28" t="n">
-        <v>142.96</v>
+        <v>187.59</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.27</v>
+        <v>-30.12</v>
       </c>
       <c r="K29" t="n">
-        <v>-29.17</v>
+        <v>-32.22</v>
       </c>
       <c r="L29" t="n">
-        <v>39.93</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>60.32</v>
+        <v>60.07</v>
       </c>
       <c r="K30" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="L30" t="n">
-        <v>76.22</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.51</v>
+        <v>-24.83</v>
       </c>
       <c r="K31" t="n">
-        <v>40.5</v>
+        <v>44.69</v>
       </c>
       <c r="L31" t="n">
-        <v>46.34</v>
+        <v>51.13</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>22.02</v>
+        <v>25.59</v>
       </c>
       <c r="K32" t="n">
-        <v>-30.78</v>
+        <v>-35.78</v>
       </c>
       <c r="L32" t="n">
-        <v>37.85</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>71.56</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>18.55</v>
+        <v>19.17</v>
       </c>
       <c r="L33" t="n">
-        <v>73.92</v>
+        <v>76.38</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>31.55</v>
+        <v>35.68</v>
       </c>
       <c r="K34" t="n">
-        <v>-43.16</v>
+        <v>-48.81</v>
       </c>
       <c r="L34" t="n">
-        <v>53.46</v>
+        <v>60.46</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>90.18000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="K35" t="n">
-        <v>-48.14</v>
+        <v>-53.05</v>
       </c>
       <c r="L35" t="n">
-        <v>102.23</v>
+        <v>112.67</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>41.09</v>
+        <v>48.97</v>
       </c>
       <c r="K36" t="n">
-        <v>-78.56999999999999</v>
+        <v>-93.62</v>
       </c>
       <c r="L36" t="n">
-        <v>88.66</v>
+        <v>105.65</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>7.8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>86.06999999999999</v>
+        <v>99.94</v>
       </c>
       <c r="L37" t="n">
-        <v>86.42</v>
+        <v>100.35</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>180.62</v>
+        <v>196</v>
       </c>
       <c r="K38" t="n">
-        <v>-107.19</v>
+        <v>-116.31</v>
       </c>
       <c r="L38" t="n">
-        <v>210.03</v>
+        <v>227.91</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>130.7</v>
+        <v>151.44</v>
       </c>
       <c r="K39" t="n">
-        <v>-72.83</v>
+        <v>-84.39</v>
       </c>
       <c r="L39" t="n">
-        <v>149.62</v>
+        <v>173.36</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>-125.32</v>
+        <v>-141.55</v>
       </c>
       <c r="K40" t="n">
-        <v>115.45</v>
+        <v>130.4</v>
       </c>
       <c r="L40" t="n">
-        <v>170.39</v>
+        <v>192.46</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>-91.04000000000001</v>
+        <v>-121.76</v>
       </c>
       <c r="K41" t="n">
-        <v>-93.66</v>
+        <v>-125.26</v>
       </c>
       <c r="L41" t="n">
-        <v>130.61</v>
+        <v>174.69</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-138.07</v>
+        <v>-157.45</v>
       </c>
       <c r="K42" t="n">
-        <v>222.5</v>
+        <v>253.74</v>
       </c>
       <c r="L42" t="n">
-        <v>261.86</v>
+        <v>298.62</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-164</v>
+        <v>-199.48</v>
       </c>
       <c r="K43" t="n">
-        <v>106.36</v>
+        <v>129.37</v>
       </c>
       <c r="L43" t="n">
-        <v>195.47</v>
+        <v>237.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-46.12</v>
+        <v>-47.2</v>
       </c>
       <c r="K44" t="n">
-        <v>-36.66</v>
+        <v>-37.52</v>
       </c>
       <c r="L44" t="n">
-        <v>58.91</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-36.16</v>
+        <v>-39.01</v>
       </c>
       <c r="K45" t="n">
-        <v>18.49</v>
+        <v>19.94</v>
       </c>
       <c r="L45" t="n">
-        <v>40.61</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>32.04</v>
+        <v>36.13</v>
       </c>
       <c r="K46" t="n">
-        <v>-19.13</v>
+        <v>-21.56</v>
       </c>
       <c r="L46" t="n">
-        <v>37.32</v>
+        <v>42.08</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-10.85</v>
+        <v>-11.61</v>
       </c>
       <c r="K47" t="n">
-        <v>-74.20999999999999</v>
+        <v>-79.41</v>
       </c>
       <c r="L47" t="n">
-        <v>75</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-53.4</v>
+        <v>-60.07</v>
       </c>
       <c r="K48" t="n">
-        <v>-21.59</v>
+        <v>-24.29</v>
       </c>
       <c r="L48" t="n">
-        <v>57.6</v>
+        <v>64.79000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>12.46</v>
+        <v>14.38</v>
       </c>
       <c r="K49" t="n">
-        <v>-44.51</v>
+        <v>-51.37</v>
       </c>
       <c r="L49" t="n">
-        <v>46.22</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.22</v>
+        <v>-3.51</v>
       </c>
       <c r="K50" t="n">
-        <v>-127</v>
+        <v>-138.36</v>
       </c>
       <c r="L50" t="n">
-        <v>127.04</v>
+        <v>138.4</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-120.49</v>
+        <v>-128.09</v>
       </c>
       <c r="K51" t="n">
-        <v>-44.74</v>
+        <v>-47.56</v>
       </c>
       <c r="L51" t="n">
-        <v>128.53</v>
+        <v>136.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.53</v>
+        <v>-5.13</v>
       </c>
       <c r="K52" t="n">
-        <v>87.40000000000001</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>87.52</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>10.8</v>
+        <v>13.87</v>
       </c>
       <c r="K53" t="n">
-        <v>14.01</v>
+        <v>17.99</v>
       </c>
       <c r="L53" t="n">
-        <v>17.69</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>115.45</v>
+        <v>141.47</v>
       </c>
       <c r="K54" t="n">
-        <v>-12.42</v>
+        <v>-15.22</v>
       </c>
       <c r="L54" t="n">
-        <v>116.12</v>
+        <v>142.29</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-73.31999999999999</v>
+        <v>-97.04000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>-58.68</v>
+        <v>-77.67</v>
       </c>
       <c r="L55" t="n">
-        <v>93.91</v>
+        <v>124.3</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-172.15</v>
+        <v>-223.86</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.89</v>
+        <v>-3.76</v>
       </c>
       <c r="L56" t="n">
-        <v>172.17</v>
+        <v>223.89</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>18</v>
       </c>
       <c r="J57" t="n">
-        <v>90.56999999999999</v>
+        <v>111.14</v>
       </c>
       <c r="K57" t="n">
-        <v>180.52</v>
+        <v>221.52</v>
       </c>
       <c r="L57" t="n">
-        <v>201.96</v>
+        <v>247.84</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-61.1</v>
+        <v>-69.77</v>
       </c>
       <c r="K58" t="n">
-        <v>-322.28</v>
+        <v>-368.06</v>
       </c>
       <c r="L58" t="n">
-        <v>328.02</v>
+        <v>374.61</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>19</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.24</v>
+        <v>-45.94</v>
       </c>
       <c r="K59" t="n">
-        <v>22.32</v>
+        <v>23.71</v>
       </c>
       <c r="L59" t="n">
-        <v>48.66</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>17</v>
       </c>
       <c r="J60" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="K60" t="n">
-        <v>29.2</v>
+        <v>31.99</v>
       </c>
       <c r="L60" t="n">
-        <v>42.17</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>38.98</v>
+        <v>45.15</v>
       </c>
       <c r="K61" t="n">
-        <v>6.51</v>
+        <v>7.53</v>
       </c>
       <c r="L61" t="n">
-        <v>39.52</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>47.57</v>
+        <v>55.77</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.87</v>
+        <v>-4.54</v>
       </c>
       <c r="L62" t="n">
-        <v>47.73</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>35.07</v>
+        <v>37.95</v>
       </c>
       <c r="K63" t="n">
-        <v>45.14</v>
+        <v>48.84</v>
       </c>
       <c r="L63" t="n">
-        <v>57.16</v>
+        <v>61.86</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.99</v>
+        <v>-9.58</v>
       </c>
       <c r="K64" t="n">
-        <v>-64.37</v>
+        <v>-68.64</v>
       </c>
       <c r="L64" t="n">
-        <v>65</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>19</v>
       </c>
       <c r="J65" t="n">
-        <v>-101.8</v>
+        <v>-114.52</v>
       </c>
       <c r="K65" t="n">
-        <v>21.51</v>
+        <v>24.2</v>
       </c>
       <c r="L65" t="n">
-        <v>104.05</v>
+        <v>117.05</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-132.44</v>
+        <v>-136.68</v>
       </c>
       <c r="K66" t="n">
-        <v>8.550000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="L66" t="n">
-        <v>132.72</v>
+        <v>136.97</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.95</v>
+        <v>-4.7</v>
       </c>
       <c r="K67" t="n">
-        <v>-79.52</v>
+        <v>-94.64</v>
       </c>
       <c r="L67" t="n">
-        <v>79.62</v>
+        <v>94.76000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-77.01000000000001</v>
+        <v>-95.44</v>
       </c>
       <c r="K68" t="n">
-        <v>-75.34999999999999</v>
+        <v>-93.38</v>
       </c>
       <c r="L68" t="n">
-        <v>107.74</v>
+        <v>133.53</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>17</v>
       </c>
       <c r="J69" t="n">
-        <v>45.45</v>
+        <v>52.65</v>
       </c>
       <c r="K69" t="n">
-        <v>142.85</v>
+        <v>165.49</v>
       </c>
       <c r="L69" t="n">
-        <v>149.91</v>
+        <v>173.67</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-184.51</v>
+        <v>-207.36</v>
       </c>
       <c r="K70" t="n">
-        <v>-37.6</v>
+        <v>-42.26</v>
       </c>
       <c r="L70" t="n">
-        <v>188.3</v>
+        <v>211.62</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>-149.94</v>
+        <v>-195.36</v>
       </c>
       <c r="K71" t="n">
-        <v>57.54</v>
+        <v>74.97</v>
       </c>
       <c r="L71" t="n">
-        <v>160.6</v>
+        <v>209.25</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-6.09</v>
+        <v>-6.8</v>
       </c>
       <c r="K72" t="n">
-        <v>286.76</v>
+        <v>320.43</v>
       </c>
       <c r="L72" t="n">
-        <v>286.82</v>
+        <v>320.5</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-53.26</v>
+        <v>-71.73</v>
       </c>
       <c r="K73" t="n">
-        <v>-9.41</v>
+        <v>-12.67</v>
       </c>
       <c r="L73" t="n">
-        <v>54.09</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>43.48</v>
+        <v>46.26</v>
       </c>
       <c r="K74" t="n">
-        <v>21.23</v>
+        <v>22.58</v>
       </c>
       <c r="L74" t="n">
-        <v>48.39</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.55</v>
+        <v>-2.67</v>
       </c>
       <c r="K75" t="n">
-        <v>60.19</v>
+        <v>63.03</v>
       </c>
       <c r="L75" t="n">
-        <v>60.24</v>
+        <v>63.09</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>30.63</v>
+        <v>36.09</v>
       </c>
       <c r="K76" t="n">
-        <v>-18.62</v>
+        <v>-21.94</v>
       </c>
       <c r="L76" t="n">
-        <v>35.85</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>32.84</v>
+        <v>33.46</v>
       </c>
       <c r="K77" t="n">
-        <v>-70.81999999999999</v>
+        <v>-72.17</v>
       </c>
       <c r="L77" t="n">
-        <v>78.06</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>51.51</v>
+        <v>56.93</v>
       </c>
       <c r="K78" t="n">
-        <v>-35.16</v>
+        <v>-38.86</v>
       </c>
       <c r="L78" t="n">
-        <v>62.36</v>
+        <v>68.93000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-64.92</v>
+        <v>-68.72</v>
       </c>
       <c r="K79" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="L79" t="n">
-        <v>64.95</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>107.92</v>
+        <v>117.07</v>
       </c>
       <c r="K80" t="n">
-        <v>67.02</v>
+        <v>72.7</v>
       </c>
       <c r="L80" t="n">
-        <v>127.04</v>
+        <v>137.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>56.11</v>
+        <v>67.97</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.01</v>
+        <v>-44.83</v>
       </c>
       <c r="L81" t="n">
-        <v>67.22</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>102.6</v>
+        <v>109.28</v>
       </c>
       <c r="K82" t="n">
-        <v>120.26</v>
+        <v>128.09</v>
       </c>
       <c r="L82" t="n">
-        <v>158.08</v>
+        <v>168.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-25.15</v>
+        <v>-27.84</v>
       </c>
       <c r="K83" t="n">
-        <v>-184.81</v>
+        <v>-204.56</v>
       </c>
       <c r="L83" t="n">
-        <v>186.52</v>
+        <v>206.45</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-72.36</v>
+        <v>-96.16</v>
       </c>
       <c r="K84" t="n">
-        <v>60.1</v>
+        <v>79.86</v>
       </c>
       <c r="L84" t="n">
-        <v>94.06</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-55.29</v>
+        <v>-62.28</v>
       </c>
       <c r="K85" t="n">
-        <v>150</v>
+        <v>168.96</v>
       </c>
       <c r="L85" t="n">
-        <v>159.86</v>
+        <v>180.07</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>84.34999999999999</v>
+        <v>98.77</v>
       </c>
       <c r="K86" t="n">
-        <v>-233.52</v>
+        <v>-273.44</v>
       </c>
       <c r="L86" t="n">
-        <v>248.28</v>
+        <v>290.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>-8.4</v>
+        <v>-10.17</v>
       </c>
       <c r="K87" t="n">
-        <v>-205.19</v>
+        <v>-248.38</v>
       </c>
       <c r="L87" t="n">
-        <v>205.36</v>
+        <v>248.59</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>157.77</v>
+        <v>200.25</v>
       </c>
       <c r="K88" t="n">
-        <v>37.44</v>
+        <v>47.52</v>
       </c>
       <c r="L88" t="n">
-        <v>162.15</v>
+        <v>205.81</v>
       </c>
     </row>
   </sheetData>
